--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
@@ -3,28 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808D8B0A-9AAF-4F30-92A3-7DB9389F016B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6804CE4-D03F-4043-9B0F-F3D888F5A19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【リクエストID】_クラス単体テスト" sheetId="23" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="24" r:id="rId4"/>
-    <sheet name="取引単体テスト" sheetId="25" r:id="rId5"/>
+    <sheet name="【テストターゲット名】_クラス単体" sheetId="23" r:id="rId3"/>
+    <sheet name="【リクエストID】_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="取引単体" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$295</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体テスト!$A$1:$R$314</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$295</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$314</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="457">
   <si>
     <t>テストデータシート名</t>
     <rPh sb="9" eb="10">
@@ -6289,6 +6289,10 @@
   </si>
   <si>
     <t>単体テスト仕様書(メッセージ)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リクエストID：</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7257,6 +7261,93 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="17" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -7355,93 +7446,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="17" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8896,55 +8900,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="139" t="s">
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="168" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="148" t="s">
+      <c r="P1" s="169"/>
+      <c r="Q1" s="169"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="177" t="s">
         <v>455</v>
       </c>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="124" t="s">
+      <c r="T1" s="178"/>
+      <c r="U1" s="178"/>
+      <c r="V1" s="178"/>
+      <c r="W1" s="178"/>
+      <c r="X1" s="178"/>
+      <c r="Y1" s="178"/>
+      <c r="Z1" s="179"/>
+      <c r="AA1" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="126" t="str">
+      <c r="AB1" s="154"/>
+      <c r="AC1" s="155" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="127"/>
-      <c r="AE1" s="127"/>
-      <c r="AF1" s="128"/>
-      <c r="AG1" s="133" t="str">
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="157"/>
+      <c r="AG1" s="162" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="134"/>
-      <c r="AI1" s="135"/>
+      <c r="AH1" s="163"/>
+      <c r="AI1" s="164"/>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
       <c r="AL1" s="23"/>
@@ -8952,51 +8956,51 @@
       <c r="AN1" s="24"/>
     </row>
     <row r="2" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="142"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="143"/>
-      <c r="R2" s="144"/>
-      <c r="S2" s="151"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="153"/>
-      <c r="AA2" s="124" t="s">
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="171"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="173"/>
+      <c r="S2" s="180"/>
+      <c r="T2" s="181"/>
+      <c r="U2" s="181"/>
+      <c r="V2" s="181"/>
+      <c r="W2" s="181"/>
+      <c r="X2" s="181"/>
+      <c r="Y2" s="181"/>
+      <c r="Z2" s="182"/>
+      <c r="AA2" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="125"/>
-      <c r="AC2" s="136" t="str">
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="165" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="137"/>
-      <c r="AE2" s="137"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="133" t="str">
+      <c r="AD2" s="166"/>
+      <c r="AE2" s="166"/>
+      <c r="AF2" s="167"/>
+      <c r="AG2" s="162" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="134"/>
-      <c r="AI2" s="135"/>
+      <c r="AH2" s="163"/>
+      <c r="AI2" s="164"/>
       <c r="AJ2" s="23"/>
       <c r="AK2" s="23"/>
       <c r="AL2" s="23"/>
@@ -9004,43 +9008,43 @@
       <c r="AN2" s="23"/>
     </row>
     <row r="3" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
-      <c r="M3" s="131"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="146"/>
-      <c r="Q3" s="146"/>
-      <c r="R3" s="147"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="155"/>
-      <c r="V3" s="155"/>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="155"/>
-      <c r="Z3" s="156"/>
-      <c r="AA3" s="124"/>
-      <c r="AB3" s="125"/>
-      <c r="AC3" s="126"/>
-      <c r="AD3" s="127"/>
-      <c r="AE3" s="127"/>
-      <c r="AF3" s="128"/>
-      <c r="AG3" s="133"/>
-      <c r="AH3" s="134"/>
-      <c r="AI3" s="135"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="175"/>
+      <c r="Q3" s="175"/>
+      <c r="R3" s="176"/>
+      <c r="S3" s="183"/>
+      <c r="T3" s="184"/>
+      <c r="U3" s="184"/>
+      <c r="V3" s="184"/>
+      <c r="W3" s="184"/>
+      <c r="X3" s="184"/>
+      <c r="Y3" s="184"/>
+      <c r="Z3" s="185"/>
+      <c r="AA3" s="153"/>
+      <c r="AB3" s="154"/>
+      <c r="AC3" s="155"/>
+      <c r="AD3" s="156"/>
+      <c r="AE3" s="156"/>
+      <c r="AF3" s="157"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="163"/>
+      <c r="AI3" s="164"/>
       <c r="AJ3" s="23"/>
       <c r="AK3" s="23"/>
       <c r="AL3" s="23"/>
@@ -9077,1020 +9081,1181 @@
       <c r="A7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="157" t="s">
+      <c r="B7" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="158"/>
-      <c r="D7" s="157" t="s">
+      <c r="C7" s="138"/>
+      <c r="D7" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="159"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="157" t="s">
+      <c r="E7" s="139"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="159"/>
-      <c r="I7" s="158"/>
-      <c r="J7" s="157" t="s">
+      <c r="H7" s="139"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="159"/>
-      <c r="L7" s="159"/>
-      <c r="M7" s="159"/>
-      <c r="N7" s="159"/>
-      <c r="O7" s="159"/>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="157" t="s">
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="M7" s="139"/>
+      <c r="N7" s="139"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="159"/>
-      <c r="S7" s="159"/>
-      <c r="T7" s="159"/>
-      <c r="U7" s="159"/>
-      <c r="V7" s="159"/>
-      <c r="W7" s="159"/>
-      <c r="X7" s="159"/>
-      <c r="Y7" s="159"/>
-      <c r="Z7" s="159"/>
-      <c r="AA7" s="159"/>
-      <c r="AB7" s="159"/>
-      <c r="AC7" s="159"/>
-      <c r="AD7" s="159"/>
-      <c r="AE7" s="158"/>
-      <c r="AF7" s="157" t="s">
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="139"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="139"/>
+      <c r="X7" s="139"/>
+      <c r="Y7" s="139"/>
+      <c r="Z7" s="139"/>
+      <c r="AA7" s="139"/>
+      <c r="AB7" s="139"/>
+      <c r="AC7" s="139"/>
+      <c r="AD7" s="139"/>
+      <c r="AE7" s="138"/>
+      <c r="AF7" s="137" t="s">
         <v>33</v>
       </c>
-      <c r="AG7" s="159"/>
-      <c r="AH7" s="159"/>
-      <c r="AI7" s="158"/>
+      <c r="AG7" s="139"/>
+      <c r="AH7" s="139"/>
+      <c r="AI7" s="138"/>
     </row>
     <row r="8" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="15"/>
-      <c r="B8" s="160"/>
-      <c r="C8" s="161"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="163"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="161"/>
-      <c r="J8" s="167"/>
-      <c r="K8" s="168"/>
-      <c r="L8" s="168"/>
-      <c r="M8" s="168"/>
-      <c r="N8" s="168"/>
-      <c r="O8" s="168"/>
-      <c r="P8" s="169"/>
-      <c r="Q8" s="170"/>
-      <c r="R8" s="171"/>
-      <c r="S8" s="171"/>
-      <c r="T8" s="171"/>
-      <c r="U8" s="171"/>
-      <c r="V8" s="171"/>
-      <c r="W8" s="171"/>
-      <c r="X8" s="171"/>
-      <c r="Y8" s="171"/>
-      <c r="Z8" s="171"/>
-      <c r="AA8" s="171"/>
-      <c r="AB8" s="171"/>
-      <c r="AC8" s="171"/>
-      <c r="AD8" s="171"/>
-      <c r="AE8" s="172"/>
-      <c r="AF8" s="167"/>
-      <c r="AG8" s="168"/>
-      <c r="AH8" s="168"/>
-      <c r="AI8" s="169"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="146"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="148"/>
+      <c r="N8" s="148"/>
+      <c r="O8" s="148"/>
+      <c r="P8" s="149"/>
+      <c r="Q8" s="150"/>
+      <c r="R8" s="151"/>
+      <c r="S8" s="151"/>
+      <c r="T8" s="151"/>
+      <c r="U8" s="151"/>
+      <c r="V8" s="151"/>
+      <c r="W8" s="151"/>
+      <c r="X8" s="151"/>
+      <c r="Y8" s="151"/>
+      <c r="Z8" s="151"/>
+      <c r="AA8" s="151"/>
+      <c r="AB8" s="151"/>
+      <c r="AC8" s="151"/>
+      <c r="AD8" s="151"/>
+      <c r="AE8" s="152"/>
+      <c r="AF8" s="147"/>
+      <c r="AG8" s="148"/>
+      <c r="AH8" s="148"/>
+      <c r="AI8" s="149"/>
     </row>
     <row r="9" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="14"/>
-      <c r="B9" s="173"/>
-      <c r="C9" s="174"/>
-      <c r="D9" s="175"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="177"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="178"/>
-      <c r="I9" s="174"/>
-      <c r="J9" s="179"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="180"/>
-      <c r="M9" s="180"/>
-      <c r="N9" s="180"/>
-      <c r="O9" s="180"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="182"/>
-      <c r="R9" s="183"/>
-      <c r="S9" s="183"/>
-      <c r="T9" s="183"/>
-      <c r="U9" s="183"/>
-      <c r="V9" s="183"/>
-      <c r="W9" s="183"/>
-      <c r="X9" s="183"/>
-      <c r="Y9" s="183"/>
-      <c r="Z9" s="183"/>
-      <c r="AA9" s="183"/>
-      <c r="AB9" s="183"/>
-      <c r="AC9" s="183"/>
-      <c r="AD9" s="183"/>
-      <c r="AE9" s="184"/>
-      <c r="AF9" s="179"/>
-      <c r="AG9" s="180"/>
-      <c r="AH9" s="180"/>
-      <c r="AI9" s="181"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="131"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="134"/>
+      <c r="S9" s="134"/>
+      <c r="T9" s="134"/>
+      <c r="U9" s="134"/>
+      <c r="V9" s="134"/>
+      <c r="W9" s="134"/>
+      <c r="X9" s="134"/>
+      <c r="Y9" s="134"/>
+      <c r="Z9" s="134"/>
+      <c r="AA9" s="134"/>
+      <c r="AB9" s="134"/>
+      <c r="AC9" s="134"/>
+      <c r="AD9" s="134"/>
+      <c r="AE9" s="135"/>
+      <c r="AF9" s="130"/>
+      <c r="AG9" s="131"/>
+      <c r="AH9" s="131"/>
+      <c r="AI9" s="132"/>
     </row>
     <row r="10" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="14"/>
-      <c r="B10" s="173"/>
-      <c r="C10" s="174"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="177"/>
-      <c r="G10" s="173"/>
-      <c r="H10" s="178"/>
-      <c r="I10" s="174"/>
-      <c r="J10" s="179"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="180"/>
-      <c r="M10" s="180"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="180"/>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="182"/>
-      <c r="R10" s="183"/>
-      <c r="S10" s="183"/>
-      <c r="T10" s="183"/>
-      <c r="U10" s="183"/>
-      <c r="V10" s="183"/>
-      <c r="W10" s="183"/>
-      <c r="X10" s="183"/>
-      <c r="Y10" s="183"/>
-      <c r="Z10" s="183"/>
-      <c r="AA10" s="183"/>
-      <c r="AB10" s="183"/>
-      <c r="AC10" s="183"/>
-      <c r="AD10" s="183"/>
-      <c r="AE10" s="184"/>
-      <c r="AF10" s="179"/>
-      <c r="AG10" s="180"/>
-      <c r="AH10" s="180"/>
-      <c r="AI10" s="181"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="134"/>
+      <c r="S10" s="134"/>
+      <c r="T10" s="134"/>
+      <c r="U10" s="134"/>
+      <c r="V10" s="134"/>
+      <c r="W10" s="134"/>
+      <c r="X10" s="134"/>
+      <c r="Y10" s="134"/>
+      <c r="Z10" s="134"/>
+      <c r="AA10" s="134"/>
+      <c r="AB10" s="134"/>
+      <c r="AC10" s="134"/>
+      <c r="AD10" s="134"/>
+      <c r="AE10" s="135"/>
+      <c r="AF10" s="130"/>
+      <c r="AG10" s="131"/>
+      <c r="AH10" s="131"/>
+      <c r="AI10" s="132"/>
     </row>
     <row r="11" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="14"/>
-      <c r="B11" s="173"/>
-      <c r="C11" s="174"/>
-      <c r="D11" s="175"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="177"/>
-      <c r="G11" s="173"/>
-      <c r="H11" s="178"/>
-      <c r="I11" s="174"/>
-      <c r="J11" s="179"/>
-      <c r="K11" s="180"/>
-      <c r="L11" s="180"/>
-      <c r="M11" s="180"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="180"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="182"/>
-      <c r="R11" s="183"/>
-      <c r="S11" s="183"/>
-      <c r="T11" s="183"/>
-      <c r="U11" s="183"/>
-      <c r="V11" s="183"/>
-      <c r="W11" s="183"/>
-      <c r="X11" s="183"/>
-      <c r="Y11" s="183"/>
-      <c r="Z11" s="183"/>
-      <c r="AA11" s="183"/>
-      <c r="AB11" s="183"/>
-      <c r="AC11" s="183"/>
-      <c r="AD11" s="183"/>
-      <c r="AE11" s="184"/>
-      <c r="AF11" s="179"/>
-      <c r="AG11" s="180"/>
-      <c r="AH11" s="180"/>
-      <c r="AI11" s="181"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="134"/>
+      <c r="U11" s="134"/>
+      <c r="V11" s="134"/>
+      <c r="W11" s="134"/>
+      <c r="X11" s="134"/>
+      <c r="Y11" s="134"/>
+      <c r="Z11" s="134"/>
+      <c r="AA11" s="134"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="134"/>
+      <c r="AD11" s="134"/>
+      <c r="AE11" s="135"/>
+      <c r="AF11" s="130"/>
+      <c r="AG11" s="131"/>
+      <c r="AH11" s="131"/>
+      <c r="AI11" s="132"/>
     </row>
     <row r="12" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="14"/>
-      <c r="B12" s="173"/>
-      <c r="C12" s="174"/>
-      <c r="D12" s="175"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="173"/>
-      <c r="H12" s="178"/>
-      <c r="I12" s="174"/>
-      <c r="J12" s="179"/>
-      <c r="K12" s="180"/>
-      <c r="L12" s="180"/>
-      <c r="M12" s="180"/>
-      <c r="N12" s="180"/>
-      <c r="O12" s="180"/>
-      <c r="P12" s="181"/>
-      <c r="Q12" s="182"/>
-      <c r="R12" s="183"/>
-      <c r="S12" s="183"/>
-      <c r="T12" s="183"/>
-      <c r="U12" s="183"/>
-      <c r="V12" s="183"/>
-      <c r="W12" s="183"/>
-      <c r="X12" s="183"/>
-      <c r="Y12" s="183"/>
-      <c r="Z12" s="183"/>
-      <c r="AA12" s="183"/>
-      <c r="AB12" s="183"/>
-      <c r="AC12" s="183"/>
-      <c r="AD12" s="183"/>
-      <c r="AE12" s="184"/>
-      <c r="AF12" s="179"/>
-      <c r="AG12" s="180"/>
-      <c r="AH12" s="180"/>
-      <c r="AI12" s="181"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="131"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="132"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="134"/>
+      <c r="S12" s="134"/>
+      <c r="T12" s="134"/>
+      <c r="U12" s="134"/>
+      <c r="V12" s="134"/>
+      <c r="W12" s="134"/>
+      <c r="X12" s="134"/>
+      <c r="Y12" s="134"/>
+      <c r="Z12" s="134"/>
+      <c r="AA12" s="134"/>
+      <c r="AB12" s="134"/>
+      <c r="AC12" s="134"/>
+      <c r="AD12" s="134"/>
+      <c r="AE12" s="135"/>
+      <c r="AF12" s="130"/>
+      <c r="AG12" s="131"/>
+      <c r="AH12" s="131"/>
+      <c r="AI12" s="132"/>
     </row>
     <row r="13" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="14"/>
-      <c r="B13" s="173"/>
-      <c r="C13" s="174"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="178"/>
-      <c r="I13" s="174"/>
-      <c r="J13" s="179"/>
-      <c r="K13" s="180"/>
-      <c r="L13" s="180"/>
-      <c r="M13" s="180"/>
-      <c r="N13" s="180"/>
-      <c r="O13" s="180"/>
-      <c r="P13" s="181"/>
-      <c r="Q13" s="182"/>
-      <c r="R13" s="183"/>
-      <c r="S13" s="183"/>
-      <c r="T13" s="183"/>
-      <c r="U13" s="183"/>
-      <c r="V13" s="183"/>
-      <c r="W13" s="183"/>
-      <c r="X13" s="183"/>
-      <c r="Y13" s="183"/>
-      <c r="Z13" s="183"/>
-      <c r="AA13" s="183"/>
-      <c r="AB13" s="183"/>
-      <c r="AC13" s="183"/>
-      <c r="AD13" s="183"/>
-      <c r="AE13" s="184"/>
-      <c r="AF13" s="179"/>
-      <c r="AG13" s="180"/>
-      <c r="AH13" s="180"/>
-      <c r="AI13" s="181"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="131"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="133"/>
+      <c r="R13" s="134"/>
+      <c r="S13" s="134"/>
+      <c r="T13" s="134"/>
+      <c r="U13" s="134"/>
+      <c r="V13" s="134"/>
+      <c r="W13" s="134"/>
+      <c r="X13" s="134"/>
+      <c r="Y13" s="134"/>
+      <c r="Z13" s="134"/>
+      <c r="AA13" s="134"/>
+      <c r="AB13" s="134"/>
+      <c r="AC13" s="134"/>
+      <c r="AD13" s="134"/>
+      <c r="AE13" s="135"/>
+      <c r="AF13" s="130"/>
+      <c r="AG13" s="131"/>
+      <c r="AH13" s="131"/>
+      <c r="AI13" s="132"/>
     </row>
     <row r="14" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="14"/>
-      <c r="B14" s="173"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="175"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="177"/>
-      <c r="G14" s="173"/>
-      <c r="H14" s="178"/>
-      <c r="I14" s="174"/>
-      <c r="J14" s="179"/>
-      <c r="K14" s="180"/>
-      <c r="L14" s="180"/>
-      <c r="M14" s="180"/>
-      <c r="N14" s="180"/>
-      <c r="O14" s="180"/>
-      <c r="P14" s="181"/>
-      <c r="Q14" s="182"/>
-      <c r="R14" s="183"/>
-      <c r="S14" s="183"/>
-      <c r="T14" s="183"/>
-      <c r="U14" s="183"/>
-      <c r="V14" s="183"/>
-      <c r="W14" s="183"/>
-      <c r="X14" s="183"/>
-      <c r="Y14" s="183"/>
-      <c r="Z14" s="183"/>
-      <c r="AA14" s="183"/>
-      <c r="AB14" s="183"/>
-      <c r="AC14" s="183"/>
-      <c r="AD14" s="183"/>
-      <c r="AE14" s="184"/>
-      <c r="AF14" s="179"/>
-      <c r="AG14" s="180"/>
-      <c r="AH14" s="180"/>
-      <c r="AI14" s="181"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="131"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="131"/>
+      <c r="P14" s="132"/>
+      <c r="Q14" s="133"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="134"/>
+      <c r="U14" s="134"/>
+      <c r="V14" s="134"/>
+      <c r="W14" s="134"/>
+      <c r="X14" s="134"/>
+      <c r="Y14" s="134"/>
+      <c r="Z14" s="134"/>
+      <c r="AA14" s="134"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="134"/>
+      <c r="AD14" s="134"/>
+      <c r="AE14" s="135"/>
+      <c r="AF14" s="130"/>
+      <c r="AG14" s="131"/>
+      <c r="AH14" s="131"/>
+      <c r="AI14" s="132"/>
     </row>
     <row r="15" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="173"/>
-      <c r="C15" s="174"/>
-      <c r="D15" s="175"/>
-      <c r="E15" s="176"/>
-      <c r="F15" s="177"/>
-      <c r="G15" s="173"/>
-      <c r="H15" s="178"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="179"/>
-      <c r="K15" s="180"/>
-      <c r="L15" s="180"/>
-      <c r="M15" s="180"/>
-      <c r="N15" s="180"/>
-      <c r="O15" s="180"/>
-      <c r="P15" s="181"/>
-      <c r="Q15" s="182"/>
-      <c r="R15" s="183"/>
-      <c r="S15" s="183"/>
-      <c r="T15" s="183"/>
-      <c r="U15" s="183"/>
-      <c r="V15" s="183"/>
-      <c r="W15" s="183"/>
-      <c r="X15" s="183"/>
-      <c r="Y15" s="183"/>
-      <c r="Z15" s="183"/>
-      <c r="AA15" s="183"/>
-      <c r="AB15" s="183"/>
-      <c r="AC15" s="183"/>
-      <c r="AD15" s="183"/>
-      <c r="AE15" s="184"/>
-      <c r="AF15" s="179"/>
-      <c r="AG15" s="180"/>
-      <c r="AH15" s="180"/>
-      <c r="AI15" s="181"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="131"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="131"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="134"/>
+      <c r="U15" s="134"/>
+      <c r="V15" s="134"/>
+      <c r="W15" s="134"/>
+      <c r="X15" s="134"/>
+      <c r="Y15" s="134"/>
+      <c r="Z15" s="134"/>
+      <c r="AA15" s="134"/>
+      <c r="AB15" s="134"/>
+      <c r="AC15" s="134"/>
+      <c r="AD15" s="134"/>
+      <c r="AE15" s="135"/>
+      <c r="AF15" s="130"/>
+      <c r="AG15" s="131"/>
+      <c r="AH15" s="131"/>
+      <c r="AI15" s="132"/>
     </row>
     <row r="16" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="14"/>
-      <c r="B16" s="173"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="175"/>
-      <c r="E16" s="176"/>
-      <c r="F16" s="177"/>
-      <c r="G16" s="173"/>
-      <c r="H16" s="178"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="179"/>
-      <c r="K16" s="180"/>
-      <c r="L16" s="180"/>
-      <c r="M16" s="180"/>
-      <c r="N16" s="180"/>
-      <c r="O16" s="180"/>
-      <c r="P16" s="181"/>
-      <c r="Q16" s="182"/>
-      <c r="R16" s="183"/>
-      <c r="S16" s="183"/>
-      <c r="T16" s="183"/>
-      <c r="U16" s="183"/>
-      <c r="V16" s="183"/>
-      <c r="W16" s="183"/>
-      <c r="X16" s="183"/>
-      <c r="Y16" s="183"/>
-      <c r="Z16" s="183"/>
-      <c r="AA16" s="183"/>
-      <c r="AB16" s="183"/>
-      <c r="AC16" s="183"/>
-      <c r="AD16" s="183"/>
-      <c r="AE16" s="184"/>
-      <c r="AF16" s="179"/>
-      <c r="AG16" s="180"/>
-      <c r="AH16" s="180"/>
-      <c r="AI16" s="181"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="131"/>
+      <c r="M16" s="131"/>
+      <c r="N16" s="131"/>
+      <c r="O16" s="131"/>
+      <c r="P16" s="132"/>
+      <c r="Q16" s="133"/>
+      <c r="R16" s="134"/>
+      <c r="S16" s="134"/>
+      <c r="T16" s="134"/>
+      <c r="U16" s="134"/>
+      <c r="V16" s="134"/>
+      <c r="W16" s="134"/>
+      <c r="X16" s="134"/>
+      <c r="Y16" s="134"/>
+      <c r="Z16" s="134"/>
+      <c r="AA16" s="134"/>
+      <c r="AB16" s="134"/>
+      <c r="AC16" s="134"/>
+      <c r="AD16" s="134"/>
+      <c r="AE16" s="135"/>
+      <c r="AF16" s="130"/>
+      <c r="AG16" s="131"/>
+      <c r="AH16" s="131"/>
+      <c r="AI16" s="132"/>
     </row>
     <row r="17" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="14"/>
-      <c r="B17" s="173"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="176"/>
-      <c r="F17" s="177"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="178"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="179"/>
-      <c r="K17" s="180"/>
-      <c r="L17" s="180"/>
-      <c r="M17" s="180"/>
-      <c r="N17" s="180"/>
-      <c r="O17" s="180"/>
-      <c r="P17" s="181"/>
-      <c r="Q17" s="182"/>
-      <c r="R17" s="183"/>
-      <c r="S17" s="183"/>
-      <c r="T17" s="183"/>
-      <c r="U17" s="183"/>
-      <c r="V17" s="183"/>
-      <c r="W17" s="183"/>
-      <c r="X17" s="183"/>
-      <c r="Y17" s="183"/>
-      <c r="Z17" s="183"/>
-      <c r="AA17" s="183"/>
-      <c r="AB17" s="183"/>
-      <c r="AC17" s="183"/>
-      <c r="AD17" s="183"/>
-      <c r="AE17" s="184"/>
-      <c r="AF17" s="179"/>
-      <c r="AG17" s="180"/>
-      <c r="AH17" s="180"/>
-      <c r="AI17" s="181"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="131"/>
+      <c r="L17" s="131"/>
+      <c r="M17" s="131"/>
+      <c r="N17" s="131"/>
+      <c r="O17" s="131"/>
+      <c r="P17" s="132"/>
+      <c r="Q17" s="133"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="134"/>
+      <c r="W17" s="134"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="134"/>
+      <c r="AE17" s="135"/>
+      <c r="AF17" s="130"/>
+      <c r="AG17" s="131"/>
+      <c r="AH17" s="131"/>
+      <c r="AI17" s="132"/>
     </row>
     <row r="18" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="14"/>
-      <c r="B18" s="173"/>
-      <c r="C18" s="174"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="177"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="178"/>
-      <c r="I18" s="174"/>
-      <c r="J18" s="179"/>
-      <c r="K18" s="180"/>
-      <c r="L18" s="180"/>
-      <c r="M18" s="180"/>
-      <c r="N18" s="180"/>
-      <c r="O18" s="180"/>
-      <c r="P18" s="181"/>
-      <c r="Q18" s="182"/>
-      <c r="R18" s="183"/>
-      <c r="S18" s="183"/>
-      <c r="T18" s="183"/>
-      <c r="U18" s="183"/>
-      <c r="V18" s="183"/>
-      <c r="W18" s="183"/>
-      <c r="X18" s="183"/>
-      <c r="Y18" s="183"/>
-      <c r="Z18" s="183"/>
-      <c r="AA18" s="183"/>
-      <c r="AB18" s="183"/>
-      <c r="AC18" s="183"/>
-      <c r="AD18" s="183"/>
-      <c r="AE18" s="184"/>
-      <c r="AF18" s="179"/>
-      <c r="AG18" s="180"/>
-      <c r="AH18" s="180"/>
-      <c r="AI18" s="181"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="131"/>
+      <c r="L18" s="131"/>
+      <c r="M18" s="131"/>
+      <c r="N18" s="131"/>
+      <c r="O18" s="131"/>
+      <c r="P18" s="132"/>
+      <c r="Q18" s="133"/>
+      <c r="R18" s="134"/>
+      <c r="S18" s="134"/>
+      <c r="T18" s="134"/>
+      <c r="U18" s="134"/>
+      <c r="V18" s="134"/>
+      <c r="W18" s="134"/>
+      <c r="X18" s="134"/>
+      <c r="Y18" s="134"/>
+      <c r="Z18" s="134"/>
+      <c r="AA18" s="134"/>
+      <c r="AB18" s="134"/>
+      <c r="AC18" s="134"/>
+      <c r="AD18" s="134"/>
+      <c r="AE18" s="135"/>
+      <c r="AF18" s="130"/>
+      <c r="AG18" s="131"/>
+      <c r="AH18" s="131"/>
+      <c r="AI18" s="132"/>
     </row>
     <row r="19" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="14"/>
-      <c r="B19" s="173"/>
-      <c r="C19" s="174"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="177"/>
-      <c r="G19" s="173"/>
-      <c r="H19" s="178"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="179"/>
-      <c r="K19" s="180"/>
-      <c r="L19" s="180"/>
-      <c r="M19" s="180"/>
-      <c r="N19" s="180"/>
-      <c r="O19" s="180"/>
-      <c r="P19" s="181"/>
-      <c r="Q19" s="182"/>
-      <c r="R19" s="183"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="183"/>
-      <c r="U19" s="183"/>
-      <c r="V19" s="183"/>
-      <c r="W19" s="183"/>
-      <c r="X19" s="183"/>
-      <c r="Y19" s="183"/>
-      <c r="Z19" s="183"/>
-      <c r="AA19" s="183"/>
-      <c r="AB19" s="183"/>
-      <c r="AC19" s="183"/>
-      <c r="AD19" s="183"/>
-      <c r="AE19" s="184"/>
-      <c r="AF19" s="179"/>
-      <c r="AG19" s="180"/>
-      <c r="AH19" s="180"/>
-      <c r="AI19" s="181"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="129"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="130"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="131"/>
+      <c r="N19" s="131"/>
+      <c r="O19" s="131"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="133"/>
+      <c r="R19" s="134"/>
+      <c r="S19" s="134"/>
+      <c r="T19" s="134"/>
+      <c r="U19" s="134"/>
+      <c r="V19" s="134"/>
+      <c r="W19" s="134"/>
+      <c r="X19" s="134"/>
+      <c r="Y19" s="134"/>
+      <c r="Z19" s="134"/>
+      <c r="AA19" s="134"/>
+      <c r="AB19" s="134"/>
+      <c r="AC19" s="134"/>
+      <c r="AD19" s="134"/>
+      <c r="AE19" s="135"/>
+      <c r="AF19" s="130"/>
+      <c r="AG19" s="131"/>
+      <c r="AH19" s="131"/>
+      <c r="AI19" s="132"/>
     </row>
     <row r="20" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="14"/>
-      <c r="B20" s="173"/>
-      <c r="C20" s="174"/>
-      <c r="D20" s="175"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="177"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="178"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="179"/>
-      <c r="K20" s="180"/>
-      <c r="L20" s="180"/>
-      <c r="M20" s="180"/>
-      <c r="N20" s="180"/>
-      <c r="O20" s="180"/>
-      <c r="P20" s="181"/>
-      <c r="Q20" s="182"/>
-      <c r="R20" s="183"/>
-      <c r="S20" s="183"/>
-      <c r="T20" s="183"/>
-      <c r="U20" s="183"/>
-      <c r="V20" s="183"/>
-      <c r="W20" s="183"/>
-      <c r="X20" s="183"/>
-      <c r="Y20" s="183"/>
-      <c r="Z20" s="183"/>
-      <c r="AA20" s="183"/>
-      <c r="AB20" s="183"/>
-      <c r="AC20" s="183"/>
-      <c r="AD20" s="183"/>
-      <c r="AE20" s="184"/>
-      <c r="AF20" s="179"/>
-      <c r="AG20" s="180"/>
-      <c r="AH20" s="180"/>
-      <c r="AI20" s="181"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="127"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="129"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="130"/>
+      <c r="K20" s="131"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="131"/>
+      <c r="N20" s="131"/>
+      <c r="O20" s="131"/>
+      <c r="P20" s="132"/>
+      <c r="Q20" s="133"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="134"/>
+      <c r="W20" s="134"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="134"/>
+      <c r="Z20" s="134"/>
+      <c r="AA20" s="134"/>
+      <c r="AB20" s="134"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="134"/>
+      <c r="AE20" s="135"/>
+      <c r="AF20" s="130"/>
+      <c r="AG20" s="131"/>
+      <c r="AH20" s="131"/>
+      <c r="AI20" s="132"/>
     </row>
     <row r="21" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="14"/>
-      <c r="B21" s="173"/>
-      <c r="C21" s="174"/>
-      <c r="D21" s="175"/>
-      <c r="E21" s="176"/>
-      <c r="F21" s="177"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="178"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="179"/>
-      <c r="K21" s="180"/>
-      <c r="L21" s="180"/>
-      <c r="M21" s="180"/>
-      <c r="N21" s="180"/>
-      <c r="O21" s="180"/>
-      <c r="P21" s="181"/>
-      <c r="Q21" s="182"/>
-      <c r="R21" s="183"/>
-      <c r="S21" s="183"/>
-      <c r="T21" s="183"/>
-      <c r="U21" s="183"/>
-      <c r="V21" s="183"/>
-      <c r="W21" s="183"/>
-      <c r="X21" s="183"/>
-      <c r="Y21" s="183"/>
-      <c r="Z21" s="183"/>
-      <c r="AA21" s="183"/>
-      <c r="AB21" s="183"/>
-      <c r="AC21" s="183"/>
-      <c r="AD21" s="183"/>
-      <c r="AE21" s="184"/>
-      <c r="AF21" s="179"/>
-      <c r="AG21" s="180"/>
-      <c r="AH21" s="180"/>
-      <c r="AI21" s="181"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="130"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="134"/>
+      <c r="S21" s="134"/>
+      <c r="T21" s="134"/>
+      <c r="U21" s="134"/>
+      <c r="V21" s="134"/>
+      <c r="W21" s="134"/>
+      <c r="X21" s="134"/>
+      <c r="Y21" s="134"/>
+      <c r="Z21" s="134"/>
+      <c r="AA21" s="134"/>
+      <c r="AB21" s="134"/>
+      <c r="AC21" s="134"/>
+      <c r="AD21" s="134"/>
+      <c r="AE21" s="135"/>
+      <c r="AF21" s="130"/>
+      <c r="AG21" s="131"/>
+      <c r="AH21" s="131"/>
+      <c r="AI21" s="132"/>
     </row>
     <row r="22" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="14"/>
-      <c r="B22" s="173"/>
-      <c r="C22" s="174"/>
-      <c r="D22" s="175"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="178"/>
-      <c r="I22" s="174"/>
-      <c r="J22" s="179"/>
-      <c r="K22" s="180"/>
-      <c r="L22" s="180"/>
-      <c r="M22" s="180"/>
-      <c r="N22" s="180"/>
-      <c r="O22" s="180"/>
-      <c r="P22" s="181"/>
-      <c r="Q22" s="182"/>
-      <c r="R22" s="183"/>
-      <c r="S22" s="183"/>
-      <c r="T22" s="183"/>
-      <c r="U22" s="183"/>
-      <c r="V22" s="183"/>
-      <c r="W22" s="183"/>
-      <c r="X22" s="183"/>
-      <c r="Y22" s="183"/>
-      <c r="Z22" s="183"/>
-      <c r="AA22" s="183"/>
-      <c r="AB22" s="183"/>
-      <c r="AC22" s="183"/>
-      <c r="AD22" s="183"/>
-      <c r="AE22" s="184"/>
-      <c r="AF22" s="179"/>
-      <c r="AG22" s="180"/>
-      <c r="AH22" s="180"/>
-      <c r="AI22" s="181"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="125"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="129"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
+      <c r="M22" s="131"/>
+      <c r="N22" s="131"/>
+      <c r="O22" s="131"/>
+      <c r="P22" s="132"/>
+      <c r="Q22" s="133"/>
+      <c r="R22" s="134"/>
+      <c r="S22" s="134"/>
+      <c r="T22" s="134"/>
+      <c r="U22" s="134"/>
+      <c r="V22" s="134"/>
+      <c r="W22" s="134"/>
+      <c r="X22" s="134"/>
+      <c r="Y22" s="134"/>
+      <c r="Z22" s="134"/>
+      <c r="AA22" s="134"/>
+      <c r="AB22" s="134"/>
+      <c r="AC22" s="134"/>
+      <c r="AD22" s="134"/>
+      <c r="AE22" s="135"/>
+      <c r="AF22" s="130"/>
+      <c r="AG22" s="131"/>
+      <c r="AH22" s="131"/>
+      <c r="AI22" s="132"/>
     </row>
     <row r="23" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="14"/>
-      <c r="B23" s="173"/>
-      <c r="C23" s="174"/>
-      <c r="D23" s="175"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="177"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="178"/>
-      <c r="I23" s="174"/>
-      <c r="J23" s="179"/>
-      <c r="K23" s="180"/>
-      <c r="L23" s="180"/>
-      <c r="M23" s="180"/>
-      <c r="N23" s="180"/>
-      <c r="O23" s="180"/>
-      <c r="P23" s="181"/>
-      <c r="Q23" s="182"/>
-      <c r="R23" s="183"/>
-      <c r="S23" s="183"/>
-      <c r="T23" s="183"/>
-      <c r="U23" s="183"/>
-      <c r="V23" s="183"/>
-      <c r="W23" s="183"/>
-      <c r="X23" s="183"/>
-      <c r="Y23" s="183"/>
-      <c r="Z23" s="183"/>
-      <c r="AA23" s="183"/>
-      <c r="AB23" s="183"/>
-      <c r="AC23" s="183"/>
-      <c r="AD23" s="183"/>
-      <c r="AE23" s="184"/>
-      <c r="AF23" s="179"/>
-      <c r="AG23" s="180"/>
-      <c r="AH23" s="180"/>
-      <c r="AI23" s="181"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
+      <c r="M23" s="131"/>
+      <c r="N23" s="131"/>
+      <c r="O23" s="131"/>
+      <c r="P23" s="132"/>
+      <c r="Q23" s="133"/>
+      <c r="R23" s="134"/>
+      <c r="S23" s="134"/>
+      <c r="T23" s="134"/>
+      <c r="U23" s="134"/>
+      <c r="V23" s="134"/>
+      <c r="W23" s="134"/>
+      <c r="X23" s="134"/>
+      <c r="Y23" s="134"/>
+      <c r="Z23" s="134"/>
+      <c r="AA23" s="134"/>
+      <c r="AB23" s="134"/>
+      <c r="AC23" s="134"/>
+      <c r="AD23" s="134"/>
+      <c r="AE23" s="135"/>
+      <c r="AF23" s="130"/>
+      <c r="AG23" s="131"/>
+      <c r="AH23" s="131"/>
+      <c r="AI23" s="132"/>
     </row>
     <row r="24" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="14"/>
-      <c r="B24" s="173"/>
-      <c r="C24" s="174"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="177"/>
-      <c r="G24" s="173"/>
-      <c r="H24" s="178"/>
-      <c r="I24" s="174"/>
-      <c r="J24" s="179"/>
-      <c r="K24" s="180"/>
-      <c r="L24" s="180"/>
-      <c r="M24" s="180"/>
-      <c r="N24" s="180"/>
-      <c r="O24" s="180"/>
-      <c r="P24" s="181"/>
-      <c r="Q24" s="182"/>
-      <c r="R24" s="183"/>
-      <c r="S24" s="183"/>
-      <c r="T24" s="183"/>
-      <c r="U24" s="183"/>
-      <c r="V24" s="183"/>
-      <c r="W24" s="183"/>
-      <c r="X24" s="183"/>
-      <c r="Y24" s="183"/>
-      <c r="Z24" s="183"/>
-      <c r="AA24" s="183"/>
-      <c r="AB24" s="183"/>
-      <c r="AC24" s="183"/>
-      <c r="AD24" s="183"/>
-      <c r="AE24" s="184"/>
-      <c r="AF24" s="179"/>
-      <c r="AG24" s="180"/>
-      <c r="AH24" s="180"/>
-      <c r="AI24" s="181"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="126"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="130"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="133"/>
+      <c r="R24" s="134"/>
+      <c r="S24" s="134"/>
+      <c r="T24" s="134"/>
+      <c r="U24" s="134"/>
+      <c r="V24" s="134"/>
+      <c r="W24" s="134"/>
+      <c r="X24" s="134"/>
+      <c r="Y24" s="134"/>
+      <c r="Z24" s="134"/>
+      <c r="AA24" s="134"/>
+      <c r="AB24" s="134"/>
+      <c r="AC24" s="134"/>
+      <c r="AD24" s="134"/>
+      <c r="AE24" s="135"/>
+      <c r="AF24" s="130"/>
+      <c r="AG24" s="131"/>
+      <c r="AH24" s="131"/>
+      <c r="AI24" s="132"/>
     </row>
     <row r="25" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="14"/>
-      <c r="B25" s="173"/>
-      <c r="C25" s="174"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="176"/>
-      <c r="F25" s="177"/>
-      <c r="G25" s="173"/>
-      <c r="H25" s="178"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="179"/>
-      <c r="K25" s="180"/>
-      <c r="L25" s="180"/>
-      <c r="M25" s="180"/>
-      <c r="N25" s="180"/>
-      <c r="O25" s="180"/>
-      <c r="P25" s="181"/>
-      <c r="Q25" s="182"/>
-      <c r="R25" s="183"/>
-      <c r="S25" s="183"/>
-      <c r="T25" s="183"/>
-      <c r="U25" s="183"/>
-      <c r="V25" s="183"/>
-      <c r="W25" s="183"/>
-      <c r="X25" s="183"/>
-      <c r="Y25" s="183"/>
-      <c r="Z25" s="183"/>
-      <c r="AA25" s="183"/>
-      <c r="AB25" s="183"/>
-      <c r="AC25" s="183"/>
-      <c r="AD25" s="183"/>
-      <c r="AE25" s="184"/>
-      <c r="AF25" s="179"/>
-      <c r="AG25" s="180"/>
-      <c r="AH25" s="180"/>
-      <c r="AI25" s="181"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="129"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="130"/>
+      <c r="K25" s="131"/>
+      <c r="L25" s="131"/>
+      <c r="M25" s="131"/>
+      <c r="N25" s="131"/>
+      <c r="O25" s="131"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="133"/>
+      <c r="R25" s="134"/>
+      <c r="S25" s="134"/>
+      <c r="T25" s="134"/>
+      <c r="U25" s="134"/>
+      <c r="V25" s="134"/>
+      <c r="W25" s="134"/>
+      <c r="X25" s="134"/>
+      <c r="Y25" s="134"/>
+      <c r="Z25" s="134"/>
+      <c r="AA25" s="134"/>
+      <c r="AB25" s="134"/>
+      <c r="AC25" s="134"/>
+      <c r="AD25" s="134"/>
+      <c r="AE25" s="135"/>
+      <c r="AF25" s="130"/>
+      <c r="AG25" s="131"/>
+      <c r="AH25" s="131"/>
+      <c r="AI25" s="132"/>
     </row>
     <row r="26" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="14"/>
-      <c r="B26" s="173"/>
-      <c r="C26" s="174"/>
-      <c r="D26" s="175"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="177"/>
-      <c r="G26" s="173"/>
-      <c r="H26" s="178"/>
-      <c r="I26" s="174"/>
-      <c r="J26" s="179"/>
-      <c r="K26" s="180"/>
-      <c r="L26" s="180"/>
-      <c r="M26" s="180"/>
-      <c r="N26" s="180"/>
-      <c r="O26" s="180"/>
-      <c r="P26" s="181"/>
-      <c r="Q26" s="182"/>
-      <c r="R26" s="183"/>
-      <c r="S26" s="183"/>
-      <c r="T26" s="183"/>
-      <c r="U26" s="183"/>
-      <c r="V26" s="183"/>
-      <c r="W26" s="183"/>
-      <c r="X26" s="183"/>
-      <c r="Y26" s="183"/>
-      <c r="Z26" s="183"/>
-      <c r="AA26" s="183"/>
-      <c r="AB26" s="183"/>
-      <c r="AC26" s="183"/>
-      <c r="AD26" s="183"/>
-      <c r="AE26" s="184"/>
-      <c r="AF26" s="179"/>
-      <c r="AG26" s="180"/>
-      <c r="AH26" s="180"/>
-      <c r="AI26" s="181"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="126"/>
+      <c r="E26" s="127"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="129"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="131"/>
+      <c r="L26" s="131"/>
+      <c r="M26" s="131"/>
+      <c r="N26" s="131"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="132"/>
+      <c r="Q26" s="133"/>
+      <c r="R26" s="134"/>
+      <c r="S26" s="134"/>
+      <c r="T26" s="134"/>
+      <c r="U26" s="134"/>
+      <c r="V26" s="134"/>
+      <c r="W26" s="134"/>
+      <c r="X26" s="134"/>
+      <c r="Y26" s="134"/>
+      <c r="Z26" s="134"/>
+      <c r="AA26" s="134"/>
+      <c r="AB26" s="134"/>
+      <c r="AC26" s="134"/>
+      <c r="AD26" s="134"/>
+      <c r="AE26" s="135"/>
+      <c r="AF26" s="130"/>
+      <c r="AG26" s="131"/>
+      <c r="AH26" s="131"/>
+      <c r="AI26" s="132"/>
     </row>
     <row r="27" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="14"/>
-      <c r="B27" s="173"/>
-      <c r="C27" s="174"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="176"/>
-      <c r="F27" s="177"/>
-      <c r="G27" s="173"/>
-      <c r="H27" s="178"/>
-      <c r="I27" s="174"/>
-      <c r="J27" s="179"/>
-      <c r="K27" s="180"/>
-      <c r="L27" s="180"/>
-      <c r="M27" s="180"/>
-      <c r="N27" s="180"/>
-      <c r="O27" s="180"/>
-      <c r="P27" s="181"/>
-      <c r="Q27" s="182"/>
-      <c r="R27" s="183"/>
-      <c r="S27" s="183"/>
-      <c r="T27" s="183"/>
-      <c r="U27" s="183"/>
-      <c r="V27" s="183"/>
-      <c r="W27" s="183"/>
-      <c r="X27" s="183"/>
-      <c r="Y27" s="183"/>
-      <c r="Z27" s="183"/>
-      <c r="AA27" s="183"/>
-      <c r="AB27" s="183"/>
-      <c r="AC27" s="183"/>
-      <c r="AD27" s="183"/>
-      <c r="AE27" s="184"/>
-      <c r="AF27" s="179"/>
-      <c r="AG27" s="180"/>
-      <c r="AH27" s="180"/>
-      <c r="AI27" s="181"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="127"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="129"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="130"/>
+      <c r="K27" s="131"/>
+      <c r="L27" s="131"/>
+      <c r="M27" s="131"/>
+      <c r="N27" s="131"/>
+      <c r="O27" s="131"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="133"/>
+      <c r="R27" s="134"/>
+      <c r="S27" s="134"/>
+      <c r="T27" s="134"/>
+      <c r="U27" s="134"/>
+      <c r="V27" s="134"/>
+      <c r="W27" s="134"/>
+      <c r="X27" s="134"/>
+      <c r="Y27" s="134"/>
+      <c r="Z27" s="134"/>
+      <c r="AA27" s="134"/>
+      <c r="AB27" s="134"/>
+      <c r="AC27" s="134"/>
+      <c r="AD27" s="134"/>
+      <c r="AE27" s="135"/>
+      <c r="AF27" s="130"/>
+      <c r="AG27" s="131"/>
+      <c r="AH27" s="131"/>
+      <c r="AI27" s="132"/>
     </row>
     <row r="28" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="14"/>
-      <c r="B28" s="173"/>
-      <c r="C28" s="174"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="177"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="178"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="179"/>
-      <c r="K28" s="180"/>
-      <c r="L28" s="180"/>
-      <c r="M28" s="180"/>
-      <c r="N28" s="180"/>
-      <c r="O28" s="180"/>
-      <c r="P28" s="181"/>
-      <c r="Q28" s="182"/>
-      <c r="R28" s="183"/>
-      <c r="S28" s="183"/>
-      <c r="T28" s="183"/>
-      <c r="U28" s="183"/>
-      <c r="V28" s="183"/>
-      <c r="W28" s="183"/>
-      <c r="X28" s="183"/>
-      <c r="Y28" s="183"/>
-      <c r="Z28" s="183"/>
-      <c r="AA28" s="183"/>
-      <c r="AB28" s="183"/>
-      <c r="AC28" s="183"/>
-      <c r="AD28" s="183"/>
-      <c r="AE28" s="184"/>
-      <c r="AF28" s="179"/>
-      <c r="AG28" s="180"/>
-      <c r="AH28" s="180"/>
-      <c r="AI28" s="181"/>
+      <c r="B28" s="124"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="126"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="129"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="131"/>
+      <c r="N28" s="131"/>
+      <c r="O28" s="131"/>
+      <c r="P28" s="132"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="134"/>
+      <c r="S28" s="134"/>
+      <c r="T28" s="134"/>
+      <c r="U28" s="134"/>
+      <c r="V28" s="134"/>
+      <c r="W28" s="134"/>
+      <c r="X28" s="134"/>
+      <c r="Y28" s="134"/>
+      <c r="Z28" s="134"/>
+      <c r="AA28" s="134"/>
+      <c r="AB28" s="134"/>
+      <c r="AC28" s="134"/>
+      <c r="AD28" s="134"/>
+      <c r="AE28" s="135"/>
+      <c r="AF28" s="130"/>
+      <c r="AG28" s="131"/>
+      <c r="AH28" s="131"/>
+      <c r="AI28" s="132"/>
     </row>
     <row r="29" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="14"/>
-      <c r="B29" s="173"/>
-      <c r="C29" s="174"/>
-      <c r="D29" s="175"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="177"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="179"/>
-      <c r="K29" s="180"/>
-      <c r="L29" s="180"/>
-      <c r="M29" s="180"/>
-      <c r="N29" s="180"/>
-      <c r="O29" s="180"/>
-      <c r="P29" s="181"/>
-      <c r="Q29" s="182"/>
-      <c r="R29" s="183"/>
-      <c r="S29" s="183"/>
-      <c r="T29" s="183"/>
-      <c r="U29" s="183"/>
-      <c r="V29" s="183"/>
-      <c r="W29" s="183"/>
-      <c r="X29" s="183"/>
-      <c r="Y29" s="183"/>
-      <c r="Z29" s="183"/>
-      <c r="AA29" s="183"/>
-      <c r="AB29" s="183"/>
-      <c r="AC29" s="183"/>
-      <c r="AD29" s="183"/>
-      <c r="AE29" s="184"/>
-      <c r="AF29" s="179"/>
-      <c r="AG29" s="180"/>
-      <c r="AH29" s="180"/>
-      <c r="AI29" s="181"/>
+      <c r="B29" s="124"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="126"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="124"/>
+      <c r="H29" s="129"/>
+      <c r="I29" s="125"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="131"/>
+      <c r="L29" s="131"/>
+      <c r="M29" s="131"/>
+      <c r="N29" s="131"/>
+      <c r="O29" s="131"/>
+      <c r="P29" s="132"/>
+      <c r="Q29" s="133"/>
+      <c r="R29" s="134"/>
+      <c r="S29" s="134"/>
+      <c r="T29" s="134"/>
+      <c r="U29" s="134"/>
+      <c r="V29" s="134"/>
+      <c r="W29" s="134"/>
+      <c r="X29" s="134"/>
+      <c r="Y29" s="134"/>
+      <c r="Z29" s="134"/>
+      <c r="AA29" s="134"/>
+      <c r="AB29" s="134"/>
+      <c r="AC29" s="134"/>
+      <c r="AD29" s="134"/>
+      <c r="AE29" s="135"/>
+      <c r="AF29" s="130"/>
+      <c r="AG29" s="131"/>
+      <c r="AH29" s="131"/>
+      <c r="AI29" s="132"/>
     </row>
     <row r="30" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="14"/>
-      <c r="B30" s="173"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="177"/>
-      <c r="G30" s="173"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="180"/>
-      <c r="L30" s="180"/>
-      <c r="M30" s="180"/>
-      <c r="N30" s="180"/>
-      <c r="O30" s="180"/>
-      <c r="P30" s="181"/>
-      <c r="Q30" s="182"/>
-      <c r="R30" s="183"/>
-      <c r="S30" s="183"/>
-      <c r="T30" s="183"/>
-      <c r="U30" s="183"/>
-      <c r="V30" s="183"/>
-      <c r="W30" s="183"/>
-      <c r="X30" s="183"/>
-      <c r="Y30" s="183"/>
-      <c r="Z30" s="183"/>
-      <c r="AA30" s="183"/>
-      <c r="AB30" s="183"/>
-      <c r="AC30" s="183"/>
-      <c r="AD30" s="183"/>
-      <c r="AE30" s="184"/>
-      <c r="AF30" s="179"/>
-      <c r="AG30" s="180"/>
-      <c r="AH30" s="180"/>
-      <c r="AI30" s="181"/>
+      <c r="B30" s="124"/>
+      <c r="C30" s="125"/>
+      <c r="D30" s="126"/>
+      <c r="E30" s="127"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="124"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="125"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="131"/>
+      <c r="N30" s="131"/>
+      <c r="O30" s="131"/>
+      <c r="P30" s="132"/>
+      <c r="Q30" s="133"/>
+      <c r="R30" s="134"/>
+      <c r="S30" s="134"/>
+      <c r="T30" s="134"/>
+      <c r="U30" s="134"/>
+      <c r="V30" s="134"/>
+      <c r="W30" s="134"/>
+      <c r="X30" s="134"/>
+      <c r="Y30" s="134"/>
+      <c r="Z30" s="134"/>
+      <c r="AA30" s="134"/>
+      <c r="AB30" s="134"/>
+      <c r="AC30" s="134"/>
+      <c r="AD30" s="134"/>
+      <c r="AE30" s="135"/>
+      <c r="AF30" s="130"/>
+      <c r="AG30" s="131"/>
+      <c r="AH30" s="131"/>
+      <c r="AI30" s="132"/>
     </row>
     <row r="31" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="14"/>
-      <c r="B31" s="173"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="177"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="180"/>
-      <c r="L31" s="180"/>
-      <c r="M31" s="180"/>
-      <c r="N31" s="180"/>
-      <c r="O31" s="180"/>
-      <c r="P31" s="181"/>
-      <c r="Q31" s="182"/>
-      <c r="R31" s="183"/>
-      <c r="S31" s="183"/>
-      <c r="T31" s="183"/>
-      <c r="U31" s="183"/>
-      <c r="V31" s="183"/>
-      <c r="W31" s="183"/>
-      <c r="X31" s="183"/>
-      <c r="Y31" s="183"/>
-      <c r="Z31" s="183"/>
-      <c r="AA31" s="183"/>
-      <c r="AB31" s="183"/>
-      <c r="AC31" s="183"/>
-      <c r="AD31" s="183"/>
-      <c r="AE31" s="184"/>
-      <c r="AF31" s="179"/>
-      <c r="AG31" s="180"/>
-      <c r="AH31" s="180"/>
-      <c r="AI31" s="181"/>
+      <c r="B31" s="124"/>
+      <c r="C31" s="125"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="127"/>
+      <c r="F31" s="128"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="129"/>
+      <c r="I31" s="125"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="131"/>
+      <c r="L31" s="131"/>
+      <c r="M31" s="131"/>
+      <c r="N31" s="131"/>
+      <c r="O31" s="131"/>
+      <c r="P31" s="132"/>
+      <c r="Q31" s="133"/>
+      <c r="R31" s="134"/>
+      <c r="S31" s="134"/>
+      <c r="T31" s="134"/>
+      <c r="U31" s="134"/>
+      <c r="V31" s="134"/>
+      <c r="W31" s="134"/>
+      <c r="X31" s="134"/>
+      <c r="Y31" s="134"/>
+      <c r="Z31" s="134"/>
+      <c r="AA31" s="134"/>
+      <c r="AB31" s="134"/>
+      <c r="AC31" s="134"/>
+      <c r="AD31" s="134"/>
+      <c r="AE31" s="135"/>
+      <c r="AF31" s="130"/>
+      <c r="AG31" s="131"/>
+      <c r="AH31" s="131"/>
+      <c r="AI31" s="132"/>
     </row>
     <row r="32" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="14"/>
-      <c r="B32" s="173"/>
-      <c r="C32" s="174"/>
-      <c r="D32" s="175"/>
-      <c r="E32" s="176"/>
-      <c r="F32" s="177"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="178"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="179"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="180"/>
-      <c r="M32" s="180"/>
-      <c r="N32" s="180"/>
-      <c r="O32" s="180"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="182"/>
-      <c r="R32" s="183"/>
-      <c r="S32" s="183"/>
-      <c r="T32" s="183"/>
-      <c r="U32" s="183"/>
-      <c r="V32" s="183"/>
-      <c r="W32" s="183"/>
-      <c r="X32" s="183"/>
-      <c r="Y32" s="183"/>
-      <c r="Z32" s="183"/>
-      <c r="AA32" s="183"/>
-      <c r="AB32" s="183"/>
-      <c r="AC32" s="183"/>
-      <c r="AD32" s="183"/>
-      <c r="AE32" s="184"/>
-      <c r="AF32" s="179"/>
-      <c r="AG32" s="180"/>
-      <c r="AH32" s="180"/>
-      <c r="AI32" s="181"/>
+      <c r="B32" s="124"/>
+      <c r="C32" s="125"/>
+      <c r="D32" s="126"/>
+      <c r="E32" s="127"/>
+      <c r="F32" s="128"/>
+      <c r="G32" s="124"/>
+      <c r="H32" s="129"/>
+      <c r="I32" s="125"/>
+      <c r="J32" s="130"/>
+      <c r="K32" s="136"/>
+      <c r="L32" s="131"/>
+      <c r="M32" s="131"/>
+      <c r="N32" s="131"/>
+      <c r="O32" s="131"/>
+      <c r="P32" s="132"/>
+      <c r="Q32" s="133"/>
+      <c r="R32" s="134"/>
+      <c r="S32" s="134"/>
+      <c r="T32" s="134"/>
+      <c r="U32" s="134"/>
+      <c r="V32" s="134"/>
+      <c r="W32" s="134"/>
+      <c r="X32" s="134"/>
+      <c r="Y32" s="134"/>
+      <c r="Z32" s="134"/>
+      <c r="AA32" s="134"/>
+      <c r="AB32" s="134"/>
+      <c r="AC32" s="134"/>
+      <c r="AD32" s="134"/>
+      <c r="AE32" s="135"/>
+      <c r="AF32" s="130"/>
+      <c r="AG32" s="131"/>
+      <c r="AH32" s="131"/>
+      <c r="AI32" s="132"/>
     </row>
     <row r="33" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="14"/>
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="177"/>
-      <c r="G33" s="173"/>
-      <c r="H33" s="178"/>
-      <c r="I33" s="174"/>
-      <c r="J33" s="179"/>
-      <c r="K33" s="180"/>
-      <c r="L33" s="180"/>
-      <c r="M33" s="180"/>
-      <c r="N33" s="180"/>
-      <c r="O33" s="180"/>
-      <c r="P33" s="181"/>
-      <c r="Q33" s="182"/>
-      <c r="R33" s="183"/>
-      <c r="S33" s="183"/>
-      <c r="T33" s="183"/>
-      <c r="U33" s="183"/>
-      <c r="V33" s="183"/>
-      <c r="W33" s="183"/>
-      <c r="X33" s="183"/>
-      <c r="Y33" s="183"/>
-      <c r="Z33" s="183"/>
-      <c r="AA33" s="183"/>
-      <c r="AB33" s="183"/>
-      <c r="AC33" s="183"/>
-      <c r="AD33" s="183"/>
-      <c r="AE33" s="184"/>
-      <c r="AF33" s="179"/>
-      <c r="AG33" s="180"/>
-      <c r="AH33" s="180"/>
-      <c r="AI33" s="181"/>
+      <c r="B33" s="124"/>
+      <c r="C33" s="125"/>
+      <c r="D33" s="126"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="128"/>
+      <c r="G33" s="124"/>
+      <c r="H33" s="129"/>
+      <c r="I33" s="125"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="131"/>
+      <c r="L33" s="131"/>
+      <c r="M33" s="131"/>
+      <c r="N33" s="131"/>
+      <c r="O33" s="131"/>
+      <c r="P33" s="132"/>
+      <c r="Q33" s="133"/>
+      <c r="R33" s="134"/>
+      <c r="S33" s="134"/>
+      <c r="T33" s="134"/>
+      <c r="U33" s="134"/>
+      <c r="V33" s="134"/>
+      <c r="W33" s="134"/>
+      <c r="X33" s="134"/>
+      <c r="Y33" s="134"/>
+      <c r="Z33" s="134"/>
+      <c r="AA33" s="134"/>
+      <c r="AB33" s="134"/>
+      <c r="AC33" s="134"/>
+      <c r="AD33" s="134"/>
+      <c r="AE33" s="135"/>
+      <c r="AF33" s="130"/>
+      <c r="AG33" s="131"/>
+      <c r="AH33" s="131"/>
+      <c r="AI33" s="132"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:N2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="Q7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="G33:I33"/>
@@ -10109,167 +10274,6 @@
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="Q32:AE32"/>
     <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:N2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="S1:Z3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -20264,7 +20268,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="25" t="s">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="O7" s="25" t="s">
         <v>23</v>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77983908-8A7F-43B9-98BB-2CABC852A0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A09B8BB-D8F2-4B7A-9733-9F7EA8D59506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="【テストターゲット名】_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="【テストターゲット名】_リクエスト単体" sheetId="24" r:id="rId4"/>
     <sheet name="取引単体" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【テストターゲット名】_リクエスト単体!$A$10:$R$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$295</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$314</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【テストターゲット名】_リクエスト単体!$A$1:$R$314</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【テストターゲット名】_リクエスト単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="454">
   <si>
     <t>テストデータシート名</t>
     <rPh sb="9" eb="10">
@@ -6281,10 +6281,6 @@
   </si>
   <si>
     <t>単体テスト仕様書(メッセージ)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>リクエストID：</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7232,6 +7228,93 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -7330,93 +7413,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8871,55 +8867,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="137" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="146" t="s">
+      <c r="P1" s="167"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="168"/>
+      <c r="S1" s="175" t="s">
         <v>453</v>
       </c>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
-      <c r="V1" s="147"/>
-      <c r="W1" s="147"/>
-      <c r="X1" s="147"/>
-      <c r="Y1" s="147"/>
-      <c r="Z1" s="148"/>
-      <c r="AA1" s="122" t="s">
+      <c r="T1" s="176"/>
+      <c r="U1" s="176"/>
+      <c r="V1" s="176"/>
+      <c r="W1" s="176"/>
+      <c r="X1" s="176"/>
+      <c r="Y1" s="176"/>
+      <c r="Z1" s="177"/>
+      <c r="AA1" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="123"/>
-      <c r="AC1" s="124" t="str">
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="153" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="126"/>
-      <c r="AG1" s="131" t="str">
+      <c r="AD1" s="154"/>
+      <c r="AE1" s="154"/>
+      <c r="AF1" s="155"/>
+      <c r="AG1" s="160" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="132"/>
-      <c r="AI1" s="133"/>
+      <c r="AH1" s="161"/>
+      <c r="AI1" s="162"/>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
       <c r="AL1" s="23"/>
@@ -8927,51 +8923,51 @@
       <c r="AN1" s="24"/>
     </row>
     <row r="2" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="149"/>
-      <c r="T2" s="150"/>
-      <c r="U2" s="150"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
-      <c r="Z2" s="151"/>
-      <c r="AA2" s="122" t="s">
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="170"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="171"/>
+      <c r="S2" s="178"/>
+      <c r="T2" s="179"/>
+      <c r="U2" s="179"/>
+      <c r="V2" s="179"/>
+      <c r="W2" s="179"/>
+      <c r="X2" s="179"/>
+      <c r="Y2" s="179"/>
+      <c r="Z2" s="180"/>
+      <c r="AA2" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="AB2" s="123"/>
-      <c r="AC2" s="134" t="str">
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="163" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="135"/>
-      <c r="AF2" s="136"/>
-      <c r="AG2" s="131" t="str">
+      <c r="AD2" s="164"/>
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="165"/>
+      <c r="AG2" s="160" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="132"/>
-      <c r="AI2" s="133"/>
+      <c r="AH2" s="161"/>
+      <c r="AI2" s="162"/>
       <c r="AJ2" s="23"/>
       <c r="AK2" s="23"/>
       <c r="AL2" s="23"/>
@@ -8979,43 +8975,43 @@
       <c r="AN2" s="23"/>
     </row>
     <row r="3" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="144"/>
-      <c r="Q3" s="144"/>
-      <c r="R3" s="145"/>
-      <c r="S3" s="152"/>
-      <c r="T3" s="153"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="153"/>
-      <c r="Y3" s="153"/>
-      <c r="Z3" s="154"/>
-      <c r="AA3" s="122"/>
-      <c r="AB3" s="123"/>
-      <c r="AC3" s="124"/>
-      <c r="AD3" s="125"/>
-      <c r="AE3" s="125"/>
-      <c r="AF3" s="126"/>
-      <c r="AG3" s="131"/>
-      <c r="AH3" s="132"/>
-      <c r="AI3" s="133"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
+      <c r="O3" s="172"/>
+      <c r="P3" s="173"/>
+      <c r="Q3" s="173"/>
+      <c r="R3" s="174"/>
+      <c r="S3" s="181"/>
+      <c r="T3" s="182"/>
+      <c r="U3" s="182"/>
+      <c r="V3" s="182"/>
+      <c r="W3" s="182"/>
+      <c r="X3" s="182"/>
+      <c r="Y3" s="182"/>
+      <c r="Z3" s="183"/>
+      <c r="AA3" s="151"/>
+      <c r="AB3" s="152"/>
+      <c r="AC3" s="153"/>
+      <c r="AD3" s="154"/>
+      <c r="AE3" s="154"/>
+      <c r="AF3" s="155"/>
+      <c r="AG3" s="160"/>
+      <c r="AH3" s="161"/>
+      <c r="AI3" s="162"/>
       <c r="AJ3" s="23"/>
       <c r="AK3" s="23"/>
       <c r="AL3" s="23"/>
@@ -9052,1020 +9048,1181 @@
       <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="155" t="s">
+      <c r="C7" s="136"/>
+      <c r="D7" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="157"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="155" t="s">
+      <c r="E7" s="137"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="157"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="155" t="s">
+      <c r="H7" s="137"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="157"/>
-      <c r="L7" s="157"/>
-      <c r="M7" s="157"/>
-      <c r="N7" s="157"/>
-      <c r="O7" s="157"/>
-      <c r="P7" s="156"/>
-      <c r="Q7" s="155" t="s">
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
+      <c r="M7" s="137"/>
+      <c r="N7" s="137"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="R7" s="157"/>
-      <c r="S7" s="157"/>
-      <c r="T7" s="157"/>
-      <c r="U7" s="157"/>
-      <c r="V7" s="157"/>
-      <c r="W7" s="157"/>
-      <c r="X7" s="157"/>
-      <c r="Y7" s="157"/>
-      <c r="Z7" s="157"/>
-      <c r="AA7" s="157"/>
-      <c r="AB7" s="157"/>
-      <c r="AC7" s="157"/>
-      <c r="AD7" s="157"/>
-      <c r="AE7" s="156"/>
-      <c r="AF7" s="155" t="s">
+      <c r="R7" s="137"/>
+      <c r="S7" s="137"/>
+      <c r="T7" s="137"/>
+      <c r="U7" s="137"/>
+      <c r="V7" s="137"/>
+      <c r="W7" s="137"/>
+      <c r="X7" s="137"/>
+      <c r="Y7" s="137"/>
+      <c r="Z7" s="137"/>
+      <c r="AA7" s="137"/>
+      <c r="AB7" s="137"/>
+      <c r="AC7" s="137"/>
+      <c r="AD7" s="137"/>
+      <c r="AE7" s="136"/>
+      <c r="AF7" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="AG7" s="157"/>
-      <c r="AH7" s="157"/>
-      <c r="AI7" s="156"/>
+      <c r="AG7" s="137"/>
+      <c r="AH7" s="137"/>
+      <c r="AI7" s="136"/>
     </row>
     <row r="8" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="15"/>
-      <c r="B8" s="158"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="160"/>
-      <c r="E8" s="161"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="163"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="159"/>
-      <c r="J8" s="165"/>
-      <c r="K8" s="166"/>
-      <c r="L8" s="166"/>
-      <c r="M8" s="166"/>
-      <c r="N8" s="166"/>
-      <c r="O8" s="166"/>
-      <c r="P8" s="167"/>
-      <c r="Q8" s="168"/>
-      <c r="R8" s="169"/>
-      <c r="S8" s="169"/>
-      <c r="T8" s="169"/>
-      <c r="U8" s="169"/>
-      <c r="V8" s="169"/>
-      <c r="W8" s="169"/>
-      <c r="X8" s="169"/>
-      <c r="Y8" s="169"/>
-      <c r="Z8" s="169"/>
-      <c r="AA8" s="169"/>
-      <c r="AB8" s="169"/>
-      <c r="AC8" s="169"/>
-      <c r="AD8" s="169"/>
-      <c r="AE8" s="170"/>
-      <c r="AF8" s="165"/>
-      <c r="AG8" s="166"/>
-      <c r="AH8" s="166"/>
-      <c r="AI8" s="167"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="145"/>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
+      <c r="M8" s="146"/>
+      <c r="N8" s="146"/>
+      <c r="O8" s="146"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="148"/>
+      <c r="R8" s="149"/>
+      <c r="S8" s="149"/>
+      <c r="T8" s="149"/>
+      <c r="U8" s="149"/>
+      <c r="V8" s="149"/>
+      <c r="W8" s="149"/>
+      <c r="X8" s="149"/>
+      <c r="Y8" s="149"/>
+      <c r="Z8" s="149"/>
+      <c r="AA8" s="149"/>
+      <c r="AB8" s="149"/>
+      <c r="AC8" s="149"/>
+      <c r="AD8" s="149"/>
+      <c r="AE8" s="150"/>
+      <c r="AF8" s="145"/>
+      <c r="AG8" s="146"/>
+      <c r="AH8" s="146"/>
+      <c r="AI8" s="147"/>
     </row>
     <row r="9" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="14"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="172"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="174"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="173"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="172"/>
-      <c r="J9" s="177"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-      <c r="M9" s="178"/>
-      <c r="N9" s="178"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="179"/>
-      <c r="Q9" s="180"/>
-      <c r="R9" s="181"/>
-      <c r="S9" s="181"/>
-      <c r="T9" s="181"/>
-      <c r="U9" s="181"/>
-      <c r="V9" s="181"/>
-      <c r="W9" s="181"/>
-      <c r="X9" s="181"/>
-      <c r="Y9" s="181"/>
-      <c r="Z9" s="181"/>
-      <c r="AA9" s="181"/>
-      <c r="AB9" s="181"/>
-      <c r="AC9" s="181"/>
-      <c r="AD9" s="181"/>
-      <c r="AE9" s="182"/>
-      <c r="AF9" s="177"/>
-      <c r="AG9" s="178"/>
-      <c r="AH9" s="178"/>
-      <c r="AI9" s="179"/>
+      <c r="B9" s="122"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="129"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="129"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="132"/>
+      <c r="T9" s="132"/>
+      <c r="U9" s="132"/>
+      <c r="V9" s="132"/>
+      <c r="W9" s="132"/>
+      <c r="X9" s="132"/>
+      <c r="Y9" s="132"/>
+      <c r="Z9" s="132"/>
+      <c r="AA9" s="132"/>
+      <c r="AB9" s="132"/>
+      <c r="AC9" s="132"/>
+      <c r="AD9" s="132"/>
+      <c r="AE9" s="133"/>
+      <c r="AF9" s="128"/>
+      <c r="AG9" s="129"/>
+      <c r="AH9" s="129"/>
+      <c r="AI9" s="130"/>
     </row>
     <row r="10" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="14"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="172"/>
-      <c r="D10" s="173"/>
-      <c r="E10" s="174"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="171"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="172"/>
-      <c r="J10" s="177"/>
-      <c r="K10" s="178"/>
-      <c r="L10" s="178"/>
-      <c r="M10" s="178"/>
-      <c r="N10" s="178"/>
-      <c r="O10" s="178"/>
-      <c r="P10" s="179"/>
-      <c r="Q10" s="180"/>
-      <c r="R10" s="181"/>
-      <c r="S10" s="181"/>
-      <c r="T10" s="181"/>
-      <c r="U10" s="181"/>
-      <c r="V10" s="181"/>
-      <c r="W10" s="181"/>
-      <c r="X10" s="181"/>
-      <c r="Y10" s="181"/>
-      <c r="Z10" s="181"/>
-      <c r="AA10" s="181"/>
-      <c r="AB10" s="181"/>
-      <c r="AC10" s="181"/>
-      <c r="AD10" s="181"/>
-      <c r="AE10" s="182"/>
-      <c r="AF10" s="177"/>
-      <c r="AG10" s="178"/>
-      <c r="AH10" s="178"/>
-      <c r="AI10" s="179"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="123"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="129"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="129"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="132"/>
+      <c r="S10" s="132"/>
+      <c r="T10" s="132"/>
+      <c r="U10" s="132"/>
+      <c r="V10" s="132"/>
+      <c r="W10" s="132"/>
+      <c r="X10" s="132"/>
+      <c r="Y10" s="132"/>
+      <c r="Z10" s="132"/>
+      <c r="AA10" s="132"/>
+      <c r="AB10" s="132"/>
+      <c r="AC10" s="132"/>
+      <c r="AD10" s="132"/>
+      <c r="AE10" s="133"/>
+      <c r="AF10" s="128"/>
+      <c r="AG10" s="129"/>
+      <c r="AH10" s="129"/>
+      <c r="AI10" s="130"/>
     </row>
     <row r="11" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="14"/>
-      <c r="B11" s="171"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="172"/>
-      <c r="J11" s="177"/>
-      <c r="K11" s="178"/>
-      <c r="L11" s="178"/>
-      <c r="M11" s="178"/>
-      <c r="N11" s="178"/>
-      <c r="O11" s="178"/>
-      <c r="P11" s="179"/>
-      <c r="Q11" s="180"/>
-      <c r="R11" s="181"/>
-      <c r="S11" s="181"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="182"/>
-      <c r="AF11" s="177"/>
-      <c r="AG11" s="178"/>
-      <c r="AH11" s="178"/>
-      <c r="AI11" s="179"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
+      <c r="N11" s="129"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="132"/>
+      <c r="U11" s="132"/>
+      <c r="V11" s="132"/>
+      <c r="W11" s="132"/>
+      <c r="X11" s="132"/>
+      <c r="Y11" s="132"/>
+      <c r="Z11" s="132"/>
+      <c r="AA11" s="132"/>
+      <c r="AB11" s="132"/>
+      <c r="AC11" s="132"/>
+      <c r="AD11" s="132"/>
+      <c r="AE11" s="133"/>
+      <c r="AF11" s="128"/>
+      <c r="AG11" s="129"/>
+      <c r="AH11" s="129"/>
+      <c r="AI11" s="130"/>
     </row>
     <row r="12" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="14"/>
-      <c r="B12" s="171"/>
-      <c r="C12" s="172"/>
-      <c r="D12" s="173"/>
-      <c r="E12" s="174"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="172"/>
-      <c r="J12" s="177"/>
-      <c r="K12" s="178"/>
-      <c r="L12" s="178"/>
-      <c r="M12" s="178"/>
-      <c r="N12" s="178"/>
-      <c r="O12" s="178"/>
-      <c r="P12" s="179"/>
-      <c r="Q12" s="180"/>
-      <c r="R12" s="181"/>
-      <c r="S12" s="181"/>
-      <c r="T12" s="181"/>
-      <c r="U12" s="181"/>
-      <c r="V12" s="181"/>
-      <c r="W12" s="181"/>
-      <c r="X12" s="181"/>
-      <c r="Y12" s="181"/>
-      <c r="Z12" s="181"/>
-      <c r="AA12" s="181"/>
-      <c r="AB12" s="181"/>
-      <c r="AC12" s="181"/>
-      <c r="AD12" s="181"/>
-      <c r="AE12" s="182"/>
-      <c r="AF12" s="177"/>
-      <c r="AG12" s="178"/>
-      <c r="AH12" s="178"/>
-      <c r="AI12" s="179"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+      <c r="M12" s="129"/>
+      <c r="N12" s="129"/>
+      <c r="O12" s="129"/>
+      <c r="P12" s="130"/>
+      <c r="Q12" s="131"/>
+      <c r="R12" s="132"/>
+      <c r="S12" s="132"/>
+      <c r="T12" s="132"/>
+      <c r="U12" s="132"/>
+      <c r="V12" s="132"/>
+      <c r="W12" s="132"/>
+      <c r="X12" s="132"/>
+      <c r="Y12" s="132"/>
+      <c r="Z12" s="132"/>
+      <c r="AA12" s="132"/>
+      <c r="AB12" s="132"/>
+      <c r="AC12" s="132"/>
+      <c r="AD12" s="132"/>
+      <c r="AE12" s="133"/>
+      <c r="AF12" s="128"/>
+      <c r="AG12" s="129"/>
+      <c r="AH12" s="129"/>
+      <c r="AI12" s="130"/>
     </row>
     <row r="13" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="14"/>
-      <c r="B13" s="171"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="173"/>
-      <c r="E13" s="174"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="171"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="172"/>
-      <c r="J13" s="177"/>
-      <c r="K13" s="178"/>
-      <c r="L13" s="178"/>
-      <c r="M13" s="178"/>
-      <c r="N13" s="178"/>
-      <c r="O13" s="178"/>
-      <c r="P13" s="179"/>
-      <c r="Q13" s="180"/>
-      <c r="R13" s="181"/>
-      <c r="S13" s="181"/>
-      <c r="T13" s="181"/>
-      <c r="U13" s="181"/>
-      <c r="V13" s="181"/>
-      <c r="W13" s="181"/>
-      <c r="X13" s="181"/>
-      <c r="Y13" s="181"/>
-      <c r="Z13" s="181"/>
-      <c r="AA13" s="181"/>
-      <c r="AB13" s="181"/>
-      <c r="AC13" s="181"/>
-      <c r="AD13" s="181"/>
-      <c r="AE13" s="182"/>
-      <c r="AF13" s="177"/>
-      <c r="AG13" s="178"/>
-      <c r="AH13" s="178"/>
-      <c r="AI13" s="179"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="132"/>
+      <c r="T13" s="132"/>
+      <c r="U13" s="132"/>
+      <c r="V13" s="132"/>
+      <c r="W13" s="132"/>
+      <c r="X13" s="132"/>
+      <c r="Y13" s="132"/>
+      <c r="Z13" s="132"/>
+      <c r="AA13" s="132"/>
+      <c r="AB13" s="132"/>
+      <c r="AC13" s="132"/>
+      <c r="AD13" s="132"/>
+      <c r="AE13" s="133"/>
+      <c r="AF13" s="128"/>
+      <c r="AG13" s="129"/>
+      <c r="AH13" s="129"/>
+      <c r="AI13" s="130"/>
     </row>
     <row r="14" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="14"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="174"/>
-      <c r="F14" s="175"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="176"/>
-      <c r="I14" s="172"/>
-      <c r="J14" s="177"/>
-      <c r="K14" s="178"/>
-      <c r="L14" s="178"/>
-      <c r="M14" s="178"/>
-      <c r="N14" s="178"/>
-      <c r="O14" s="178"/>
-      <c r="P14" s="179"/>
-      <c r="Q14" s="180"/>
-      <c r="R14" s="181"/>
-      <c r="S14" s="181"/>
-      <c r="T14" s="181"/>
-      <c r="U14" s="181"/>
-      <c r="V14" s="181"/>
-      <c r="W14" s="181"/>
-      <c r="X14" s="181"/>
-      <c r="Y14" s="181"/>
-      <c r="Z14" s="181"/>
-      <c r="AA14" s="181"/>
-      <c r="AB14" s="181"/>
-      <c r="AC14" s="181"/>
-      <c r="AD14" s="181"/>
-      <c r="AE14" s="182"/>
-      <c r="AF14" s="177"/>
-      <c r="AG14" s="178"/>
-      <c r="AH14" s="178"/>
-      <c r="AI14" s="179"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="132"/>
+      <c r="S14" s="132"/>
+      <c r="T14" s="132"/>
+      <c r="U14" s="132"/>
+      <c r="V14" s="132"/>
+      <c r="W14" s="132"/>
+      <c r="X14" s="132"/>
+      <c r="Y14" s="132"/>
+      <c r="Z14" s="132"/>
+      <c r="AA14" s="132"/>
+      <c r="AB14" s="132"/>
+      <c r="AC14" s="132"/>
+      <c r="AD14" s="132"/>
+      <c r="AE14" s="133"/>
+      <c r="AF14" s="128"/>
+      <c r="AG14" s="129"/>
+      <c r="AH14" s="129"/>
+      <c r="AI14" s="130"/>
     </row>
     <row r="15" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="172"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="174"/>
-      <c r="F15" s="175"/>
-      <c r="G15" s="171"/>
-      <c r="H15" s="176"/>
-      <c r="I15" s="172"/>
-      <c r="J15" s="177"/>
-      <c r="K15" s="178"/>
-      <c r="L15" s="178"/>
-      <c r="M15" s="178"/>
-      <c r="N15" s="178"/>
-      <c r="O15" s="178"/>
-      <c r="P15" s="179"/>
-      <c r="Q15" s="180"/>
-      <c r="R15" s="181"/>
-      <c r="S15" s="181"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="181"/>
-      <c r="V15" s="181"/>
-      <c r="W15" s="181"/>
-      <c r="X15" s="181"/>
-      <c r="Y15" s="181"/>
-      <c r="Z15" s="181"/>
-      <c r="AA15" s="181"/>
-      <c r="AB15" s="181"/>
-      <c r="AC15" s="181"/>
-      <c r="AD15" s="181"/>
-      <c r="AE15" s="182"/>
-      <c r="AF15" s="177"/>
-      <c r="AG15" s="178"/>
-      <c r="AH15" s="178"/>
-      <c r="AI15" s="179"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="129"/>
+      <c r="L15" s="129"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="129"/>
+      <c r="O15" s="129"/>
+      <c r="P15" s="130"/>
+      <c r="Q15" s="131"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="132"/>
+      <c r="U15" s="132"/>
+      <c r="V15" s="132"/>
+      <c r="W15" s="132"/>
+      <c r="X15" s="132"/>
+      <c r="Y15" s="132"/>
+      <c r="Z15" s="132"/>
+      <c r="AA15" s="132"/>
+      <c r="AB15" s="132"/>
+      <c r="AC15" s="132"/>
+      <c r="AD15" s="132"/>
+      <c r="AE15" s="133"/>
+      <c r="AF15" s="128"/>
+      <c r="AG15" s="129"/>
+      <c r="AH15" s="129"/>
+      <c r="AI15" s="130"/>
     </row>
     <row r="16" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="14"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="172"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="176"/>
-      <c r="I16" s="172"/>
-      <c r="J16" s="177"/>
-      <c r="K16" s="178"/>
-      <c r="L16" s="178"/>
-      <c r="M16" s="178"/>
-      <c r="N16" s="178"/>
-      <c r="O16" s="178"/>
-      <c r="P16" s="179"/>
-      <c r="Q16" s="180"/>
-      <c r="R16" s="181"/>
-      <c r="S16" s="181"/>
-      <c r="T16" s="181"/>
-      <c r="U16" s="181"/>
-      <c r="V16" s="181"/>
-      <c r="W16" s="181"/>
-      <c r="X16" s="181"/>
-      <c r="Y16" s="181"/>
-      <c r="Z16" s="181"/>
-      <c r="AA16" s="181"/>
-      <c r="AB16" s="181"/>
-      <c r="AC16" s="181"/>
-      <c r="AD16" s="181"/>
-      <c r="AE16" s="182"/>
-      <c r="AF16" s="177"/>
-      <c r="AG16" s="178"/>
-      <c r="AH16" s="178"/>
-      <c r="AI16" s="179"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="129"/>
+      <c r="M16" s="129"/>
+      <c r="N16" s="129"/>
+      <c r="O16" s="129"/>
+      <c r="P16" s="130"/>
+      <c r="Q16" s="131"/>
+      <c r="R16" s="132"/>
+      <c r="S16" s="132"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="132"/>
+      <c r="V16" s="132"/>
+      <c r="W16" s="132"/>
+      <c r="X16" s="132"/>
+      <c r="Y16" s="132"/>
+      <c r="Z16" s="132"/>
+      <c r="AA16" s="132"/>
+      <c r="AB16" s="132"/>
+      <c r="AC16" s="132"/>
+      <c r="AD16" s="132"/>
+      <c r="AE16" s="133"/>
+      <c r="AF16" s="128"/>
+      <c r="AG16" s="129"/>
+      <c r="AH16" s="129"/>
+      <c r="AI16" s="130"/>
     </row>
     <row r="17" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="14"/>
-      <c r="B17" s="171"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="175"/>
-      <c r="G17" s="171"/>
-      <c r="H17" s="176"/>
-      <c r="I17" s="172"/>
-      <c r="J17" s="177"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="178"/>
-      <c r="M17" s="178"/>
-      <c r="N17" s="178"/>
-      <c r="O17" s="178"/>
-      <c r="P17" s="179"/>
-      <c r="Q17" s="180"/>
-      <c r="R17" s="181"/>
-      <c r="S17" s="181"/>
-      <c r="T17" s="181"/>
-      <c r="U17" s="181"/>
-      <c r="V17" s="181"/>
-      <c r="W17" s="181"/>
-      <c r="X17" s="181"/>
-      <c r="Y17" s="181"/>
-      <c r="Z17" s="181"/>
-      <c r="AA17" s="181"/>
-      <c r="AB17" s="181"/>
-      <c r="AC17" s="181"/>
-      <c r="AD17" s="181"/>
-      <c r="AE17" s="182"/>
-      <c r="AF17" s="177"/>
-      <c r="AG17" s="178"/>
-      <c r="AH17" s="178"/>
-      <c r="AI17" s="179"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="129"/>
+      <c r="N17" s="129"/>
+      <c r="O17" s="129"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="131"/>
+      <c r="R17" s="132"/>
+      <c r="S17" s="132"/>
+      <c r="T17" s="132"/>
+      <c r="U17" s="132"/>
+      <c r="V17" s="132"/>
+      <c r="W17" s="132"/>
+      <c r="X17" s="132"/>
+      <c r="Y17" s="132"/>
+      <c r="Z17" s="132"/>
+      <c r="AA17" s="132"/>
+      <c r="AB17" s="132"/>
+      <c r="AC17" s="132"/>
+      <c r="AD17" s="132"/>
+      <c r="AE17" s="133"/>
+      <c r="AF17" s="128"/>
+      <c r="AG17" s="129"/>
+      <c r="AH17" s="129"/>
+      <c r="AI17" s="130"/>
     </row>
     <row r="18" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="14"/>
-      <c r="B18" s="171"/>
-      <c r="C18" s="172"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="174"/>
-      <c r="F18" s="175"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="176"/>
-      <c r="I18" s="172"/>
-      <c r="J18" s="177"/>
-      <c r="K18" s="178"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="178"/>
-      <c r="N18" s="178"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="179"/>
-      <c r="Q18" s="180"/>
-      <c r="R18" s="181"/>
-      <c r="S18" s="181"/>
-      <c r="T18" s="181"/>
-      <c r="U18" s="181"/>
-      <c r="V18" s="181"/>
-      <c r="W18" s="181"/>
-      <c r="X18" s="181"/>
-      <c r="Y18" s="181"/>
-      <c r="Z18" s="181"/>
-      <c r="AA18" s="181"/>
-      <c r="AB18" s="181"/>
-      <c r="AC18" s="181"/>
-      <c r="AD18" s="181"/>
-      <c r="AE18" s="182"/>
-      <c r="AF18" s="177"/>
-      <c r="AG18" s="178"/>
-      <c r="AH18" s="178"/>
-      <c r="AI18" s="179"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="129"/>
+      <c r="M18" s="129"/>
+      <c r="N18" s="129"/>
+      <c r="O18" s="129"/>
+      <c r="P18" s="130"/>
+      <c r="Q18" s="131"/>
+      <c r="R18" s="132"/>
+      <c r="S18" s="132"/>
+      <c r="T18" s="132"/>
+      <c r="U18" s="132"/>
+      <c r="V18" s="132"/>
+      <c r="W18" s="132"/>
+      <c r="X18" s="132"/>
+      <c r="Y18" s="132"/>
+      <c r="Z18" s="132"/>
+      <c r="AA18" s="132"/>
+      <c r="AB18" s="132"/>
+      <c r="AC18" s="132"/>
+      <c r="AD18" s="132"/>
+      <c r="AE18" s="133"/>
+      <c r="AF18" s="128"/>
+      <c r="AG18" s="129"/>
+      <c r="AH18" s="129"/>
+      <c r="AI18" s="130"/>
     </row>
     <row r="19" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="14"/>
-      <c r="B19" s="171"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="174"/>
-      <c r="F19" s="175"/>
-      <c r="G19" s="171"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="172"/>
-      <c r="J19" s="177"/>
-      <c r="K19" s="178"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="178"/>
-      <c r="N19" s="178"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="180"/>
-      <c r="R19" s="181"/>
-      <c r="S19" s="181"/>
-      <c r="T19" s="181"/>
-      <c r="U19" s="181"/>
-      <c r="V19" s="181"/>
-      <c r="W19" s="181"/>
-      <c r="X19" s="181"/>
-      <c r="Y19" s="181"/>
-      <c r="Z19" s="181"/>
-      <c r="AA19" s="181"/>
-      <c r="AB19" s="181"/>
-      <c r="AC19" s="181"/>
-      <c r="AD19" s="181"/>
-      <c r="AE19" s="182"/>
-      <c r="AF19" s="177"/>
-      <c r="AG19" s="178"/>
-      <c r="AH19" s="178"/>
-      <c r="AI19" s="179"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="129"/>
+      <c r="L19" s="129"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="129"/>
+      <c r="O19" s="129"/>
+      <c r="P19" s="130"/>
+      <c r="Q19" s="131"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="132"/>
+      <c r="T19" s="132"/>
+      <c r="U19" s="132"/>
+      <c r="V19" s="132"/>
+      <c r="W19" s="132"/>
+      <c r="X19" s="132"/>
+      <c r="Y19" s="132"/>
+      <c r="Z19" s="132"/>
+      <c r="AA19" s="132"/>
+      <c r="AB19" s="132"/>
+      <c r="AC19" s="132"/>
+      <c r="AD19" s="132"/>
+      <c r="AE19" s="133"/>
+      <c r="AF19" s="128"/>
+      <c r="AG19" s="129"/>
+      <c r="AH19" s="129"/>
+      <c r="AI19" s="130"/>
     </row>
     <row r="20" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="14"/>
-      <c r="B20" s="171"/>
-      <c r="C20" s="172"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="174"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="176"/>
-      <c r="I20" s="172"/>
-      <c r="J20" s="177"/>
-      <c r="K20" s="178"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="178"/>
-      <c r="N20" s="178"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="179"/>
-      <c r="Q20" s="180"/>
-      <c r="R20" s="181"/>
-      <c r="S20" s="181"/>
-      <c r="T20" s="181"/>
-      <c r="U20" s="181"/>
-      <c r="V20" s="181"/>
-      <c r="W20" s="181"/>
-      <c r="X20" s="181"/>
-      <c r="Y20" s="181"/>
-      <c r="Z20" s="181"/>
-      <c r="AA20" s="181"/>
-      <c r="AB20" s="181"/>
-      <c r="AC20" s="181"/>
-      <c r="AD20" s="181"/>
-      <c r="AE20" s="182"/>
-      <c r="AF20" s="177"/>
-      <c r="AG20" s="178"/>
-      <c r="AH20" s="178"/>
-      <c r="AI20" s="179"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="129"/>
+      <c r="M20" s="129"/>
+      <c r="N20" s="129"/>
+      <c r="O20" s="129"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="132"/>
+      <c r="S20" s="132"/>
+      <c r="T20" s="132"/>
+      <c r="U20" s="132"/>
+      <c r="V20" s="132"/>
+      <c r="W20" s="132"/>
+      <c r="X20" s="132"/>
+      <c r="Y20" s="132"/>
+      <c r="Z20" s="132"/>
+      <c r="AA20" s="132"/>
+      <c r="AB20" s="132"/>
+      <c r="AC20" s="132"/>
+      <c r="AD20" s="132"/>
+      <c r="AE20" s="133"/>
+      <c r="AF20" s="128"/>
+      <c r="AG20" s="129"/>
+      <c r="AH20" s="129"/>
+      <c r="AI20" s="130"/>
     </row>
     <row r="21" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="14"/>
-      <c r="B21" s="171"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="174"/>
-      <c r="F21" s="175"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="176"/>
-      <c r="I21" s="172"/>
-      <c r="J21" s="177"/>
-      <c r="K21" s="178"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="178"/>
-      <c r="N21" s="178"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="179"/>
-      <c r="Q21" s="180"/>
-      <c r="R21" s="181"/>
-      <c r="S21" s="181"/>
-      <c r="T21" s="181"/>
-      <c r="U21" s="181"/>
-      <c r="V21" s="181"/>
-      <c r="W21" s="181"/>
-      <c r="X21" s="181"/>
-      <c r="Y21" s="181"/>
-      <c r="Z21" s="181"/>
-      <c r="AA21" s="181"/>
-      <c r="AB21" s="181"/>
-      <c r="AC21" s="181"/>
-      <c r="AD21" s="181"/>
-      <c r="AE21" s="182"/>
-      <c r="AF21" s="177"/>
-      <c r="AG21" s="178"/>
-      <c r="AH21" s="178"/>
-      <c r="AI21" s="179"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="129"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="129"/>
+      <c r="O21" s="129"/>
+      <c r="P21" s="130"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="132"/>
+      <c r="S21" s="132"/>
+      <c r="T21" s="132"/>
+      <c r="U21" s="132"/>
+      <c r="V21" s="132"/>
+      <c r="W21" s="132"/>
+      <c r="X21" s="132"/>
+      <c r="Y21" s="132"/>
+      <c r="Z21" s="132"/>
+      <c r="AA21" s="132"/>
+      <c r="AB21" s="132"/>
+      <c r="AC21" s="132"/>
+      <c r="AD21" s="132"/>
+      <c r="AE21" s="133"/>
+      <c r="AF21" s="128"/>
+      <c r="AG21" s="129"/>
+      <c r="AH21" s="129"/>
+      <c r="AI21" s="130"/>
     </row>
     <row r="22" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="14"/>
-      <c r="B22" s="171"/>
-      <c r="C22" s="172"/>
-      <c r="D22" s="173"/>
-      <c r="E22" s="174"/>
-      <c r="F22" s="175"/>
-      <c r="G22" s="171"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="172"/>
-      <c r="J22" s="177"/>
-      <c r="K22" s="178"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="178"/>
-      <c r="N22" s="178"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="179"/>
-      <c r="Q22" s="180"/>
-      <c r="R22" s="181"/>
-      <c r="S22" s="181"/>
-      <c r="T22" s="181"/>
-      <c r="U22" s="181"/>
-      <c r="V22" s="181"/>
-      <c r="W22" s="181"/>
-      <c r="X22" s="181"/>
-      <c r="Y22" s="181"/>
-      <c r="Z22" s="181"/>
-      <c r="AA22" s="181"/>
-      <c r="AB22" s="181"/>
-      <c r="AC22" s="181"/>
-      <c r="AD22" s="181"/>
-      <c r="AE22" s="182"/>
-      <c r="AF22" s="177"/>
-      <c r="AG22" s="178"/>
-      <c r="AH22" s="178"/>
-      <c r="AI22" s="179"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="122"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="129"/>
+      <c r="M22" s="129"/>
+      <c r="N22" s="129"/>
+      <c r="O22" s="129"/>
+      <c r="P22" s="130"/>
+      <c r="Q22" s="131"/>
+      <c r="R22" s="132"/>
+      <c r="S22" s="132"/>
+      <c r="T22" s="132"/>
+      <c r="U22" s="132"/>
+      <c r="V22" s="132"/>
+      <c r="W22" s="132"/>
+      <c r="X22" s="132"/>
+      <c r="Y22" s="132"/>
+      <c r="Z22" s="132"/>
+      <c r="AA22" s="132"/>
+      <c r="AB22" s="132"/>
+      <c r="AC22" s="132"/>
+      <c r="AD22" s="132"/>
+      <c r="AE22" s="133"/>
+      <c r="AF22" s="128"/>
+      <c r="AG22" s="129"/>
+      <c r="AH22" s="129"/>
+      <c r="AI22" s="130"/>
     </row>
     <row r="23" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="14"/>
-      <c r="B23" s="171"/>
-      <c r="C23" s="172"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="174"/>
-      <c r="F23" s="175"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="176"/>
-      <c r="I23" s="172"/>
-      <c r="J23" s="177"/>
-      <c r="K23" s="178"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="178"/>
-      <c r="N23" s="178"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="179"/>
-      <c r="Q23" s="180"/>
-      <c r="R23" s="181"/>
-      <c r="S23" s="181"/>
-      <c r="T23" s="181"/>
-      <c r="U23" s="181"/>
-      <c r="V23" s="181"/>
-      <c r="W23" s="181"/>
-      <c r="X23" s="181"/>
-      <c r="Y23" s="181"/>
-      <c r="Z23" s="181"/>
-      <c r="AA23" s="181"/>
-      <c r="AB23" s="181"/>
-      <c r="AC23" s="181"/>
-      <c r="AD23" s="181"/>
-      <c r="AE23" s="182"/>
-      <c r="AF23" s="177"/>
-      <c r="AG23" s="178"/>
-      <c r="AH23" s="178"/>
-      <c r="AI23" s="179"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="129"/>
+      <c r="N23" s="129"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="130"/>
+      <c r="Q23" s="131"/>
+      <c r="R23" s="132"/>
+      <c r="S23" s="132"/>
+      <c r="T23" s="132"/>
+      <c r="U23" s="132"/>
+      <c r="V23" s="132"/>
+      <c r="W23" s="132"/>
+      <c r="X23" s="132"/>
+      <c r="Y23" s="132"/>
+      <c r="Z23" s="132"/>
+      <c r="AA23" s="132"/>
+      <c r="AB23" s="132"/>
+      <c r="AC23" s="132"/>
+      <c r="AD23" s="132"/>
+      <c r="AE23" s="133"/>
+      <c r="AF23" s="128"/>
+      <c r="AG23" s="129"/>
+      <c r="AH23" s="129"/>
+      <c r="AI23" s="130"/>
     </row>
     <row r="24" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="14"/>
-      <c r="B24" s="171"/>
-      <c r="C24" s="172"/>
-      <c r="D24" s="173"/>
-      <c r="E24" s="174"/>
-      <c r="F24" s="175"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="176"/>
-      <c r="I24" s="172"/>
-      <c r="J24" s="177"/>
-      <c r="K24" s="178"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="178"/>
-      <c r="N24" s="178"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="179"/>
-      <c r="Q24" s="180"/>
-      <c r="R24" s="181"/>
-      <c r="S24" s="181"/>
-      <c r="T24" s="181"/>
-      <c r="U24" s="181"/>
-      <c r="V24" s="181"/>
-      <c r="W24" s="181"/>
-      <c r="X24" s="181"/>
-      <c r="Y24" s="181"/>
-      <c r="Z24" s="181"/>
-      <c r="AA24" s="181"/>
-      <c r="AB24" s="181"/>
-      <c r="AC24" s="181"/>
-      <c r="AD24" s="181"/>
-      <c r="AE24" s="182"/>
-      <c r="AF24" s="177"/>
-      <c r="AG24" s="178"/>
-      <c r="AH24" s="178"/>
-      <c r="AI24" s="179"/>
+      <c r="B24" s="122"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="129"/>
+      <c r="M24" s="129"/>
+      <c r="N24" s="129"/>
+      <c r="O24" s="129"/>
+      <c r="P24" s="130"/>
+      <c r="Q24" s="131"/>
+      <c r="R24" s="132"/>
+      <c r="S24" s="132"/>
+      <c r="T24" s="132"/>
+      <c r="U24" s="132"/>
+      <c r="V24" s="132"/>
+      <c r="W24" s="132"/>
+      <c r="X24" s="132"/>
+      <c r="Y24" s="132"/>
+      <c r="Z24" s="132"/>
+      <c r="AA24" s="132"/>
+      <c r="AB24" s="132"/>
+      <c r="AC24" s="132"/>
+      <c r="AD24" s="132"/>
+      <c r="AE24" s="133"/>
+      <c r="AF24" s="128"/>
+      <c r="AG24" s="129"/>
+      <c r="AH24" s="129"/>
+      <c r="AI24" s="130"/>
     </row>
     <row r="25" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="14"/>
-      <c r="B25" s="171"/>
-      <c r="C25" s="172"/>
-      <c r="D25" s="173"/>
-      <c r="E25" s="174"/>
-      <c r="F25" s="175"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="176"/>
-      <c r="I25" s="172"/>
-      <c r="J25" s="177"/>
-      <c r="K25" s="178"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="178"/>
-      <c r="N25" s="178"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="179"/>
-      <c r="Q25" s="180"/>
-      <c r="R25" s="181"/>
-      <c r="S25" s="181"/>
-      <c r="T25" s="181"/>
-      <c r="U25" s="181"/>
-      <c r="V25" s="181"/>
-      <c r="W25" s="181"/>
-      <c r="X25" s="181"/>
-      <c r="Y25" s="181"/>
-      <c r="Z25" s="181"/>
-      <c r="AA25" s="181"/>
-      <c r="AB25" s="181"/>
-      <c r="AC25" s="181"/>
-      <c r="AD25" s="181"/>
-      <c r="AE25" s="182"/>
-      <c r="AF25" s="177"/>
-      <c r="AG25" s="178"/>
-      <c r="AH25" s="178"/>
-      <c r="AI25" s="179"/>
+      <c r="B25" s="122"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="122"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="129"/>
+      <c r="M25" s="129"/>
+      <c r="N25" s="129"/>
+      <c r="O25" s="129"/>
+      <c r="P25" s="130"/>
+      <c r="Q25" s="131"/>
+      <c r="R25" s="132"/>
+      <c r="S25" s="132"/>
+      <c r="T25" s="132"/>
+      <c r="U25" s="132"/>
+      <c r="V25" s="132"/>
+      <c r="W25" s="132"/>
+      <c r="X25" s="132"/>
+      <c r="Y25" s="132"/>
+      <c r="Z25" s="132"/>
+      <c r="AA25" s="132"/>
+      <c r="AB25" s="132"/>
+      <c r="AC25" s="132"/>
+      <c r="AD25" s="132"/>
+      <c r="AE25" s="133"/>
+      <c r="AF25" s="128"/>
+      <c r="AG25" s="129"/>
+      <c r="AH25" s="129"/>
+      <c r="AI25" s="130"/>
     </row>
     <row r="26" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="14"/>
-      <c r="B26" s="171"/>
-      <c r="C26" s="172"/>
-      <c r="D26" s="173"/>
-      <c r="E26" s="174"/>
-      <c r="F26" s="175"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="176"/>
-      <c r="I26" s="172"/>
-      <c r="J26" s="177"/>
-      <c r="K26" s="178"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="178"/>
-      <c r="N26" s="178"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="179"/>
-      <c r="Q26" s="180"/>
-      <c r="R26" s="181"/>
-      <c r="S26" s="181"/>
-      <c r="T26" s="181"/>
-      <c r="U26" s="181"/>
-      <c r="V26" s="181"/>
-      <c r="W26" s="181"/>
-      <c r="X26" s="181"/>
-      <c r="Y26" s="181"/>
-      <c r="Z26" s="181"/>
-      <c r="AA26" s="181"/>
-      <c r="AB26" s="181"/>
-      <c r="AC26" s="181"/>
-      <c r="AD26" s="181"/>
-      <c r="AE26" s="182"/>
-      <c r="AF26" s="177"/>
-      <c r="AG26" s="178"/>
-      <c r="AH26" s="178"/>
-      <c r="AI26" s="179"/>
+      <c r="B26" s="122"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="122"/>
+      <c r="H26" s="127"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="129"/>
+      <c r="L26" s="129"/>
+      <c r="M26" s="129"/>
+      <c r="N26" s="129"/>
+      <c r="O26" s="129"/>
+      <c r="P26" s="130"/>
+      <c r="Q26" s="131"/>
+      <c r="R26" s="132"/>
+      <c r="S26" s="132"/>
+      <c r="T26" s="132"/>
+      <c r="U26" s="132"/>
+      <c r="V26" s="132"/>
+      <c r="W26" s="132"/>
+      <c r="X26" s="132"/>
+      <c r="Y26" s="132"/>
+      <c r="Z26" s="132"/>
+      <c r="AA26" s="132"/>
+      <c r="AB26" s="132"/>
+      <c r="AC26" s="132"/>
+      <c r="AD26" s="132"/>
+      <c r="AE26" s="133"/>
+      <c r="AF26" s="128"/>
+      <c r="AG26" s="129"/>
+      <c r="AH26" s="129"/>
+      <c r="AI26" s="130"/>
     </row>
     <row r="27" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="14"/>
-      <c r="B27" s="171"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="173"/>
-      <c r="E27" s="174"/>
-      <c r="F27" s="175"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="176"/>
-      <c r="I27" s="172"/>
-      <c r="J27" s="177"/>
-      <c r="K27" s="178"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="178"/>
-      <c r="N27" s="178"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="179"/>
-      <c r="Q27" s="180"/>
-      <c r="R27" s="181"/>
-      <c r="S27" s="181"/>
-      <c r="T27" s="181"/>
-      <c r="U27" s="181"/>
-      <c r="V27" s="181"/>
-      <c r="W27" s="181"/>
-      <c r="X27" s="181"/>
-      <c r="Y27" s="181"/>
-      <c r="Z27" s="181"/>
-      <c r="AA27" s="181"/>
-      <c r="AB27" s="181"/>
-      <c r="AC27" s="181"/>
-      <c r="AD27" s="181"/>
-      <c r="AE27" s="182"/>
-      <c r="AF27" s="177"/>
-      <c r="AG27" s="178"/>
-      <c r="AH27" s="178"/>
-      <c r="AI27" s="179"/>
+      <c r="B27" s="122"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="127"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="129"/>
+      <c r="M27" s="129"/>
+      <c r="N27" s="129"/>
+      <c r="O27" s="129"/>
+      <c r="P27" s="130"/>
+      <c r="Q27" s="131"/>
+      <c r="R27" s="132"/>
+      <c r="S27" s="132"/>
+      <c r="T27" s="132"/>
+      <c r="U27" s="132"/>
+      <c r="V27" s="132"/>
+      <c r="W27" s="132"/>
+      <c r="X27" s="132"/>
+      <c r="Y27" s="132"/>
+      <c r="Z27" s="132"/>
+      <c r="AA27" s="132"/>
+      <c r="AB27" s="132"/>
+      <c r="AC27" s="132"/>
+      <c r="AD27" s="132"/>
+      <c r="AE27" s="133"/>
+      <c r="AF27" s="128"/>
+      <c r="AG27" s="129"/>
+      <c r="AH27" s="129"/>
+      <c r="AI27" s="130"/>
     </row>
     <row r="28" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="14"/>
-      <c r="B28" s="171"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="175"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="176"/>
-      <c r="I28" s="172"/>
-      <c r="J28" s="177"/>
-      <c r="K28" s="178"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="178"/>
-      <c r="N28" s="178"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="179"/>
-      <c r="Q28" s="180"/>
-      <c r="R28" s="181"/>
-      <c r="S28" s="181"/>
-      <c r="T28" s="181"/>
-      <c r="U28" s="181"/>
-      <c r="V28" s="181"/>
-      <c r="W28" s="181"/>
-      <c r="X28" s="181"/>
-      <c r="Y28" s="181"/>
-      <c r="Z28" s="181"/>
-      <c r="AA28" s="181"/>
-      <c r="AB28" s="181"/>
-      <c r="AC28" s="181"/>
-      <c r="AD28" s="181"/>
-      <c r="AE28" s="182"/>
-      <c r="AF28" s="177"/>
-      <c r="AG28" s="178"/>
-      <c r="AH28" s="178"/>
-      <c r="AI28" s="179"/>
+      <c r="B28" s="122"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="126"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="123"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="129"/>
+      <c r="L28" s="129"/>
+      <c r="M28" s="129"/>
+      <c r="N28" s="129"/>
+      <c r="O28" s="129"/>
+      <c r="P28" s="130"/>
+      <c r="Q28" s="131"/>
+      <c r="R28" s="132"/>
+      <c r="S28" s="132"/>
+      <c r="T28" s="132"/>
+      <c r="U28" s="132"/>
+      <c r="V28" s="132"/>
+      <c r="W28" s="132"/>
+      <c r="X28" s="132"/>
+      <c r="Y28" s="132"/>
+      <c r="Z28" s="132"/>
+      <c r="AA28" s="132"/>
+      <c r="AB28" s="132"/>
+      <c r="AC28" s="132"/>
+      <c r="AD28" s="132"/>
+      <c r="AE28" s="133"/>
+      <c r="AF28" s="128"/>
+      <c r="AG28" s="129"/>
+      <c r="AH28" s="129"/>
+      <c r="AI28" s="130"/>
     </row>
     <row r="29" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="14"/>
-      <c r="B29" s="171"/>
-      <c r="C29" s="172"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="175"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="176"/>
-      <c r="I29" s="172"/>
-      <c r="J29" s="177"/>
-      <c r="K29" s="178"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="178"/>
-      <c r="N29" s="178"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="179"/>
-      <c r="Q29" s="180"/>
-      <c r="R29" s="181"/>
-      <c r="S29" s="181"/>
-      <c r="T29" s="181"/>
-      <c r="U29" s="181"/>
-      <c r="V29" s="181"/>
-      <c r="W29" s="181"/>
-      <c r="X29" s="181"/>
-      <c r="Y29" s="181"/>
-      <c r="Z29" s="181"/>
-      <c r="AA29" s="181"/>
-      <c r="AB29" s="181"/>
-      <c r="AC29" s="181"/>
-      <c r="AD29" s="181"/>
-      <c r="AE29" s="182"/>
-      <c r="AF29" s="177"/>
-      <c r="AG29" s="178"/>
-      <c r="AH29" s="178"/>
-      <c r="AI29" s="179"/>
+      <c r="B29" s="122"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="124"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="123"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="129"/>
+      <c r="L29" s="129"/>
+      <c r="M29" s="129"/>
+      <c r="N29" s="129"/>
+      <c r="O29" s="129"/>
+      <c r="P29" s="130"/>
+      <c r="Q29" s="131"/>
+      <c r="R29" s="132"/>
+      <c r="S29" s="132"/>
+      <c r="T29" s="132"/>
+      <c r="U29" s="132"/>
+      <c r="V29" s="132"/>
+      <c r="W29" s="132"/>
+      <c r="X29" s="132"/>
+      <c r="Y29" s="132"/>
+      <c r="Z29" s="132"/>
+      <c r="AA29" s="132"/>
+      <c r="AB29" s="132"/>
+      <c r="AC29" s="132"/>
+      <c r="AD29" s="132"/>
+      <c r="AE29" s="133"/>
+      <c r="AF29" s="128"/>
+      <c r="AG29" s="129"/>
+      <c r="AH29" s="129"/>
+      <c r="AI29" s="130"/>
     </row>
     <row r="30" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="14"/>
-      <c r="B30" s="171"/>
-      <c r="C30" s="172"/>
-      <c r="D30" s="173"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="175"/>
-      <c r="G30" s="171"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="172"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="178"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="178"/>
-      <c r="N30" s="178"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="179"/>
-      <c r="Q30" s="180"/>
-      <c r="R30" s="181"/>
-      <c r="S30" s="181"/>
-      <c r="T30" s="181"/>
-      <c r="U30" s="181"/>
-      <c r="V30" s="181"/>
-      <c r="W30" s="181"/>
-      <c r="X30" s="181"/>
-      <c r="Y30" s="181"/>
-      <c r="Z30" s="181"/>
-      <c r="AA30" s="181"/>
-      <c r="AB30" s="181"/>
-      <c r="AC30" s="181"/>
-      <c r="AD30" s="181"/>
-      <c r="AE30" s="182"/>
-      <c r="AF30" s="177"/>
-      <c r="AG30" s="178"/>
-      <c r="AH30" s="178"/>
-      <c r="AI30" s="179"/>
+      <c r="B30" s="122"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="126"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="127"/>
+      <c r="I30" s="123"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="129"/>
+      <c r="L30" s="129"/>
+      <c r="M30" s="129"/>
+      <c r="N30" s="129"/>
+      <c r="O30" s="129"/>
+      <c r="P30" s="130"/>
+      <c r="Q30" s="131"/>
+      <c r="R30" s="132"/>
+      <c r="S30" s="132"/>
+      <c r="T30" s="132"/>
+      <c r="U30" s="132"/>
+      <c r="V30" s="132"/>
+      <c r="W30" s="132"/>
+      <c r="X30" s="132"/>
+      <c r="Y30" s="132"/>
+      <c r="Z30" s="132"/>
+      <c r="AA30" s="132"/>
+      <c r="AB30" s="132"/>
+      <c r="AC30" s="132"/>
+      <c r="AD30" s="132"/>
+      <c r="AE30" s="133"/>
+      <c r="AF30" s="128"/>
+      <c r="AG30" s="129"/>
+      <c r="AH30" s="129"/>
+      <c r="AI30" s="130"/>
     </row>
     <row r="31" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="14"/>
-      <c r="B31" s="171"/>
-      <c r="C31" s="172"/>
-      <c r="D31" s="173"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="171"/>
-      <c r="H31" s="176"/>
-      <c r="I31" s="172"/>
-      <c r="J31" s="177"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="178"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="180"/>
-      <c r="R31" s="181"/>
-      <c r="S31" s="181"/>
-      <c r="T31" s="181"/>
-      <c r="U31" s="181"/>
-      <c r="V31" s="181"/>
-      <c r="W31" s="181"/>
-      <c r="X31" s="181"/>
-      <c r="Y31" s="181"/>
-      <c r="Z31" s="181"/>
-      <c r="AA31" s="181"/>
-      <c r="AB31" s="181"/>
-      <c r="AC31" s="181"/>
-      <c r="AD31" s="181"/>
-      <c r="AE31" s="182"/>
-      <c r="AF31" s="177"/>
-      <c r="AG31" s="178"/>
-      <c r="AH31" s="178"/>
-      <c r="AI31" s="179"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="127"/>
+      <c r="I31" s="123"/>
+      <c r="J31" s="128"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="129"/>
+      <c r="M31" s="129"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="129"/>
+      <c r="P31" s="130"/>
+      <c r="Q31" s="131"/>
+      <c r="R31" s="132"/>
+      <c r="S31" s="132"/>
+      <c r="T31" s="132"/>
+      <c r="U31" s="132"/>
+      <c r="V31" s="132"/>
+      <c r="W31" s="132"/>
+      <c r="X31" s="132"/>
+      <c r="Y31" s="132"/>
+      <c r="Z31" s="132"/>
+      <c r="AA31" s="132"/>
+      <c r="AB31" s="132"/>
+      <c r="AC31" s="132"/>
+      <c r="AD31" s="132"/>
+      <c r="AE31" s="133"/>
+      <c r="AF31" s="128"/>
+      <c r="AG31" s="129"/>
+      <c r="AH31" s="129"/>
+      <c r="AI31" s="130"/>
     </row>
     <row r="32" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="14"/>
-      <c r="B32" s="171"/>
-      <c r="C32" s="172"/>
-      <c r="D32" s="173"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="175"/>
-      <c r="G32" s="171"/>
-      <c r="H32" s="176"/>
-      <c r="I32" s="172"/>
-      <c r="J32" s="177"/>
-      <c r="K32" s="183"/>
-      <c r="L32" s="178"/>
-      <c r="M32" s="178"/>
-      <c r="N32" s="178"/>
-      <c r="O32" s="178"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="180"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="181"/>
-      <c r="T32" s="181"/>
-      <c r="U32" s="181"/>
-      <c r="V32" s="181"/>
-      <c r="W32" s="181"/>
-      <c r="X32" s="181"/>
-      <c r="Y32" s="181"/>
-      <c r="Z32" s="181"/>
-      <c r="AA32" s="181"/>
-      <c r="AB32" s="181"/>
-      <c r="AC32" s="181"/>
-      <c r="AD32" s="181"/>
-      <c r="AE32" s="182"/>
-      <c r="AF32" s="177"/>
-      <c r="AG32" s="178"/>
-      <c r="AH32" s="178"/>
-      <c r="AI32" s="179"/>
+      <c r="B32" s="122"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="127"/>
+      <c r="I32" s="123"/>
+      <c r="J32" s="128"/>
+      <c r="K32" s="134"/>
+      <c r="L32" s="129"/>
+      <c r="M32" s="129"/>
+      <c r="N32" s="129"/>
+      <c r="O32" s="129"/>
+      <c r="P32" s="130"/>
+      <c r="Q32" s="131"/>
+      <c r="R32" s="132"/>
+      <c r="S32" s="132"/>
+      <c r="T32" s="132"/>
+      <c r="U32" s="132"/>
+      <c r="V32" s="132"/>
+      <c r="W32" s="132"/>
+      <c r="X32" s="132"/>
+      <c r="Y32" s="132"/>
+      <c r="Z32" s="132"/>
+      <c r="AA32" s="132"/>
+      <c r="AB32" s="132"/>
+      <c r="AC32" s="132"/>
+      <c r="AD32" s="132"/>
+      <c r="AE32" s="133"/>
+      <c r="AF32" s="128"/>
+      <c r="AG32" s="129"/>
+      <c r="AH32" s="129"/>
+      <c r="AI32" s="130"/>
     </row>
     <row r="33" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="14"/>
-      <c r="B33" s="171"/>
-      <c r="C33" s="172"/>
-      <c r="D33" s="173"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="175"/>
-      <c r="G33" s="171"/>
-      <c r="H33" s="176"/>
-      <c r="I33" s="172"/>
-      <c r="J33" s="177"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="178"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="178"/>
-      <c r="O33" s="178"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="180"/>
-      <c r="R33" s="181"/>
-      <c r="S33" s="181"/>
-      <c r="T33" s="181"/>
-      <c r="U33" s="181"/>
-      <c r="V33" s="181"/>
-      <c r="W33" s="181"/>
-      <c r="X33" s="181"/>
-      <c r="Y33" s="181"/>
-      <c r="Z33" s="181"/>
-      <c r="AA33" s="181"/>
-      <c r="AB33" s="181"/>
-      <c r="AC33" s="181"/>
-      <c r="AD33" s="181"/>
-      <c r="AE33" s="182"/>
-      <c r="AF33" s="177"/>
-      <c r="AG33" s="178"/>
-      <c r="AH33" s="178"/>
-      <c r="AI33" s="179"/>
+      <c r="B33" s="122"/>
+      <c r="C33" s="123"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="122"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="129"/>
+      <c r="M33" s="129"/>
+      <c r="N33" s="129"/>
+      <c r="O33" s="129"/>
+      <c r="P33" s="130"/>
+      <c r="Q33" s="131"/>
+      <c r="R33" s="132"/>
+      <c r="S33" s="132"/>
+      <c r="T33" s="132"/>
+      <c r="U33" s="132"/>
+      <c r="V33" s="132"/>
+      <c r="W33" s="132"/>
+      <c r="X33" s="132"/>
+      <c r="Y33" s="132"/>
+      <c r="Z33" s="132"/>
+      <c r="AA33" s="132"/>
+      <c r="AB33" s="132"/>
+      <c r="AC33" s="132"/>
+      <c r="AD33" s="132"/>
+      <c r="AE33" s="133"/>
+      <c r="AF33" s="128"/>
+      <c r="AG33" s="129"/>
+      <c r="AH33" s="129"/>
+      <c r="AI33" s="130"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:N2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="Q7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="G33:I33"/>
@@ -10084,167 +10241,6 @@
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="Q32:AE32"/>
     <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:N2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="S1:Z3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -20239,7 +20235,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="25" t="s">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="O7" s="25" t="s">
         <v>23</v>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A09B8BB-D8F2-4B7A-9733-9F7EA8D59506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4F791D-6B2B-40BA-A89E-17F0158261A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7228,93 +7228,6 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -7413,6 +7326,93 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8867,55 +8867,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="159"/>
-      <c r="O1" s="166" t="s">
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="167"/>
-      <c r="Q1" s="167"/>
-      <c r="R1" s="168"/>
-      <c r="S1" s="175" t="s">
+      <c r="P1" s="138"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="139"/>
+      <c r="S1" s="146" t="s">
         <v>453</v>
       </c>
-      <c r="T1" s="176"/>
-      <c r="U1" s="176"/>
-      <c r="V1" s="176"/>
-      <c r="W1" s="176"/>
-      <c r="X1" s="176"/>
-      <c r="Y1" s="176"/>
-      <c r="Z1" s="177"/>
-      <c r="AA1" s="151" t="s">
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="148"/>
+      <c r="AA1" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="152"/>
-      <c r="AC1" s="153" t="str">
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="124" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="155"/>
-      <c r="AG1" s="160" t="str">
+      <c r="AD1" s="125"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="126"/>
+      <c r="AG1" s="131" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="161"/>
-      <c r="AI1" s="162"/>
+      <c r="AH1" s="132"/>
+      <c r="AI1" s="133"/>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
       <c r="AL1" s="23"/>
@@ -8923,51 +8923,51 @@
       <c r="AN1" s="24"/>
     </row>
     <row r="2" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="170"/>
-      <c r="Q2" s="170"/>
-      <c r="R2" s="171"/>
-      <c r="S2" s="178"/>
-      <c r="T2" s="179"/>
-      <c r="U2" s="179"/>
-      <c r="V2" s="179"/>
-      <c r="W2" s="179"/>
-      <c r="X2" s="179"/>
-      <c r="Y2" s="179"/>
-      <c r="Z2" s="180"/>
-      <c r="AA2" s="151" t="s">
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="142"/>
+      <c r="S2" s="149"/>
+      <c r="T2" s="150"/>
+      <c r="U2" s="150"/>
+      <c r="V2" s="150"/>
+      <c r="W2" s="150"/>
+      <c r="X2" s="150"/>
+      <c r="Y2" s="150"/>
+      <c r="Z2" s="151"/>
+      <c r="AA2" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="163" t="str">
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="134" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="164"/>
-      <c r="AE2" s="164"/>
-      <c r="AF2" s="165"/>
-      <c r="AG2" s="160" t="str">
+      <c r="AD2" s="135"/>
+      <c r="AE2" s="135"/>
+      <c r="AF2" s="136"/>
+      <c r="AG2" s="131" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="161"/>
-      <c r="AI2" s="162"/>
+      <c r="AH2" s="132"/>
+      <c r="AI2" s="133"/>
       <c r="AJ2" s="23"/>
       <c r="AK2" s="23"/>
       <c r="AL2" s="23"/>
@@ -8975,43 +8975,43 @@
       <c r="AN2" s="23"/>
     </row>
     <row r="3" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="151" t="s">
+      <c r="A3" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="158"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="159"/>
-      <c r="O3" s="172"/>
-      <c r="P3" s="173"/>
-      <c r="Q3" s="173"/>
-      <c r="R3" s="174"/>
-      <c r="S3" s="181"/>
-      <c r="T3" s="182"/>
-      <c r="U3" s="182"/>
-      <c r="V3" s="182"/>
-      <c r="W3" s="182"/>
-      <c r="X3" s="182"/>
-      <c r="Y3" s="182"/>
-      <c r="Z3" s="183"/>
-      <c r="AA3" s="151"/>
-      <c r="AB3" s="152"/>
-      <c r="AC3" s="153"/>
-      <c r="AD3" s="154"/>
-      <c r="AE3" s="154"/>
-      <c r="AF3" s="155"/>
-      <c r="AG3" s="160"/>
-      <c r="AH3" s="161"/>
-      <c r="AI3" s="162"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="144"/>
+      <c r="Q3" s="144"/>
+      <c r="R3" s="145"/>
+      <c r="S3" s="152"/>
+      <c r="T3" s="153"/>
+      <c r="U3" s="153"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="153"/>
+      <c r="Y3" s="153"/>
+      <c r="Z3" s="154"/>
+      <c r="AA3" s="122"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="124"/>
+      <c r="AD3" s="125"/>
+      <c r="AE3" s="125"/>
+      <c r="AF3" s="126"/>
+      <c r="AG3" s="131"/>
+      <c r="AH3" s="132"/>
+      <c r="AI3" s="133"/>
       <c r="AJ3" s="23"/>
       <c r="AK3" s="23"/>
       <c r="AL3" s="23"/>
@@ -9048,1181 +9048,1020 @@
       <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="135" t="s">
+      <c r="B7" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="136"/>
-      <c r="D7" s="135" t="s">
+      <c r="C7" s="156"/>
+      <c r="D7" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="137"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="135" t="s">
+      <c r="E7" s="157"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="137"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="135" t="s">
+      <c r="H7" s="157"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="137"/>
-      <c r="L7" s="137"/>
-      <c r="M7" s="137"/>
-      <c r="N7" s="137"/>
-      <c r="O7" s="137"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="135" t="s">
+      <c r="K7" s="157"/>
+      <c r="L7" s="157"/>
+      <c r="M7" s="157"/>
+      <c r="N7" s="157"/>
+      <c r="O7" s="157"/>
+      <c r="P7" s="156"/>
+      <c r="Q7" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="R7" s="137"/>
-      <c r="S7" s="137"/>
-      <c r="T7" s="137"/>
-      <c r="U7" s="137"/>
-      <c r="V7" s="137"/>
-      <c r="W7" s="137"/>
-      <c r="X7" s="137"/>
-      <c r="Y7" s="137"/>
-      <c r="Z7" s="137"/>
-      <c r="AA7" s="137"/>
-      <c r="AB7" s="137"/>
-      <c r="AC7" s="137"/>
-      <c r="AD7" s="137"/>
-      <c r="AE7" s="136"/>
-      <c r="AF7" s="135" t="s">
+      <c r="R7" s="157"/>
+      <c r="S7" s="157"/>
+      <c r="T7" s="157"/>
+      <c r="U7" s="157"/>
+      <c r="V7" s="157"/>
+      <c r="W7" s="157"/>
+      <c r="X7" s="157"/>
+      <c r="Y7" s="157"/>
+      <c r="Z7" s="157"/>
+      <c r="AA7" s="157"/>
+      <c r="AB7" s="157"/>
+      <c r="AC7" s="157"/>
+      <c r="AD7" s="157"/>
+      <c r="AE7" s="156"/>
+      <c r="AF7" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="AG7" s="137"/>
-      <c r="AH7" s="137"/>
-      <c r="AI7" s="136"/>
+      <c r="AG7" s="157"/>
+      <c r="AH7" s="157"/>
+      <c r="AI7" s="156"/>
     </row>
     <row r="8" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="15"/>
-      <c r="B8" s="138"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="145"/>
-      <c r="K8" s="146"/>
-      <c r="L8" s="146"/>
-      <c r="M8" s="146"/>
-      <c r="N8" s="146"/>
-      <c r="O8" s="146"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="148"/>
-      <c r="R8" s="149"/>
-      <c r="S8" s="149"/>
-      <c r="T8" s="149"/>
-      <c r="U8" s="149"/>
-      <c r="V8" s="149"/>
-      <c r="W8" s="149"/>
-      <c r="X8" s="149"/>
-      <c r="Y8" s="149"/>
-      <c r="Z8" s="149"/>
-      <c r="AA8" s="149"/>
-      <c r="AB8" s="149"/>
-      <c r="AC8" s="149"/>
-      <c r="AD8" s="149"/>
-      <c r="AE8" s="150"/>
-      <c r="AF8" s="145"/>
-      <c r="AG8" s="146"/>
-      <c r="AH8" s="146"/>
-      <c r="AI8" s="147"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="161"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="164"/>
+      <c r="I8" s="159"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="166"/>
+      <c r="L8" s="166"/>
+      <c r="M8" s="166"/>
+      <c r="N8" s="166"/>
+      <c r="O8" s="166"/>
+      <c r="P8" s="167"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="169"/>
+      <c r="S8" s="169"/>
+      <c r="T8" s="169"/>
+      <c r="U8" s="169"/>
+      <c r="V8" s="169"/>
+      <c r="W8" s="169"/>
+      <c r="X8" s="169"/>
+      <c r="Y8" s="169"/>
+      <c r="Z8" s="169"/>
+      <c r="AA8" s="169"/>
+      <c r="AB8" s="169"/>
+      <c r="AC8" s="169"/>
+      <c r="AD8" s="169"/>
+      <c r="AE8" s="170"/>
+      <c r="AF8" s="165"/>
+      <c r="AG8" s="166"/>
+      <c r="AH8" s="166"/>
+      <c r="AI8" s="167"/>
     </row>
     <row r="9" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="14"/>
-      <c r="B9" s="122"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="124"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="123"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="129"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="129"/>
-      <c r="O9" s="129"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="132"/>
-      <c r="S9" s="132"/>
-      <c r="T9" s="132"/>
-      <c r="U9" s="132"/>
-      <c r="V9" s="132"/>
-      <c r="W9" s="132"/>
-      <c r="X9" s="132"/>
-      <c r="Y9" s="132"/>
-      <c r="Z9" s="132"/>
-      <c r="AA9" s="132"/>
-      <c r="AB9" s="132"/>
-      <c r="AC9" s="132"/>
-      <c r="AD9" s="132"/>
-      <c r="AE9" s="133"/>
-      <c r="AF9" s="128"/>
-      <c r="AG9" s="129"/>
-      <c r="AH9" s="129"/>
-      <c r="AI9" s="130"/>
+      <c r="B9" s="171"/>
+      <c r="C9" s="172"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="174"/>
+      <c r="F9" s="175"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="177"/>
+      <c r="K9" s="178"/>
+      <c r="L9" s="178"/>
+      <c r="M9" s="178"/>
+      <c r="N9" s="178"/>
+      <c r="O9" s="178"/>
+      <c r="P9" s="179"/>
+      <c r="Q9" s="180"/>
+      <c r="R9" s="181"/>
+      <c r="S9" s="181"/>
+      <c r="T9" s="181"/>
+      <c r="U9" s="181"/>
+      <c r="V9" s="181"/>
+      <c r="W9" s="181"/>
+      <c r="X9" s="181"/>
+      <c r="Y9" s="181"/>
+      <c r="Z9" s="181"/>
+      <c r="AA9" s="181"/>
+      <c r="AB9" s="181"/>
+      <c r="AC9" s="181"/>
+      <c r="AD9" s="181"/>
+      <c r="AE9" s="182"/>
+      <c r="AF9" s="177"/>
+      <c r="AG9" s="178"/>
+      <c r="AH9" s="178"/>
+      <c r="AI9" s="179"/>
     </row>
     <row r="10" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="14"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="123"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="129"/>
-      <c r="L10" s="129"/>
-      <c r="M10" s="129"/>
-      <c r="N10" s="129"/>
-      <c r="O10" s="129"/>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="132"/>
-      <c r="S10" s="132"/>
-      <c r="T10" s="132"/>
-      <c r="U10" s="132"/>
-      <c r="V10" s="132"/>
-      <c r="W10" s="132"/>
-      <c r="X10" s="132"/>
-      <c r="Y10" s="132"/>
-      <c r="Z10" s="132"/>
-      <c r="AA10" s="132"/>
-      <c r="AB10" s="132"/>
-      <c r="AC10" s="132"/>
-      <c r="AD10" s="132"/>
-      <c r="AE10" s="133"/>
-      <c r="AF10" s="128"/>
-      <c r="AG10" s="129"/>
-      <c r="AH10" s="129"/>
-      <c r="AI10" s="130"/>
+      <c r="B10" s="171"/>
+      <c r="C10" s="172"/>
+      <c r="D10" s="173"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="175"/>
+      <c r="G10" s="171"/>
+      <c r="H10" s="176"/>
+      <c r="I10" s="172"/>
+      <c r="J10" s="177"/>
+      <c r="K10" s="178"/>
+      <c r="L10" s="178"/>
+      <c r="M10" s="178"/>
+      <c r="N10" s="178"/>
+      <c r="O10" s="178"/>
+      <c r="P10" s="179"/>
+      <c r="Q10" s="180"/>
+      <c r="R10" s="181"/>
+      <c r="S10" s="181"/>
+      <c r="T10" s="181"/>
+      <c r="U10" s="181"/>
+      <c r="V10" s="181"/>
+      <c r="W10" s="181"/>
+      <c r="X10" s="181"/>
+      <c r="Y10" s="181"/>
+      <c r="Z10" s="181"/>
+      <c r="AA10" s="181"/>
+      <c r="AB10" s="181"/>
+      <c r="AC10" s="181"/>
+      <c r="AD10" s="181"/>
+      <c r="AE10" s="182"/>
+      <c r="AF10" s="177"/>
+      <c r="AG10" s="178"/>
+      <c r="AH10" s="178"/>
+      <c r="AI10" s="179"/>
     </row>
     <row r="11" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="14"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="129"/>
-      <c r="N11" s="129"/>
-      <c r="O11" s="129"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="131"/>
-      <c r="R11" s="132"/>
-      <c r="S11" s="132"/>
-      <c r="T11" s="132"/>
-      <c r="U11" s="132"/>
-      <c r="V11" s="132"/>
-      <c r="W11" s="132"/>
-      <c r="X11" s="132"/>
-      <c r="Y11" s="132"/>
-      <c r="Z11" s="132"/>
-      <c r="AA11" s="132"/>
-      <c r="AB11" s="132"/>
-      <c r="AC11" s="132"/>
-      <c r="AD11" s="132"/>
-      <c r="AE11" s="133"/>
-      <c r="AF11" s="128"/>
-      <c r="AG11" s="129"/>
-      <c r="AH11" s="129"/>
-      <c r="AI11" s="130"/>
+      <c r="B11" s="171"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="171"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="172"/>
+      <c r="J11" s="177"/>
+      <c r="K11" s="178"/>
+      <c r="L11" s="178"/>
+      <c r="M11" s="178"/>
+      <c r="N11" s="178"/>
+      <c r="O11" s="178"/>
+      <c r="P11" s="179"/>
+      <c r="Q11" s="180"/>
+      <c r="R11" s="181"/>
+      <c r="S11" s="181"/>
+      <c r="T11" s="181"/>
+      <c r="U11" s="181"/>
+      <c r="V11" s="181"/>
+      <c r="W11" s="181"/>
+      <c r="X11" s="181"/>
+      <c r="Y11" s="181"/>
+      <c r="Z11" s="181"/>
+      <c r="AA11" s="181"/>
+      <c r="AB11" s="181"/>
+      <c r="AC11" s="181"/>
+      <c r="AD11" s="181"/>
+      <c r="AE11" s="182"/>
+      <c r="AF11" s="177"/>
+      <c r="AG11" s="178"/>
+      <c r="AH11" s="178"/>
+      <c r="AI11" s="179"/>
     </row>
     <row r="12" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="14"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="123"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-      <c r="M12" s="129"/>
-      <c r="N12" s="129"/>
-      <c r="O12" s="129"/>
-      <c r="P12" s="130"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="132"/>
-      <c r="S12" s="132"/>
-      <c r="T12" s="132"/>
-      <c r="U12" s="132"/>
-      <c r="V12" s="132"/>
-      <c r="W12" s="132"/>
-      <c r="X12" s="132"/>
-      <c r="Y12" s="132"/>
-      <c r="Z12" s="132"/>
-      <c r="AA12" s="132"/>
-      <c r="AB12" s="132"/>
-      <c r="AC12" s="132"/>
-      <c r="AD12" s="132"/>
-      <c r="AE12" s="133"/>
-      <c r="AF12" s="128"/>
-      <c r="AG12" s="129"/>
-      <c r="AH12" s="129"/>
-      <c r="AI12" s="130"/>
+      <c r="B12" s="171"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="175"/>
+      <c r="G12" s="171"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="172"/>
+      <c r="J12" s="177"/>
+      <c r="K12" s="178"/>
+      <c r="L12" s="178"/>
+      <c r="M12" s="178"/>
+      <c r="N12" s="178"/>
+      <c r="O12" s="178"/>
+      <c r="P12" s="179"/>
+      <c r="Q12" s="180"/>
+      <c r="R12" s="181"/>
+      <c r="S12" s="181"/>
+      <c r="T12" s="181"/>
+      <c r="U12" s="181"/>
+      <c r="V12" s="181"/>
+      <c r="W12" s="181"/>
+      <c r="X12" s="181"/>
+      <c r="Y12" s="181"/>
+      <c r="Z12" s="181"/>
+      <c r="AA12" s="181"/>
+      <c r="AB12" s="181"/>
+      <c r="AC12" s="181"/>
+      <c r="AD12" s="181"/>
+      <c r="AE12" s="182"/>
+      <c r="AF12" s="177"/>
+      <c r="AG12" s="178"/>
+      <c r="AH12" s="178"/>
+      <c r="AI12" s="179"/>
     </row>
     <row r="13" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="14"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="129"/>
-      <c r="L13" s="129"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="129"/>
-      <c r="O13" s="129"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="132"/>
-      <c r="T13" s="132"/>
-      <c r="U13" s="132"/>
-      <c r="V13" s="132"/>
-      <c r="W13" s="132"/>
-      <c r="X13" s="132"/>
-      <c r="Y13" s="132"/>
-      <c r="Z13" s="132"/>
-      <c r="AA13" s="132"/>
-      <c r="AB13" s="132"/>
-      <c r="AC13" s="132"/>
-      <c r="AD13" s="132"/>
-      <c r="AE13" s="133"/>
-      <c r="AF13" s="128"/>
-      <c r="AG13" s="129"/>
-      <c r="AH13" s="129"/>
-      <c r="AI13" s="130"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="172"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="171"/>
+      <c r="H13" s="176"/>
+      <c r="I13" s="172"/>
+      <c r="J13" s="177"/>
+      <c r="K13" s="178"/>
+      <c r="L13" s="178"/>
+      <c r="M13" s="178"/>
+      <c r="N13" s="178"/>
+      <c r="O13" s="178"/>
+      <c r="P13" s="179"/>
+      <c r="Q13" s="180"/>
+      <c r="R13" s="181"/>
+      <c r="S13" s="181"/>
+      <c r="T13" s="181"/>
+      <c r="U13" s="181"/>
+      <c r="V13" s="181"/>
+      <c r="W13" s="181"/>
+      <c r="X13" s="181"/>
+      <c r="Y13" s="181"/>
+      <c r="Z13" s="181"/>
+      <c r="AA13" s="181"/>
+      <c r="AB13" s="181"/>
+      <c r="AC13" s="181"/>
+      <c r="AD13" s="181"/>
+      <c r="AE13" s="182"/>
+      <c r="AF13" s="177"/>
+      <c r="AG13" s="178"/>
+      <c r="AH13" s="178"/>
+      <c r="AI13" s="179"/>
     </row>
     <row r="14" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="14"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="123"/>
-      <c r="J14" s="128"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
-      <c r="N14" s="129"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="130"/>
-      <c r="Q14" s="131"/>
-      <c r="R14" s="132"/>
-      <c r="S14" s="132"/>
-      <c r="T14" s="132"/>
-      <c r="U14" s="132"/>
-      <c r="V14" s="132"/>
-      <c r="W14" s="132"/>
-      <c r="X14" s="132"/>
-      <c r="Y14" s="132"/>
-      <c r="Z14" s="132"/>
-      <c r="AA14" s="132"/>
-      <c r="AB14" s="132"/>
-      <c r="AC14" s="132"/>
-      <c r="AD14" s="132"/>
-      <c r="AE14" s="133"/>
-      <c r="AF14" s="128"/>
-      <c r="AG14" s="129"/>
-      <c r="AH14" s="129"/>
-      <c r="AI14" s="130"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="172"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="174"/>
+      <c r="F14" s="175"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="176"/>
+      <c r="I14" s="172"/>
+      <c r="J14" s="177"/>
+      <c r="K14" s="178"/>
+      <c r="L14" s="178"/>
+      <c r="M14" s="178"/>
+      <c r="N14" s="178"/>
+      <c r="O14" s="178"/>
+      <c r="P14" s="179"/>
+      <c r="Q14" s="180"/>
+      <c r="R14" s="181"/>
+      <c r="S14" s="181"/>
+      <c r="T14" s="181"/>
+      <c r="U14" s="181"/>
+      <c r="V14" s="181"/>
+      <c r="W14" s="181"/>
+      <c r="X14" s="181"/>
+      <c r="Y14" s="181"/>
+      <c r="Z14" s="181"/>
+      <c r="AA14" s="181"/>
+      <c r="AB14" s="181"/>
+      <c r="AC14" s="181"/>
+      <c r="AD14" s="181"/>
+      <c r="AE14" s="182"/>
+      <c r="AF14" s="177"/>
+      <c r="AG14" s="178"/>
+      <c r="AH14" s="178"/>
+      <c r="AI14" s="179"/>
     </row>
     <row r="15" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="129"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="129"/>
-      <c r="O15" s="129"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="131"/>
-      <c r="R15" s="132"/>
-      <c r="S15" s="132"/>
-      <c r="T15" s="132"/>
-      <c r="U15" s="132"/>
-      <c r="V15" s="132"/>
-      <c r="W15" s="132"/>
-      <c r="X15" s="132"/>
-      <c r="Y15" s="132"/>
-      <c r="Z15" s="132"/>
-      <c r="AA15" s="132"/>
-      <c r="AB15" s="132"/>
-      <c r="AC15" s="132"/>
-      <c r="AD15" s="132"/>
-      <c r="AE15" s="133"/>
-      <c r="AF15" s="128"/>
-      <c r="AG15" s="129"/>
-      <c r="AH15" s="129"/>
-      <c r="AI15" s="130"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="174"/>
+      <c r="F15" s="175"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="176"/>
+      <c r="I15" s="172"/>
+      <c r="J15" s="177"/>
+      <c r="K15" s="178"/>
+      <c r="L15" s="178"/>
+      <c r="M15" s="178"/>
+      <c r="N15" s="178"/>
+      <c r="O15" s="178"/>
+      <c r="P15" s="179"/>
+      <c r="Q15" s="180"/>
+      <c r="R15" s="181"/>
+      <c r="S15" s="181"/>
+      <c r="T15" s="181"/>
+      <c r="U15" s="181"/>
+      <c r="V15" s="181"/>
+      <c r="W15" s="181"/>
+      <c r="X15" s="181"/>
+      <c r="Y15" s="181"/>
+      <c r="Z15" s="181"/>
+      <c r="AA15" s="181"/>
+      <c r="AB15" s="181"/>
+      <c r="AC15" s="181"/>
+      <c r="AD15" s="181"/>
+      <c r="AE15" s="182"/>
+      <c r="AF15" s="177"/>
+      <c r="AG15" s="178"/>
+      <c r="AH15" s="178"/>
+      <c r="AI15" s="179"/>
     </row>
     <row r="16" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="14"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="123"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="128"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
-      <c r="M16" s="129"/>
-      <c r="N16" s="129"/>
-      <c r="O16" s="129"/>
-      <c r="P16" s="130"/>
-      <c r="Q16" s="131"/>
-      <c r="R16" s="132"/>
-      <c r="S16" s="132"/>
-      <c r="T16" s="132"/>
-      <c r="U16" s="132"/>
-      <c r="V16" s="132"/>
-      <c r="W16" s="132"/>
-      <c r="X16" s="132"/>
-      <c r="Y16" s="132"/>
-      <c r="Z16" s="132"/>
-      <c r="AA16" s="132"/>
-      <c r="AB16" s="132"/>
-      <c r="AC16" s="132"/>
-      <c r="AD16" s="132"/>
-      <c r="AE16" s="133"/>
-      <c r="AF16" s="128"/>
-      <c r="AG16" s="129"/>
-      <c r="AH16" s="129"/>
-      <c r="AI16" s="130"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="173"/>
+      <c r="E16" s="174"/>
+      <c r="F16" s="175"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="176"/>
+      <c r="I16" s="172"/>
+      <c r="J16" s="177"/>
+      <c r="K16" s="178"/>
+      <c r="L16" s="178"/>
+      <c r="M16" s="178"/>
+      <c r="N16" s="178"/>
+      <c r="O16" s="178"/>
+      <c r="P16" s="179"/>
+      <c r="Q16" s="180"/>
+      <c r="R16" s="181"/>
+      <c r="S16" s="181"/>
+      <c r="T16" s="181"/>
+      <c r="U16" s="181"/>
+      <c r="V16" s="181"/>
+      <c r="W16" s="181"/>
+      <c r="X16" s="181"/>
+      <c r="Y16" s="181"/>
+      <c r="Z16" s="181"/>
+      <c r="AA16" s="181"/>
+      <c r="AB16" s="181"/>
+      <c r="AC16" s="181"/>
+      <c r="AD16" s="181"/>
+      <c r="AE16" s="182"/>
+      <c r="AF16" s="177"/>
+      <c r="AG16" s="178"/>
+      <c r="AH16" s="178"/>
+      <c r="AI16" s="179"/>
     </row>
     <row r="17" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="14"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="123"/>
-      <c r="J17" s="128"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="129"/>
-      <c r="N17" s="129"/>
-      <c r="O17" s="129"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="131"/>
-      <c r="R17" s="132"/>
-      <c r="S17" s="132"/>
-      <c r="T17" s="132"/>
-      <c r="U17" s="132"/>
-      <c r="V17" s="132"/>
-      <c r="W17" s="132"/>
-      <c r="X17" s="132"/>
-      <c r="Y17" s="132"/>
-      <c r="Z17" s="132"/>
-      <c r="AA17" s="132"/>
-      <c r="AB17" s="132"/>
-      <c r="AC17" s="132"/>
-      <c r="AD17" s="132"/>
-      <c r="AE17" s="133"/>
-      <c r="AF17" s="128"/>
-      <c r="AG17" s="129"/>
-      <c r="AH17" s="129"/>
-      <c r="AI17" s="130"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="173"/>
+      <c r="E17" s="174"/>
+      <c r="F17" s="175"/>
+      <c r="G17" s="171"/>
+      <c r="H17" s="176"/>
+      <c r="I17" s="172"/>
+      <c r="J17" s="177"/>
+      <c r="K17" s="178"/>
+      <c r="L17" s="178"/>
+      <c r="M17" s="178"/>
+      <c r="N17" s="178"/>
+      <c r="O17" s="178"/>
+      <c r="P17" s="179"/>
+      <c r="Q17" s="180"/>
+      <c r="R17" s="181"/>
+      <c r="S17" s="181"/>
+      <c r="T17" s="181"/>
+      <c r="U17" s="181"/>
+      <c r="V17" s="181"/>
+      <c r="W17" s="181"/>
+      <c r="X17" s="181"/>
+      <c r="Y17" s="181"/>
+      <c r="Z17" s="181"/>
+      <c r="AA17" s="181"/>
+      <c r="AB17" s="181"/>
+      <c r="AC17" s="181"/>
+      <c r="AD17" s="181"/>
+      <c r="AE17" s="182"/>
+      <c r="AF17" s="177"/>
+      <c r="AG17" s="178"/>
+      <c r="AH17" s="178"/>
+      <c r="AI17" s="179"/>
     </row>
     <row r="18" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="14"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="123"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="129"/>
-      <c r="L18" s="129"/>
-      <c r="M18" s="129"/>
-      <c r="N18" s="129"/>
-      <c r="O18" s="129"/>
-      <c r="P18" s="130"/>
-      <c r="Q18" s="131"/>
-      <c r="R18" s="132"/>
-      <c r="S18" s="132"/>
-      <c r="T18" s="132"/>
-      <c r="U18" s="132"/>
-      <c r="V18" s="132"/>
-      <c r="W18" s="132"/>
-      <c r="X18" s="132"/>
-      <c r="Y18" s="132"/>
-      <c r="Z18" s="132"/>
-      <c r="AA18" s="132"/>
-      <c r="AB18" s="132"/>
-      <c r="AC18" s="132"/>
-      <c r="AD18" s="132"/>
-      <c r="AE18" s="133"/>
-      <c r="AF18" s="128"/>
-      <c r="AG18" s="129"/>
-      <c r="AH18" s="129"/>
-      <c r="AI18" s="130"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="172"/>
+      <c r="D18" s="173"/>
+      <c r="E18" s="174"/>
+      <c r="F18" s="175"/>
+      <c r="G18" s="171"/>
+      <c r="H18" s="176"/>
+      <c r="I18" s="172"/>
+      <c r="J18" s="177"/>
+      <c r="K18" s="178"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="178"/>
+      <c r="N18" s="178"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="179"/>
+      <c r="Q18" s="180"/>
+      <c r="R18" s="181"/>
+      <c r="S18" s="181"/>
+      <c r="T18" s="181"/>
+      <c r="U18" s="181"/>
+      <c r="V18" s="181"/>
+      <c r="W18" s="181"/>
+      <c r="X18" s="181"/>
+      <c r="Y18" s="181"/>
+      <c r="Z18" s="181"/>
+      <c r="AA18" s="181"/>
+      <c r="AB18" s="181"/>
+      <c r="AC18" s="181"/>
+      <c r="AD18" s="181"/>
+      <c r="AE18" s="182"/>
+      <c r="AF18" s="177"/>
+      <c r="AG18" s="178"/>
+      <c r="AH18" s="178"/>
+      <c r="AI18" s="179"/>
     </row>
     <row r="19" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="14"/>
-      <c r="B19" s="122"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="124"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="122"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="123"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="129"/>
-      <c r="L19" s="129"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="129"/>
-      <c r="O19" s="129"/>
-      <c r="P19" s="130"/>
-      <c r="Q19" s="131"/>
-      <c r="R19" s="132"/>
-      <c r="S19" s="132"/>
-      <c r="T19" s="132"/>
-      <c r="U19" s="132"/>
-      <c r="V19" s="132"/>
-      <c r="W19" s="132"/>
-      <c r="X19" s="132"/>
-      <c r="Y19" s="132"/>
-      <c r="Z19" s="132"/>
-      <c r="AA19" s="132"/>
-      <c r="AB19" s="132"/>
-      <c r="AC19" s="132"/>
-      <c r="AD19" s="132"/>
-      <c r="AE19" s="133"/>
-      <c r="AF19" s="128"/>
-      <c r="AG19" s="129"/>
-      <c r="AH19" s="129"/>
-      <c r="AI19" s="130"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="174"/>
+      <c r="F19" s="175"/>
+      <c r="G19" s="171"/>
+      <c r="H19" s="176"/>
+      <c r="I19" s="172"/>
+      <c r="J19" s="177"/>
+      <c r="K19" s="178"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="178"/>
+      <c r="N19" s="178"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="180"/>
+      <c r="R19" s="181"/>
+      <c r="S19" s="181"/>
+      <c r="T19" s="181"/>
+      <c r="U19" s="181"/>
+      <c r="V19" s="181"/>
+      <c r="W19" s="181"/>
+      <c r="X19" s="181"/>
+      <c r="Y19" s="181"/>
+      <c r="Z19" s="181"/>
+      <c r="AA19" s="181"/>
+      <c r="AB19" s="181"/>
+      <c r="AC19" s="181"/>
+      <c r="AD19" s="181"/>
+      <c r="AE19" s="182"/>
+      <c r="AF19" s="177"/>
+      <c r="AG19" s="178"/>
+      <c r="AH19" s="178"/>
+      <c r="AI19" s="179"/>
     </row>
     <row r="20" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="14"/>
-      <c r="B20" s="122"/>
-      <c r="C20" s="123"/>
-      <c r="D20" s="124"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="129"/>
-      <c r="L20" s="129"/>
-      <c r="M20" s="129"/>
-      <c r="N20" s="129"/>
-      <c r="O20" s="129"/>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="131"/>
-      <c r="R20" s="132"/>
-      <c r="S20" s="132"/>
-      <c r="T20" s="132"/>
-      <c r="U20" s="132"/>
-      <c r="V20" s="132"/>
-      <c r="W20" s="132"/>
-      <c r="X20" s="132"/>
-      <c r="Y20" s="132"/>
-      <c r="Z20" s="132"/>
-      <c r="AA20" s="132"/>
-      <c r="AB20" s="132"/>
-      <c r="AC20" s="132"/>
-      <c r="AD20" s="132"/>
-      <c r="AE20" s="133"/>
-      <c r="AF20" s="128"/>
-      <c r="AG20" s="129"/>
-      <c r="AH20" s="129"/>
-      <c r="AI20" s="130"/>
+      <c r="B20" s="171"/>
+      <c r="C20" s="172"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="174"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="171"/>
+      <c r="H20" s="176"/>
+      <c r="I20" s="172"/>
+      <c r="J20" s="177"/>
+      <c r="K20" s="178"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="178"/>
+      <c r="N20" s="178"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="179"/>
+      <c r="Q20" s="180"/>
+      <c r="R20" s="181"/>
+      <c r="S20" s="181"/>
+      <c r="T20" s="181"/>
+      <c r="U20" s="181"/>
+      <c r="V20" s="181"/>
+      <c r="W20" s="181"/>
+      <c r="X20" s="181"/>
+      <c r="Y20" s="181"/>
+      <c r="Z20" s="181"/>
+      <c r="AA20" s="181"/>
+      <c r="AB20" s="181"/>
+      <c r="AC20" s="181"/>
+      <c r="AD20" s="181"/>
+      <c r="AE20" s="182"/>
+      <c r="AF20" s="177"/>
+      <c r="AG20" s="178"/>
+      <c r="AH20" s="178"/>
+      <c r="AI20" s="179"/>
     </row>
     <row r="21" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="14"/>
-      <c r="B21" s="122"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="124"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="123"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="129"/>
-      <c r="L21" s="129"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="129"/>
-      <c r="O21" s="129"/>
-      <c r="P21" s="130"/>
-      <c r="Q21" s="131"/>
-      <c r="R21" s="132"/>
-      <c r="S21" s="132"/>
-      <c r="T21" s="132"/>
-      <c r="U21" s="132"/>
-      <c r="V21" s="132"/>
-      <c r="W21" s="132"/>
-      <c r="X21" s="132"/>
-      <c r="Y21" s="132"/>
-      <c r="Z21" s="132"/>
-      <c r="AA21" s="132"/>
-      <c r="AB21" s="132"/>
-      <c r="AC21" s="132"/>
-      <c r="AD21" s="132"/>
-      <c r="AE21" s="133"/>
-      <c r="AF21" s="128"/>
-      <c r="AG21" s="129"/>
-      <c r="AH21" s="129"/>
-      <c r="AI21" s="130"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="172"/>
+      <c r="D21" s="173"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="175"/>
+      <c r="G21" s="171"/>
+      <c r="H21" s="176"/>
+      <c r="I21" s="172"/>
+      <c r="J21" s="177"/>
+      <c r="K21" s="178"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="178"/>
+      <c r="N21" s="178"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="179"/>
+      <c r="Q21" s="180"/>
+      <c r="R21" s="181"/>
+      <c r="S21" s="181"/>
+      <c r="T21" s="181"/>
+      <c r="U21" s="181"/>
+      <c r="V21" s="181"/>
+      <c r="W21" s="181"/>
+      <c r="X21" s="181"/>
+      <c r="Y21" s="181"/>
+      <c r="Z21" s="181"/>
+      <c r="AA21" s="181"/>
+      <c r="AB21" s="181"/>
+      <c r="AC21" s="181"/>
+      <c r="AD21" s="181"/>
+      <c r="AE21" s="182"/>
+      <c r="AF21" s="177"/>
+      <c r="AG21" s="178"/>
+      <c r="AH21" s="178"/>
+      <c r="AI21" s="179"/>
     </row>
     <row r="22" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="14"/>
-      <c r="B22" s="122"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="128"/>
-      <c r="K22" s="129"/>
-      <c r="L22" s="129"/>
-      <c r="M22" s="129"/>
-      <c r="N22" s="129"/>
-      <c r="O22" s="129"/>
-      <c r="P22" s="130"/>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="132"/>
-      <c r="S22" s="132"/>
-      <c r="T22" s="132"/>
-      <c r="U22" s="132"/>
-      <c r="V22" s="132"/>
-      <c r="W22" s="132"/>
-      <c r="X22" s="132"/>
-      <c r="Y22" s="132"/>
-      <c r="Z22" s="132"/>
-      <c r="AA22" s="132"/>
-      <c r="AB22" s="132"/>
-      <c r="AC22" s="132"/>
-      <c r="AD22" s="132"/>
-      <c r="AE22" s="133"/>
-      <c r="AF22" s="128"/>
-      <c r="AG22" s="129"/>
-      <c r="AH22" s="129"/>
-      <c r="AI22" s="130"/>
+      <c r="B22" s="171"/>
+      <c r="C22" s="172"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="174"/>
+      <c r="F22" s="175"/>
+      <c r="G22" s="171"/>
+      <c r="H22" s="176"/>
+      <c r="I22" s="172"/>
+      <c r="J22" s="177"/>
+      <c r="K22" s="178"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="178"/>
+      <c r="N22" s="178"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="179"/>
+      <c r="Q22" s="180"/>
+      <c r="R22" s="181"/>
+      <c r="S22" s="181"/>
+      <c r="T22" s="181"/>
+      <c r="U22" s="181"/>
+      <c r="V22" s="181"/>
+      <c r="W22" s="181"/>
+      <c r="X22" s="181"/>
+      <c r="Y22" s="181"/>
+      <c r="Z22" s="181"/>
+      <c r="AA22" s="181"/>
+      <c r="AB22" s="181"/>
+      <c r="AC22" s="181"/>
+      <c r="AD22" s="181"/>
+      <c r="AE22" s="182"/>
+      <c r="AF22" s="177"/>
+      <c r="AG22" s="178"/>
+      <c r="AH22" s="178"/>
+      <c r="AI22" s="179"/>
     </row>
     <row r="23" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="14"/>
-      <c r="B23" s="122"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="122"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="129"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="130"/>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="132"/>
-      <c r="S23" s="132"/>
-      <c r="T23" s="132"/>
-      <c r="U23" s="132"/>
-      <c r="V23" s="132"/>
-      <c r="W23" s="132"/>
-      <c r="X23" s="132"/>
-      <c r="Y23" s="132"/>
-      <c r="Z23" s="132"/>
-      <c r="AA23" s="132"/>
-      <c r="AB23" s="132"/>
-      <c r="AC23" s="132"/>
-      <c r="AD23" s="132"/>
-      <c r="AE23" s="133"/>
-      <c r="AF23" s="128"/>
-      <c r="AG23" s="129"/>
-      <c r="AH23" s="129"/>
-      <c r="AI23" s="130"/>
+      <c r="B23" s="171"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="174"/>
+      <c r="F23" s="175"/>
+      <c r="G23" s="171"/>
+      <c r="H23" s="176"/>
+      <c r="I23" s="172"/>
+      <c r="J23" s="177"/>
+      <c r="K23" s="178"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="178"/>
+      <c r="N23" s="178"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="179"/>
+      <c r="Q23" s="180"/>
+      <c r="R23" s="181"/>
+      <c r="S23" s="181"/>
+      <c r="T23" s="181"/>
+      <c r="U23" s="181"/>
+      <c r="V23" s="181"/>
+      <c r="W23" s="181"/>
+      <c r="X23" s="181"/>
+      <c r="Y23" s="181"/>
+      <c r="Z23" s="181"/>
+      <c r="AA23" s="181"/>
+      <c r="AB23" s="181"/>
+      <c r="AC23" s="181"/>
+      <c r="AD23" s="181"/>
+      <c r="AE23" s="182"/>
+      <c r="AF23" s="177"/>
+      <c r="AG23" s="178"/>
+      <c r="AH23" s="178"/>
+      <c r="AI23" s="179"/>
     </row>
     <row r="24" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="14"/>
-      <c r="B24" s="122"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="123"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="129"/>
-      <c r="L24" s="129"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="129"/>
-      <c r="O24" s="129"/>
-      <c r="P24" s="130"/>
-      <c r="Q24" s="131"/>
-      <c r="R24" s="132"/>
-      <c r="S24" s="132"/>
-      <c r="T24" s="132"/>
-      <c r="U24" s="132"/>
-      <c r="V24" s="132"/>
-      <c r="W24" s="132"/>
-      <c r="X24" s="132"/>
-      <c r="Y24" s="132"/>
-      <c r="Z24" s="132"/>
-      <c r="AA24" s="132"/>
-      <c r="AB24" s="132"/>
-      <c r="AC24" s="132"/>
-      <c r="AD24" s="132"/>
-      <c r="AE24" s="133"/>
-      <c r="AF24" s="128"/>
-      <c r="AG24" s="129"/>
-      <c r="AH24" s="129"/>
-      <c r="AI24" s="130"/>
+      <c r="B24" s="171"/>
+      <c r="C24" s="172"/>
+      <c r="D24" s="173"/>
+      <c r="E24" s="174"/>
+      <c r="F24" s="175"/>
+      <c r="G24" s="171"/>
+      <c r="H24" s="176"/>
+      <c r="I24" s="172"/>
+      <c r="J24" s="177"/>
+      <c r="K24" s="178"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="178"/>
+      <c r="N24" s="178"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="179"/>
+      <c r="Q24" s="180"/>
+      <c r="R24" s="181"/>
+      <c r="S24" s="181"/>
+      <c r="T24" s="181"/>
+      <c r="U24" s="181"/>
+      <c r="V24" s="181"/>
+      <c r="W24" s="181"/>
+      <c r="X24" s="181"/>
+      <c r="Y24" s="181"/>
+      <c r="Z24" s="181"/>
+      <c r="AA24" s="181"/>
+      <c r="AB24" s="181"/>
+      <c r="AC24" s="181"/>
+      <c r="AD24" s="181"/>
+      <c r="AE24" s="182"/>
+      <c r="AF24" s="177"/>
+      <c r="AG24" s="178"/>
+      <c r="AH24" s="178"/>
+      <c r="AI24" s="179"/>
     </row>
     <row r="25" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="14"/>
-      <c r="B25" s="122"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="122"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="128"/>
-      <c r="K25" s="129"/>
-      <c r="L25" s="129"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="129"/>
-      <c r="O25" s="129"/>
-      <c r="P25" s="130"/>
-      <c r="Q25" s="131"/>
-      <c r="R25" s="132"/>
-      <c r="S25" s="132"/>
-      <c r="T25" s="132"/>
-      <c r="U25" s="132"/>
-      <c r="V25" s="132"/>
-      <c r="W25" s="132"/>
-      <c r="X25" s="132"/>
-      <c r="Y25" s="132"/>
-      <c r="Z25" s="132"/>
-      <c r="AA25" s="132"/>
-      <c r="AB25" s="132"/>
-      <c r="AC25" s="132"/>
-      <c r="AD25" s="132"/>
-      <c r="AE25" s="133"/>
-      <c r="AF25" s="128"/>
-      <c r="AG25" s="129"/>
-      <c r="AH25" s="129"/>
-      <c r="AI25" s="130"/>
+      <c r="B25" s="171"/>
+      <c r="C25" s="172"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="174"/>
+      <c r="F25" s="175"/>
+      <c r="G25" s="171"/>
+      <c r="H25" s="176"/>
+      <c r="I25" s="172"/>
+      <c r="J25" s="177"/>
+      <c r="K25" s="178"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="178"/>
+      <c r="N25" s="178"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="179"/>
+      <c r="Q25" s="180"/>
+      <c r="R25" s="181"/>
+      <c r="S25" s="181"/>
+      <c r="T25" s="181"/>
+      <c r="U25" s="181"/>
+      <c r="V25" s="181"/>
+      <c r="W25" s="181"/>
+      <c r="X25" s="181"/>
+      <c r="Y25" s="181"/>
+      <c r="Z25" s="181"/>
+      <c r="AA25" s="181"/>
+      <c r="AB25" s="181"/>
+      <c r="AC25" s="181"/>
+      <c r="AD25" s="181"/>
+      <c r="AE25" s="182"/>
+      <c r="AF25" s="177"/>
+      <c r="AG25" s="178"/>
+      <c r="AH25" s="178"/>
+      <c r="AI25" s="179"/>
     </row>
     <row r="26" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="14"/>
-      <c r="B26" s="122"/>
-      <c r="C26" s="123"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="122"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="128"/>
-      <c r="K26" s="129"/>
-      <c r="L26" s="129"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="129"/>
-      <c r="P26" s="130"/>
-      <c r="Q26" s="131"/>
-      <c r="R26" s="132"/>
-      <c r="S26" s="132"/>
-      <c r="T26" s="132"/>
-      <c r="U26" s="132"/>
-      <c r="V26" s="132"/>
-      <c r="W26" s="132"/>
-      <c r="X26" s="132"/>
-      <c r="Y26" s="132"/>
-      <c r="Z26" s="132"/>
-      <c r="AA26" s="132"/>
-      <c r="AB26" s="132"/>
-      <c r="AC26" s="132"/>
-      <c r="AD26" s="132"/>
-      <c r="AE26" s="133"/>
-      <c r="AF26" s="128"/>
-      <c r="AG26" s="129"/>
-      <c r="AH26" s="129"/>
-      <c r="AI26" s="130"/>
+      <c r="B26" s="171"/>
+      <c r="C26" s="172"/>
+      <c r="D26" s="173"/>
+      <c r="E26" s="174"/>
+      <c r="F26" s="175"/>
+      <c r="G26" s="171"/>
+      <c r="H26" s="176"/>
+      <c r="I26" s="172"/>
+      <c r="J26" s="177"/>
+      <c r="K26" s="178"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="178"/>
+      <c r="N26" s="178"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="179"/>
+      <c r="Q26" s="180"/>
+      <c r="R26" s="181"/>
+      <c r="S26" s="181"/>
+      <c r="T26" s="181"/>
+      <c r="U26" s="181"/>
+      <c r="V26" s="181"/>
+      <c r="W26" s="181"/>
+      <c r="X26" s="181"/>
+      <c r="Y26" s="181"/>
+      <c r="Z26" s="181"/>
+      <c r="AA26" s="181"/>
+      <c r="AB26" s="181"/>
+      <c r="AC26" s="181"/>
+      <c r="AD26" s="181"/>
+      <c r="AE26" s="182"/>
+      <c r="AF26" s="177"/>
+      <c r="AG26" s="178"/>
+      <c r="AH26" s="178"/>
+      <c r="AI26" s="179"/>
     </row>
     <row r="27" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="14"/>
-      <c r="B27" s="122"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="123"/>
-      <c r="J27" s="128"/>
-      <c r="K27" s="129"/>
-      <c r="L27" s="129"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="129"/>
-      <c r="O27" s="129"/>
-      <c r="P27" s="130"/>
-      <c r="Q27" s="131"/>
-      <c r="R27" s="132"/>
-      <c r="S27" s="132"/>
-      <c r="T27" s="132"/>
-      <c r="U27" s="132"/>
-      <c r="V27" s="132"/>
-      <c r="W27" s="132"/>
-      <c r="X27" s="132"/>
-      <c r="Y27" s="132"/>
-      <c r="Z27" s="132"/>
-      <c r="AA27" s="132"/>
-      <c r="AB27" s="132"/>
-      <c r="AC27" s="132"/>
-      <c r="AD27" s="132"/>
-      <c r="AE27" s="133"/>
-      <c r="AF27" s="128"/>
-      <c r="AG27" s="129"/>
-      <c r="AH27" s="129"/>
-      <c r="AI27" s="130"/>
+      <c r="B27" s="171"/>
+      <c r="C27" s="172"/>
+      <c r="D27" s="173"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="175"/>
+      <c r="G27" s="171"/>
+      <c r="H27" s="176"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="177"/>
+      <c r="K27" s="178"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="178"/>
+      <c r="N27" s="178"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="180"/>
+      <c r="R27" s="181"/>
+      <c r="S27" s="181"/>
+      <c r="T27" s="181"/>
+      <c r="U27" s="181"/>
+      <c r="V27" s="181"/>
+      <c r="W27" s="181"/>
+      <c r="X27" s="181"/>
+      <c r="Y27" s="181"/>
+      <c r="Z27" s="181"/>
+      <c r="AA27" s="181"/>
+      <c r="AB27" s="181"/>
+      <c r="AC27" s="181"/>
+      <c r="AD27" s="181"/>
+      <c r="AE27" s="182"/>
+      <c r="AF27" s="177"/>
+      <c r="AG27" s="178"/>
+      <c r="AH27" s="178"/>
+      <c r="AI27" s="179"/>
     </row>
     <row r="28" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="14"/>
-      <c r="B28" s="122"/>
-      <c r="C28" s="123"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="122"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="123"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="129"/>
-      <c r="L28" s="129"/>
-      <c r="M28" s="129"/>
-      <c r="N28" s="129"/>
-      <c r="O28" s="129"/>
-      <c r="P28" s="130"/>
-      <c r="Q28" s="131"/>
-      <c r="R28" s="132"/>
-      <c r="S28" s="132"/>
-      <c r="T28" s="132"/>
-      <c r="U28" s="132"/>
-      <c r="V28" s="132"/>
-      <c r="W28" s="132"/>
-      <c r="X28" s="132"/>
-      <c r="Y28" s="132"/>
-      <c r="Z28" s="132"/>
-      <c r="AA28" s="132"/>
-      <c r="AB28" s="132"/>
-      <c r="AC28" s="132"/>
-      <c r="AD28" s="132"/>
-      <c r="AE28" s="133"/>
-      <c r="AF28" s="128"/>
-      <c r="AG28" s="129"/>
-      <c r="AH28" s="129"/>
-      <c r="AI28" s="130"/>
+      <c r="B28" s="171"/>
+      <c r="C28" s="172"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="175"/>
+      <c r="G28" s="171"/>
+      <c r="H28" s="176"/>
+      <c r="I28" s="172"/>
+      <c r="J28" s="177"/>
+      <c r="K28" s="178"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="178"/>
+      <c r="N28" s="178"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="180"/>
+      <c r="R28" s="181"/>
+      <c r="S28" s="181"/>
+      <c r="T28" s="181"/>
+      <c r="U28" s="181"/>
+      <c r="V28" s="181"/>
+      <c r="W28" s="181"/>
+      <c r="X28" s="181"/>
+      <c r="Y28" s="181"/>
+      <c r="Z28" s="181"/>
+      <c r="AA28" s="181"/>
+      <c r="AB28" s="181"/>
+      <c r="AC28" s="181"/>
+      <c r="AD28" s="181"/>
+      <c r="AE28" s="182"/>
+      <c r="AF28" s="177"/>
+      <c r="AG28" s="178"/>
+      <c r="AH28" s="178"/>
+      <c r="AI28" s="179"/>
     </row>
     <row r="29" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="14"/>
-      <c r="B29" s="122"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="124"/>
-      <c r="E29" s="125"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="123"/>
-      <c r="J29" s="128"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="129"/>
-      <c r="M29" s="129"/>
-      <c r="N29" s="129"/>
-      <c r="O29" s="129"/>
-      <c r="P29" s="130"/>
-      <c r="Q29" s="131"/>
-      <c r="R29" s="132"/>
-      <c r="S29" s="132"/>
-      <c r="T29" s="132"/>
-      <c r="U29" s="132"/>
-      <c r="V29" s="132"/>
-      <c r="W29" s="132"/>
-      <c r="X29" s="132"/>
-      <c r="Y29" s="132"/>
-      <c r="Z29" s="132"/>
-      <c r="AA29" s="132"/>
-      <c r="AB29" s="132"/>
-      <c r="AC29" s="132"/>
-      <c r="AD29" s="132"/>
-      <c r="AE29" s="133"/>
-      <c r="AF29" s="128"/>
-      <c r="AG29" s="129"/>
-      <c r="AH29" s="129"/>
-      <c r="AI29" s="130"/>
+      <c r="B29" s="171"/>
+      <c r="C29" s="172"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="175"/>
+      <c r="G29" s="171"/>
+      <c r="H29" s="176"/>
+      <c r="I29" s="172"/>
+      <c r="J29" s="177"/>
+      <c r="K29" s="178"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="178"/>
+      <c r="N29" s="178"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="179"/>
+      <c r="Q29" s="180"/>
+      <c r="R29" s="181"/>
+      <c r="S29" s="181"/>
+      <c r="T29" s="181"/>
+      <c r="U29" s="181"/>
+      <c r="V29" s="181"/>
+      <c r="W29" s="181"/>
+      <c r="X29" s="181"/>
+      <c r="Y29" s="181"/>
+      <c r="Z29" s="181"/>
+      <c r="AA29" s="181"/>
+      <c r="AB29" s="181"/>
+      <c r="AC29" s="181"/>
+      <c r="AD29" s="181"/>
+      <c r="AE29" s="182"/>
+      <c r="AF29" s="177"/>
+      <c r="AG29" s="178"/>
+      <c r="AH29" s="178"/>
+      <c r="AI29" s="179"/>
     </row>
     <row r="30" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="14"/>
-      <c r="B30" s="122"/>
-      <c r="C30" s="123"/>
-      <c r="D30" s="124"/>
-      <c r="E30" s="125"/>
-      <c r="F30" s="126"/>
-      <c r="G30" s="122"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="123"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="129"/>
-      <c r="L30" s="129"/>
-      <c r="M30" s="129"/>
-      <c r="N30" s="129"/>
-      <c r="O30" s="129"/>
-      <c r="P30" s="130"/>
-      <c r="Q30" s="131"/>
-      <c r="R30" s="132"/>
-      <c r="S30" s="132"/>
-      <c r="T30" s="132"/>
-      <c r="U30" s="132"/>
-      <c r="V30" s="132"/>
-      <c r="W30" s="132"/>
-      <c r="X30" s="132"/>
-      <c r="Y30" s="132"/>
-      <c r="Z30" s="132"/>
-      <c r="AA30" s="132"/>
-      <c r="AB30" s="132"/>
-      <c r="AC30" s="132"/>
-      <c r="AD30" s="132"/>
-      <c r="AE30" s="133"/>
-      <c r="AF30" s="128"/>
-      <c r="AG30" s="129"/>
-      <c r="AH30" s="129"/>
-      <c r="AI30" s="130"/>
+      <c r="B30" s="171"/>
+      <c r="C30" s="172"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="175"/>
+      <c r="G30" s="171"/>
+      <c r="H30" s="176"/>
+      <c r="I30" s="172"/>
+      <c r="J30" s="177"/>
+      <c r="K30" s="178"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="178"/>
+      <c r="N30" s="178"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="179"/>
+      <c r="Q30" s="180"/>
+      <c r="R30" s="181"/>
+      <c r="S30" s="181"/>
+      <c r="T30" s="181"/>
+      <c r="U30" s="181"/>
+      <c r="V30" s="181"/>
+      <c r="W30" s="181"/>
+      <c r="X30" s="181"/>
+      <c r="Y30" s="181"/>
+      <c r="Z30" s="181"/>
+      <c r="AA30" s="181"/>
+      <c r="AB30" s="181"/>
+      <c r="AC30" s="181"/>
+      <c r="AD30" s="181"/>
+      <c r="AE30" s="182"/>
+      <c r="AF30" s="177"/>
+      <c r="AG30" s="178"/>
+      <c r="AH30" s="178"/>
+      <c r="AI30" s="179"/>
     </row>
     <row r="31" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="14"/>
-      <c r="B31" s="122"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="124"/>
-      <c r="E31" s="125"/>
-      <c r="F31" s="126"/>
-      <c r="G31" s="122"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="123"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="129"/>
-      <c r="M31" s="129"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="129"/>
-      <c r="P31" s="130"/>
-      <c r="Q31" s="131"/>
-      <c r="R31" s="132"/>
-      <c r="S31" s="132"/>
-      <c r="T31" s="132"/>
-      <c r="U31" s="132"/>
-      <c r="V31" s="132"/>
-      <c r="W31" s="132"/>
-      <c r="X31" s="132"/>
-      <c r="Y31" s="132"/>
-      <c r="Z31" s="132"/>
-      <c r="AA31" s="132"/>
-      <c r="AB31" s="132"/>
-      <c r="AC31" s="132"/>
-      <c r="AD31" s="132"/>
-      <c r="AE31" s="133"/>
-      <c r="AF31" s="128"/>
-      <c r="AG31" s="129"/>
-      <c r="AH31" s="129"/>
-      <c r="AI31" s="130"/>
+      <c r="B31" s="171"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="171"/>
+      <c r="H31" s="176"/>
+      <c r="I31" s="172"/>
+      <c r="J31" s="177"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="178"/>
+      <c r="N31" s="178"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="179"/>
+      <c r="Q31" s="180"/>
+      <c r="R31" s="181"/>
+      <c r="S31" s="181"/>
+      <c r="T31" s="181"/>
+      <c r="U31" s="181"/>
+      <c r="V31" s="181"/>
+      <c r="W31" s="181"/>
+      <c r="X31" s="181"/>
+      <c r="Y31" s="181"/>
+      <c r="Z31" s="181"/>
+      <c r="AA31" s="181"/>
+      <c r="AB31" s="181"/>
+      <c r="AC31" s="181"/>
+      <c r="AD31" s="181"/>
+      <c r="AE31" s="182"/>
+      <c r="AF31" s="177"/>
+      <c r="AG31" s="178"/>
+      <c r="AH31" s="178"/>
+      <c r="AI31" s="179"/>
     </row>
     <row r="32" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="14"/>
-      <c r="B32" s="122"/>
-      <c r="C32" s="123"/>
-      <c r="D32" s="124"/>
-      <c r="E32" s="125"/>
-      <c r="F32" s="126"/>
-      <c r="G32" s="122"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="123"/>
-      <c r="J32" s="128"/>
-      <c r="K32" s="134"/>
-      <c r="L32" s="129"/>
-      <c r="M32" s="129"/>
-      <c r="N32" s="129"/>
-      <c r="O32" s="129"/>
-      <c r="P32" s="130"/>
-      <c r="Q32" s="131"/>
-      <c r="R32" s="132"/>
-      <c r="S32" s="132"/>
-      <c r="T32" s="132"/>
-      <c r="U32" s="132"/>
-      <c r="V32" s="132"/>
-      <c r="W32" s="132"/>
-      <c r="X32" s="132"/>
-      <c r="Y32" s="132"/>
-      <c r="Z32" s="132"/>
-      <c r="AA32" s="132"/>
-      <c r="AB32" s="132"/>
-      <c r="AC32" s="132"/>
-      <c r="AD32" s="132"/>
-      <c r="AE32" s="133"/>
-      <c r="AF32" s="128"/>
-      <c r="AG32" s="129"/>
-      <c r="AH32" s="129"/>
-      <c r="AI32" s="130"/>
+      <c r="B32" s="171"/>
+      <c r="C32" s="172"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="175"/>
+      <c r="G32" s="171"/>
+      <c r="H32" s="176"/>
+      <c r="I32" s="172"/>
+      <c r="J32" s="177"/>
+      <c r="K32" s="183"/>
+      <c r="L32" s="178"/>
+      <c r="M32" s="178"/>
+      <c r="N32" s="178"/>
+      <c r="O32" s="178"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="180"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="181"/>
+      <c r="T32" s="181"/>
+      <c r="U32" s="181"/>
+      <c r="V32" s="181"/>
+      <c r="W32" s="181"/>
+      <c r="X32" s="181"/>
+      <c r="Y32" s="181"/>
+      <c r="Z32" s="181"/>
+      <c r="AA32" s="181"/>
+      <c r="AB32" s="181"/>
+      <c r="AC32" s="181"/>
+      <c r="AD32" s="181"/>
+      <c r="AE32" s="182"/>
+      <c r="AF32" s="177"/>
+      <c r="AG32" s="178"/>
+      <c r="AH32" s="178"/>
+      <c r="AI32" s="179"/>
     </row>
     <row r="33" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="14"/>
-      <c r="B33" s="122"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="124"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="126"/>
-      <c r="G33" s="122"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="128"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="129"/>
-      <c r="M33" s="129"/>
-      <c r="N33" s="129"/>
-      <c r="O33" s="129"/>
-      <c r="P33" s="130"/>
-      <c r="Q33" s="131"/>
-      <c r="R33" s="132"/>
-      <c r="S33" s="132"/>
-      <c r="T33" s="132"/>
-      <c r="U33" s="132"/>
-      <c r="V33" s="132"/>
-      <c r="W33" s="132"/>
-      <c r="X33" s="132"/>
-      <c r="Y33" s="132"/>
-      <c r="Z33" s="132"/>
-      <c r="AA33" s="132"/>
-      <c r="AB33" s="132"/>
-      <c r="AC33" s="132"/>
-      <c r="AD33" s="132"/>
-      <c r="AE33" s="133"/>
-      <c r="AF33" s="128"/>
-      <c r="AG33" s="129"/>
-      <c r="AH33" s="129"/>
-      <c r="AI33" s="130"/>
+      <c r="B33" s="171"/>
+      <c r="C33" s="172"/>
+      <c r="D33" s="173"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="175"/>
+      <c r="G33" s="171"/>
+      <c r="H33" s="176"/>
+      <c r="I33" s="172"/>
+      <c r="J33" s="177"/>
+      <c r="K33" s="178"/>
+      <c r="L33" s="178"/>
+      <c r="M33" s="178"/>
+      <c r="N33" s="178"/>
+      <c r="O33" s="178"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="180"/>
+      <c r="R33" s="181"/>
+      <c r="S33" s="181"/>
+      <c r="T33" s="181"/>
+      <c r="U33" s="181"/>
+      <c r="V33" s="181"/>
+      <c r="W33" s="181"/>
+      <c r="X33" s="181"/>
+      <c r="Y33" s="181"/>
+      <c r="Z33" s="181"/>
+      <c r="AA33" s="181"/>
+      <c r="AB33" s="181"/>
+      <c r="AC33" s="181"/>
+      <c r="AD33" s="181"/>
+      <c r="AE33" s="182"/>
+      <c r="AF33" s="177"/>
+      <c r="AG33" s="178"/>
+      <c r="AH33" s="178"/>
+      <c r="AI33" s="179"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:N2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="S1:Z3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="G33:I33"/>
@@ -10241,6 +10080,167 @@
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="Q32:AE32"/>
     <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="Q7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:N2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -31206,7 +31206,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -31242,7 +31242,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4F791D-6B2B-40BA-A89E-17F0158261A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C929FE-3E6E-471E-9051-21DC0EF22027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="455">
   <si>
     <t>テストデータシート名</t>
     <rPh sb="9" eb="10">
@@ -6281,6 +6281,10 @@
   </si>
   <si>
     <t>単体テスト仕様書(メッセージ)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リクエストID：</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -20245,7 +20249,9 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="11.5" thickBot="1">
-      <c r="A8" s="27"/>
+      <c r="A8" s="27" t="s">
+        <v>454</v>
+      </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28"/>
       <c r="D8" s="27"/>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C929FE-3E6E-471E-9051-21DC0EF22027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7C8697-C734-4FD0-8D68-66541F6804AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="【テストターゲット名】_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="【テストターゲット名】_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="【リクエストID】_リクエスト単体" sheetId="24" r:id="rId4"/>
     <sheet name="取引単体" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【テストターゲット名】_リクエスト単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$295</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【テストターゲット名】_リクエスト単体!$A$1:$R$314</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$314</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【テストターゲット名】_リクエスト単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -7232,6 +7232,93 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -7330,93 +7417,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8871,55 +8871,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="137" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="146" t="s">
+      <c r="P1" s="167"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="168"/>
+      <c r="S1" s="175" t="s">
         <v>453</v>
       </c>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
-      <c r="V1" s="147"/>
-      <c r="W1" s="147"/>
-      <c r="X1" s="147"/>
-      <c r="Y1" s="147"/>
-      <c r="Z1" s="148"/>
-      <c r="AA1" s="122" t="s">
+      <c r="T1" s="176"/>
+      <c r="U1" s="176"/>
+      <c r="V1" s="176"/>
+      <c r="W1" s="176"/>
+      <c r="X1" s="176"/>
+      <c r="Y1" s="176"/>
+      <c r="Z1" s="177"/>
+      <c r="AA1" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="123"/>
-      <c r="AC1" s="124" t="str">
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="153" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="126"/>
-      <c r="AG1" s="131" t="str">
+      <c r="AD1" s="154"/>
+      <c r="AE1" s="154"/>
+      <c r="AF1" s="155"/>
+      <c r="AG1" s="160" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="132"/>
-      <c r="AI1" s="133"/>
+      <c r="AH1" s="161"/>
+      <c r="AI1" s="162"/>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
       <c r="AL1" s="23"/>
@@ -8927,51 +8927,51 @@
       <c r="AN1" s="24"/>
     </row>
     <row r="2" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="149"/>
-      <c r="T2" s="150"/>
-      <c r="U2" s="150"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
-      <c r="Z2" s="151"/>
-      <c r="AA2" s="122" t="s">
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="170"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="171"/>
+      <c r="S2" s="178"/>
+      <c r="T2" s="179"/>
+      <c r="U2" s="179"/>
+      <c r="V2" s="179"/>
+      <c r="W2" s="179"/>
+      <c r="X2" s="179"/>
+      <c r="Y2" s="179"/>
+      <c r="Z2" s="180"/>
+      <c r="AA2" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="AB2" s="123"/>
-      <c r="AC2" s="134" t="str">
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="163" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="135"/>
-      <c r="AF2" s="136"/>
-      <c r="AG2" s="131" t="str">
+      <c r="AD2" s="164"/>
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="165"/>
+      <c r="AG2" s="160" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="132"/>
-      <c r="AI2" s="133"/>
+      <c r="AH2" s="161"/>
+      <c r="AI2" s="162"/>
       <c r="AJ2" s="23"/>
       <c r="AK2" s="23"/>
       <c r="AL2" s="23"/>
@@ -8979,43 +8979,43 @@
       <c r="AN2" s="23"/>
     </row>
     <row r="3" spans="1:40" s="22" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="144"/>
-      <c r="Q3" s="144"/>
-      <c r="R3" s="145"/>
-      <c r="S3" s="152"/>
-      <c r="T3" s="153"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="153"/>
-      <c r="Y3" s="153"/>
-      <c r="Z3" s="154"/>
-      <c r="AA3" s="122"/>
-      <c r="AB3" s="123"/>
-      <c r="AC3" s="124"/>
-      <c r="AD3" s="125"/>
-      <c r="AE3" s="125"/>
-      <c r="AF3" s="126"/>
-      <c r="AG3" s="131"/>
-      <c r="AH3" s="132"/>
-      <c r="AI3" s="133"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
+      <c r="O3" s="172"/>
+      <c r="P3" s="173"/>
+      <c r="Q3" s="173"/>
+      <c r="R3" s="174"/>
+      <c r="S3" s="181"/>
+      <c r="T3" s="182"/>
+      <c r="U3" s="182"/>
+      <c r="V3" s="182"/>
+      <c r="W3" s="182"/>
+      <c r="X3" s="182"/>
+      <c r="Y3" s="182"/>
+      <c r="Z3" s="183"/>
+      <c r="AA3" s="151"/>
+      <c r="AB3" s="152"/>
+      <c r="AC3" s="153"/>
+      <c r="AD3" s="154"/>
+      <c r="AE3" s="154"/>
+      <c r="AF3" s="155"/>
+      <c r="AG3" s="160"/>
+      <c r="AH3" s="161"/>
+      <c r="AI3" s="162"/>
       <c r="AJ3" s="23"/>
       <c r="AK3" s="23"/>
       <c r="AL3" s="23"/>
@@ -9052,1020 +9052,1181 @@
       <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="155" t="s">
+      <c r="C7" s="136"/>
+      <c r="D7" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="157"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="155" t="s">
+      <c r="E7" s="137"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="157"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="155" t="s">
+      <c r="H7" s="137"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="157"/>
-      <c r="L7" s="157"/>
-      <c r="M7" s="157"/>
-      <c r="N7" s="157"/>
-      <c r="O7" s="157"/>
-      <c r="P7" s="156"/>
-      <c r="Q7" s="155" t="s">
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
+      <c r="M7" s="137"/>
+      <c r="N7" s="137"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="R7" s="157"/>
-      <c r="S7" s="157"/>
-      <c r="T7" s="157"/>
-      <c r="U7" s="157"/>
-      <c r="V7" s="157"/>
-      <c r="W7" s="157"/>
-      <c r="X7" s="157"/>
-      <c r="Y7" s="157"/>
-      <c r="Z7" s="157"/>
-      <c r="AA7" s="157"/>
-      <c r="AB7" s="157"/>
-      <c r="AC7" s="157"/>
-      <c r="AD7" s="157"/>
-      <c r="AE7" s="156"/>
-      <c r="AF7" s="155" t="s">
+      <c r="R7" s="137"/>
+      <c r="S7" s="137"/>
+      <c r="T7" s="137"/>
+      <c r="U7" s="137"/>
+      <c r="V7" s="137"/>
+      <c r="W7" s="137"/>
+      <c r="X7" s="137"/>
+      <c r="Y7" s="137"/>
+      <c r="Z7" s="137"/>
+      <c r="AA7" s="137"/>
+      <c r="AB7" s="137"/>
+      <c r="AC7" s="137"/>
+      <c r="AD7" s="137"/>
+      <c r="AE7" s="136"/>
+      <c r="AF7" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="AG7" s="157"/>
-      <c r="AH7" s="157"/>
-      <c r="AI7" s="156"/>
+      <c r="AG7" s="137"/>
+      <c r="AH7" s="137"/>
+      <c r="AI7" s="136"/>
     </row>
     <row r="8" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="15"/>
-      <c r="B8" s="158"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="160"/>
-      <c r="E8" s="161"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="163"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="159"/>
-      <c r="J8" s="165"/>
-      <c r="K8" s="166"/>
-      <c r="L8" s="166"/>
-      <c r="M8" s="166"/>
-      <c r="N8" s="166"/>
-      <c r="O8" s="166"/>
-      <c r="P8" s="167"/>
-      <c r="Q8" s="168"/>
-      <c r="R8" s="169"/>
-      <c r="S8" s="169"/>
-      <c r="T8" s="169"/>
-      <c r="U8" s="169"/>
-      <c r="V8" s="169"/>
-      <c r="W8" s="169"/>
-      <c r="X8" s="169"/>
-      <c r="Y8" s="169"/>
-      <c r="Z8" s="169"/>
-      <c r="AA8" s="169"/>
-      <c r="AB8" s="169"/>
-      <c r="AC8" s="169"/>
-      <c r="AD8" s="169"/>
-      <c r="AE8" s="170"/>
-      <c r="AF8" s="165"/>
-      <c r="AG8" s="166"/>
-      <c r="AH8" s="166"/>
-      <c r="AI8" s="167"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="145"/>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
+      <c r="M8" s="146"/>
+      <c r="N8" s="146"/>
+      <c r="O8" s="146"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="148"/>
+      <c r="R8" s="149"/>
+      <c r="S8" s="149"/>
+      <c r="T8" s="149"/>
+      <c r="U8" s="149"/>
+      <c r="V8" s="149"/>
+      <c r="W8" s="149"/>
+      <c r="X8" s="149"/>
+      <c r="Y8" s="149"/>
+      <c r="Z8" s="149"/>
+      <c r="AA8" s="149"/>
+      <c r="AB8" s="149"/>
+      <c r="AC8" s="149"/>
+      <c r="AD8" s="149"/>
+      <c r="AE8" s="150"/>
+      <c r="AF8" s="145"/>
+      <c r="AG8" s="146"/>
+      <c r="AH8" s="146"/>
+      <c r="AI8" s="147"/>
     </row>
     <row r="9" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="14"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="172"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="174"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="173"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="172"/>
-      <c r="J9" s="177"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-      <c r="M9" s="178"/>
-      <c r="N9" s="178"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="179"/>
-      <c r="Q9" s="180"/>
-      <c r="R9" s="181"/>
-      <c r="S9" s="181"/>
-      <c r="T9" s="181"/>
-      <c r="U9" s="181"/>
-      <c r="V9" s="181"/>
-      <c r="W9" s="181"/>
-      <c r="X9" s="181"/>
-      <c r="Y9" s="181"/>
-      <c r="Z9" s="181"/>
-      <c r="AA9" s="181"/>
-      <c r="AB9" s="181"/>
-      <c r="AC9" s="181"/>
-      <c r="AD9" s="181"/>
-      <c r="AE9" s="182"/>
-      <c r="AF9" s="177"/>
-      <c r="AG9" s="178"/>
-      <c r="AH9" s="178"/>
-      <c r="AI9" s="179"/>
+      <c r="B9" s="122"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="129"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="129"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="132"/>
+      <c r="T9" s="132"/>
+      <c r="U9" s="132"/>
+      <c r="V9" s="132"/>
+      <c r="W9" s="132"/>
+      <c r="X9" s="132"/>
+      <c r="Y9" s="132"/>
+      <c r="Z9" s="132"/>
+      <c r="AA9" s="132"/>
+      <c r="AB9" s="132"/>
+      <c r="AC9" s="132"/>
+      <c r="AD9" s="132"/>
+      <c r="AE9" s="133"/>
+      <c r="AF9" s="128"/>
+      <c r="AG9" s="129"/>
+      <c r="AH9" s="129"/>
+      <c r="AI9" s="130"/>
     </row>
     <row r="10" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="14"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="172"/>
-      <c r="D10" s="173"/>
-      <c r="E10" s="174"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="171"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="172"/>
-      <c r="J10" s="177"/>
-      <c r="K10" s="178"/>
-      <c r="L10" s="178"/>
-      <c r="M10" s="178"/>
-      <c r="N10" s="178"/>
-      <c r="O10" s="178"/>
-      <c r="P10" s="179"/>
-      <c r="Q10" s="180"/>
-      <c r="R10" s="181"/>
-      <c r="S10" s="181"/>
-      <c r="T10" s="181"/>
-      <c r="U10" s="181"/>
-      <c r="V10" s="181"/>
-      <c r="W10" s="181"/>
-      <c r="X10" s="181"/>
-      <c r="Y10" s="181"/>
-      <c r="Z10" s="181"/>
-      <c r="AA10" s="181"/>
-      <c r="AB10" s="181"/>
-      <c r="AC10" s="181"/>
-      <c r="AD10" s="181"/>
-      <c r="AE10" s="182"/>
-      <c r="AF10" s="177"/>
-      <c r="AG10" s="178"/>
-      <c r="AH10" s="178"/>
-      <c r="AI10" s="179"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="123"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="129"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="129"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="132"/>
+      <c r="S10" s="132"/>
+      <c r="T10" s="132"/>
+      <c r="U10" s="132"/>
+      <c r="V10" s="132"/>
+      <c r="W10" s="132"/>
+      <c r="X10" s="132"/>
+      <c r="Y10" s="132"/>
+      <c r="Z10" s="132"/>
+      <c r="AA10" s="132"/>
+      <c r="AB10" s="132"/>
+      <c r="AC10" s="132"/>
+      <c r="AD10" s="132"/>
+      <c r="AE10" s="133"/>
+      <c r="AF10" s="128"/>
+      <c r="AG10" s="129"/>
+      <c r="AH10" s="129"/>
+      <c r="AI10" s="130"/>
     </row>
     <row r="11" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="14"/>
-      <c r="B11" s="171"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="172"/>
-      <c r="J11" s="177"/>
-      <c r="K11" s="178"/>
-      <c r="L11" s="178"/>
-      <c r="M11" s="178"/>
-      <c r="N11" s="178"/>
-      <c r="O11" s="178"/>
-      <c r="P11" s="179"/>
-      <c r="Q11" s="180"/>
-      <c r="R11" s="181"/>
-      <c r="S11" s="181"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="182"/>
-      <c r="AF11" s="177"/>
-      <c r="AG11" s="178"/>
-      <c r="AH11" s="178"/>
-      <c r="AI11" s="179"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
+      <c r="N11" s="129"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="132"/>
+      <c r="U11" s="132"/>
+      <c r="V11" s="132"/>
+      <c r="W11" s="132"/>
+      <c r="X11" s="132"/>
+      <c r="Y11" s="132"/>
+      <c r="Z11" s="132"/>
+      <c r="AA11" s="132"/>
+      <c r="AB11" s="132"/>
+      <c r="AC11" s="132"/>
+      <c r="AD11" s="132"/>
+      <c r="AE11" s="133"/>
+      <c r="AF11" s="128"/>
+      <c r="AG11" s="129"/>
+      <c r="AH11" s="129"/>
+      <c r="AI11" s="130"/>
     </row>
     <row r="12" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="14"/>
-      <c r="B12" s="171"/>
-      <c r="C12" s="172"/>
-      <c r="D12" s="173"/>
-      <c r="E12" s="174"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="172"/>
-      <c r="J12" s="177"/>
-      <c r="K12" s="178"/>
-      <c r="L12" s="178"/>
-      <c r="M12" s="178"/>
-      <c r="N12" s="178"/>
-      <c r="O12" s="178"/>
-      <c r="P12" s="179"/>
-      <c r="Q12" s="180"/>
-      <c r="R12" s="181"/>
-      <c r="S12" s="181"/>
-      <c r="T12" s="181"/>
-      <c r="U12" s="181"/>
-      <c r="V12" s="181"/>
-      <c r="W12" s="181"/>
-      <c r="X12" s="181"/>
-      <c r="Y12" s="181"/>
-      <c r="Z12" s="181"/>
-      <c r="AA12" s="181"/>
-      <c r="AB12" s="181"/>
-      <c r="AC12" s="181"/>
-      <c r="AD12" s="181"/>
-      <c r="AE12" s="182"/>
-      <c r="AF12" s="177"/>
-      <c r="AG12" s="178"/>
-      <c r="AH12" s="178"/>
-      <c r="AI12" s="179"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+      <c r="M12" s="129"/>
+      <c r="N12" s="129"/>
+      <c r="O12" s="129"/>
+      <c r="P12" s="130"/>
+      <c r="Q12" s="131"/>
+      <c r="R12" s="132"/>
+      <c r="S12" s="132"/>
+      <c r="T12" s="132"/>
+      <c r="U12" s="132"/>
+      <c r="V12" s="132"/>
+      <c r="W12" s="132"/>
+      <c r="X12" s="132"/>
+      <c r="Y12" s="132"/>
+      <c r="Z12" s="132"/>
+      <c r="AA12" s="132"/>
+      <c r="AB12" s="132"/>
+      <c r="AC12" s="132"/>
+      <c r="AD12" s="132"/>
+      <c r="AE12" s="133"/>
+      <c r="AF12" s="128"/>
+      <c r="AG12" s="129"/>
+      <c r="AH12" s="129"/>
+      <c r="AI12" s="130"/>
     </row>
     <row r="13" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="14"/>
-      <c r="B13" s="171"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="173"/>
-      <c r="E13" s="174"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="171"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="172"/>
-      <c r="J13" s="177"/>
-      <c r="K13" s="178"/>
-      <c r="L13" s="178"/>
-      <c r="M13" s="178"/>
-      <c r="N13" s="178"/>
-      <c r="O13" s="178"/>
-      <c r="P13" s="179"/>
-      <c r="Q13" s="180"/>
-      <c r="R13" s="181"/>
-      <c r="S13" s="181"/>
-      <c r="T13" s="181"/>
-      <c r="U13" s="181"/>
-      <c r="V13" s="181"/>
-      <c r="W13" s="181"/>
-      <c r="X13" s="181"/>
-      <c r="Y13" s="181"/>
-      <c r="Z13" s="181"/>
-      <c r="AA13" s="181"/>
-      <c r="AB13" s="181"/>
-      <c r="AC13" s="181"/>
-      <c r="AD13" s="181"/>
-      <c r="AE13" s="182"/>
-      <c r="AF13" s="177"/>
-      <c r="AG13" s="178"/>
-      <c r="AH13" s="178"/>
-      <c r="AI13" s="179"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="132"/>
+      <c r="T13" s="132"/>
+      <c r="U13" s="132"/>
+      <c r="V13" s="132"/>
+      <c r="W13" s="132"/>
+      <c r="X13" s="132"/>
+      <c r="Y13" s="132"/>
+      <c r="Z13" s="132"/>
+      <c r="AA13" s="132"/>
+      <c r="AB13" s="132"/>
+      <c r="AC13" s="132"/>
+      <c r="AD13" s="132"/>
+      <c r="AE13" s="133"/>
+      <c r="AF13" s="128"/>
+      <c r="AG13" s="129"/>
+      <c r="AH13" s="129"/>
+      <c r="AI13" s="130"/>
     </row>
     <row r="14" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="14"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="174"/>
-      <c r="F14" s="175"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="176"/>
-      <c r="I14" s="172"/>
-      <c r="J14" s="177"/>
-      <c r="K14" s="178"/>
-      <c r="L14" s="178"/>
-      <c r="M14" s="178"/>
-      <c r="N14" s="178"/>
-      <c r="O14" s="178"/>
-      <c r="P14" s="179"/>
-      <c r="Q14" s="180"/>
-      <c r="R14" s="181"/>
-      <c r="S14" s="181"/>
-      <c r="T14" s="181"/>
-      <c r="U14" s="181"/>
-      <c r="V14" s="181"/>
-      <c r="W14" s="181"/>
-      <c r="X14" s="181"/>
-      <c r="Y14" s="181"/>
-      <c r="Z14" s="181"/>
-      <c r="AA14" s="181"/>
-      <c r="AB14" s="181"/>
-      <c r="AC14" s="181"/>
-      <c r="AD14" s="181"/>
-      <c r="AE14" s="182"/>
-      <c r="AF14" s="177"/>
-      <c r="AG14" s="178"/>
-      <c r="AH14" s="178"/>
-      <c r="AI14" s="179"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="132"/>
+      <c r="S14" s="132"/>
+      <c r="T14" s="132"/>
+      <c r="U14" s="132"/>
+      <c r="V14" s="132"/>
+      <c r="W14" s="132"/>
+      <c r="X14" s="132"/>
+      <c r="Y14" s="132"/>
+      <c r="Z14" s="132"/>
+      <c r="AA14" s="132"/>
+      <c r="AB14" s="132"/>
+      <c r="AC14" s="132"/>
+      <c r="AD14" s="132"/>
+      <c r="AE14" s="133"/>
+      <c r="AF14" s="128"/>
+      <c r="AG14" s="129"/>
+      <c r="AH14" s="129"/>
+      <c r="AI14" s="130"/>
     </row>
     <row r="15" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="172"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="174"/>
-      <c r="F15" s="175"/>
-      <c r="G15" s="171"/>
-      <c r="H15" s="176"/>
-      <c r="I15" s="172"/>
-      <c r="J15" s="177"/>
-      <c r="K15" s="178"/>
-      <c r="L15" s="178"/>
-      <c r="M15" s="178"/>
-      <c r="N15" s="178"/>
-      <c r="O15" s="178"/>
-      <c r="P15" s="179"/>
-      <c r="Q15" s="180"/>
-      <c r="R15" s="181"/>
-      <c r="S15" s="181"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="181"/>
-      <c r="V15" s="181"/>
-      <c r="W15" s="181"/>
-      <c r="X15" s="181"/>
-      <c r="Y15" s="181"/>
-      <c r="Z15" s="181"/>
-      <c r="AA15" s="181"/>
-      <c r="AB15" s="181"/>
-      <c r="AC15" s="181"/>
-      <c r="AD15" s="181"/>
-      <c r="AE15" s="182"/>
-      <c r="AF15" s="177"/>
-      <c r="AG15" s="178"/>
-      <c r="AH15" s="178"/>
-      <c r="AI15" s="179"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="129"/>
+      <c r="L15" s="129"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="129"/>
+      <c r="O15" s="129"/>
+      <c r="P15" s="130"/>
+      <c r="Q15" s="131"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="132"/>
+      <c r="U15" s="132"/>
+      <c r="V15" s="132"/>
+      <c r="W15" s="132"/>
+      <c r="X15" s="132"/>
+      <c r="Y15" s="132"/>
+      <c r="Z15" s="132"/>
+      <c r="AA15" s="132"/>
+      <c r="AB15" s="132"/>
+      <c r="AC15" s="132"/>
+      <c r="AD15" s="132"/>
+      <c r="AE15" s="133"/>
+      <c r="AF15" s="128"/>
+      <c r="AG15" s="129"/>
+      <c r="AH15" s="129"/>
+      <c r="AI15" s="130"/>
     </row>
     <row r="16" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="14"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="172"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="176"/>
-      <c r="I16" s="172"/>
-      <c r="J16" s="177"/>
-      <c r="K16" s="178"/>
-      <c r="L16" s="178"/>
-      <c r="M16" s="178"/>
-      <c r="N16" s="178"/>
-      <c r="O16" s="178"/>
-      <c r="P16" s="179"/>
-      <c r="Q16" s="180"/>
-      <c r="R16" s="181"/>
-      <c r="S16" s="181"/>
-      <c r="T16" s="181"/>
-      <c r="U16" s="181"/>
-      <c r="V16" s="181"/>
-      <c r="W16" s="181"/>
-      <c r="X16" s="181"/>
-      <c r="Y16" s="181"/>
-      <c r="Z16" s="181"/>
-      <c r="AA16" s="181"/>
-      <c r="AB16" s="181"/>
-      <c r="AC16" s="181"/>
-      <c r="AD16" s="181"/>
-      <c r="AE16" s="182"/>
-      <c r="AF16" s="177"/>
-      <c r="AG16" s="178"/>
-      <c r="AH16" s="178"/>
-      <c r="AI16" s="179"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="129"/>
+      <c r="M16" s="129"/>
+      <c r="N16" s="129"/>
+      <c r="O16" s="129"/>
+      <c r="P16" s="130"/>
+      <c r="Q16" s="131"/>
+      <c r="R16" s="132"/>
+      <c r="S16" s="132"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="132"/>
+      <c r="V16" s="132"/>
+      <c r="W16" s="132"/>
+      <c r="X16" s="132"/>
+      <c r="Y16" s="132"/>
+      <c r="Z16" s="132"/>
+      <c r="AA16" s="132"/>
+      <c r="AB16" s="132"/>
+      <c r="AC16" s="132"/>
+      <c r="AD16" s="132"/>
+      <c r="AE16" s="133"/>
+      <c r="AF16" s="128"/>
+      <c r="AG16" s="129"/>
+      <c r="AH16" s="129"/>
+      <c r="AI16" s="130"/>
     </row>
     <row r="17" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="14"/>
-      <c r="B17" s="171"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="175"/>
-      <c r="G17" s="171"/>
-      <c r="H17" s="176"/>
-      <c r="I17" s="172"/>
-      <c r="J17" s="177"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="178"/>
-      <c r="M17" s="178"/>
-      <c r="N17" s="178"/>
-      <c r="O17" s="178"/>
-      <c r="P17" s="179"/>
-      <c r="Q17" s="180"/>
-      <c r="R17" s="181"/>
-      <c r="S17" s="181"/>
-      <c r="T17" s="181"/>
-      <c r="U17" s="181"/>
-      <c r="V17" s="181"/>
-      <c r="W17" s="181"/>
-      <c r="X17" s="181"/>
-      <c r="Y17" s="181"/>
-      <c r="Z17" s="181"/>
-      <c r="AA17" s="181"/>
-      <c r="AB17" s="181"/>
-      <c r="AC17" s="181"/>
-      <c r="AD17" s="181"/>
-      <c r="AE17" s="182"/>
-      <c r="AF17" s="177"/>
-      <c r="AG17" s="178"/>
-      <c r="AH17" s="178"/>
-      <c r="AI17" s="179"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="129"/>
+      <c r="N17" s="129"/>
+      <c r="O17" s="129"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="131"/>
+      <c r="R17" s="132"/>
+      <c r="S17" s="132"/>
+      <c r="T17" s="132"/>
+      <c r="U17" s="132"/>
+      <c r="V17" s="132"/>
+      <c r="W17" s="132"/>
+      <c r="X17" s="132"/>
+      <c r="Y17" s="132"/>
+      <c r="Z17" s="132"/>
+      <c r="AA17" s="132"/>
+      <c r="AB17" s="132"/>
+      <c r="AC17" s="132"/>
+      <c r="AD17" s="132"/>
+      <c r="AE17" s="133"/>
+      <c r="AF17" s="128"/>
+      <c r="AG17" s="129"/>
+      <c r="AH17" s="129"/>
+      <c r="AI17" s="130"/>
     </row>
     <row r="18" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="14"/>
-      <c r="B18" s="171"/>
-      <c r="C18" s="172"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="174"/>
-      <c r="F18" s="175"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="176"/>
-      <c r="I18" s="172"/>
-      <c r="J18" s="177"/>
-      <c r="K18" s="178"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="178"/>
-      <c r="N18" s="178"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="179"/>
-      <c r="Q18" s="180"/>
-      <c r="R18" s="181"/>
-      <c r="S18" s="181"/>
-      <c r="T18" s="181"/>
-      <c r="U18" s="181"/>
-      <c r="V18" s="181"/>
-      <c r="W18" s="181"/>
-      <c r="X18" s="181"/>
-      <c r="Y18" s="181"/>
-      <c r="Z18" s="181"/>
-      <c r="AA18" s="181"/>
-      <c r="AB18" s="181"/>
-      <c r="AC18" s="181"/>
-      <c r="AD18" s="181"/>
-      <c r="AE18" s="182"/>
-      <c r="AF18" s="177"/>
-      <c r="AG18" s="178"/>
-      <c r="AH18" s="178"/>
-      <c r="AI18" s="179"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="129"/>
+      <c r="M18" s="129"/>
+      <c r="N18" s="129"/>
+      <c r="O18" s="129"/>
+      <c r="P18" s="130"/>
+      <c r="Q18" s="131"/>
+      <c r="R18" s="132"/>
+      <c r="S18" s="132"/>
+      <c r="T18" s="132"/>
+      <c r="U18" s="132"/>
+      <c r="V18" s="132"/>
+      <c r="W18" s="132"/>
+      <c r="X18" s="132"/>
+      <c r="Y18" s="132"/>
+      <c r="Z18" s="132"/>
+      <c r="AA18" s="132"/>
+      <c r="AB18" s="132"/>
+      <c r="AC18" s="132"/>
+      <c r="AD18" s="132"/>
+      <c r="AE18" s="133"/>
+      <c r="AF18" s="128"/>
+      <c r="AG18" s="129"/>
+      <c r="AH18" s="129"/>
+      <c r="AI18" s="130"/>
     </row>
     <row r="19" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="14"/>
-      <c r="B19" s="171"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="174"/>
-      <c r="F19" s="175"/>
-      <c r="G19" s="171"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="172"/>
-      <c r="J19" s="177"/>
-      <c r="K19" s="178"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="178"/>
-      <c r="N19" s="178"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="180"/>
-      <c r="R19" s="181"/>
-      <c r="S19" s="181"/>
-      <c r="T19" s="181"/>
-      <c r="U19" s="181"/>
-      <c r="V19" s="181"/>
-      <c r="W19" s="181"/>
-      <c r="X19" s="181"/>
-      <c r="Y19" s="181"/>
-      <c r="Z19" s="181"/>
-      <c r="AA19" s="181"/>
-      <c r="AB19" s="181"/>
-      <c r="AC19" s="181"/>
-      <c r="AD19" s="181"/>
-      <c r="AE19" s="182"/>
-      <c r="AF19" s="177"/>
-      <c r="AG19" s="178"/>
-      <c r="AH19" s="178"/>
-      <c r="AI19" s="179"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="129"/>
+      <c r="L19" s="129"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="129"/>
+      <c r="O19" s="129"/>
+      <c r="P19" s="130"/>
+      <c r="Q19" s="131"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="132"/>
+      <c r="T19" s="132"/>
+      <c r="U19" s="132"/>
+      <c r="V19" s="132"/>
+      <c r="W19" s="132"/>
+      <c r="X19" s="132"/>
+      <c r="Y19" s="132"/>
+      <c r="Z19" s="132"/>
+      <c r="AA19" s="132"/>
+      <c r="AB19" s="132"/>
+      <c r="AC19" s="132"/>
+      <c r="AD19" s="132"/>
+      <c r="AE19" s="133"/>
+      <c r="AF19" s="128"/>
+      <c r="AG19" s="129"/>
+      <c r="AH19" s="129"/>
+      <c r="AI19" s="130"/>
     </row>
     <row r="20" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="14"/>
-      <c r="B20" s="171"/>
-      <c r="C20" s="172"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="174"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="176"/>
-      <c r="I20" s="172"/>
-      <c r="J20" s="177"/>
-      <c r="K20" s="178"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="178"/>
-      <c r="N20" s="178"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="179"/>
-      <c r="Q20" s="180"/>
-      <c r="R20" s="181"/>
-      <c r="S20" s="181"/>
-      <c r="T20" s="181"/>
-      <c r="U20" s="181"/>
-      <c r="V20" s="181"/>
-      <c r="W20" s="181"/>
-      <c r="X20" s="181"/>
-      <c r="Y20" s="181"/>
-      <c r="Z20" s="181"/>
-      <c r="AA20" s="181"/>
-      <c r="AB20" s="181"/>
-      <c r="AC20" s="181"/>
-      <c r="AD20" s="181"/>
-      <c r="AE20" s="182"/>
-      <c r="AF20" s="177"/>
-      <c r="AG20" s="178"/>
-      <c r="AH20" s="178"/>
-      <c r="AI20" s="179"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="129"/>
+      <c r="M20" s="129"/>
+      <c r="N20" s="129"/>
+      <c r="O20" s="129"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="132"/>
+      <c r="S20" s="132"/>
+      <c r="T20" s="132"/>
+      <c r="U20" s="132"/>
+      <c r="V20" s="132"/>
+      <c r="W20" s="132"/>
+      <c r="X20" s="132"/>
+      <c r="Y20" s="132"/>
+      <c r="Z20" s="132"/>
+      <c r="AA20" s="132"/>
+      <c r="AB20" s="132"/>
+      <c r="AC20" s="132"/>
+      <c r="AD20" s="132"/>
+      <c r="AE20" s="133"/>
+      <c r="AF20" s="128"/>
+      <c r="AG20" s="129"/>
+      <c r="AH20" s="129"/>
+      <c r="AI20" s="130"/>
     </row>
     <row r="21" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="14"/>
-      <c r="B21" s="171"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="174"/>
-      <c r="F21" s="175"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="176"/>
-      <c r="I21" s="172"/>
-      <c r="J21" s="177"/>
-      <c r="K21" s="178"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="178"/>
-      <c r="N21" s="178"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="179"/>
-      <c r="Q21" s="180"/>
-      <c r="R21" s="181"/>
-      <c r="S21" s="181"/>
-      <c r="T21" s="181"/>
-      <c r="U21" s="181"/>
-      <c r="V21" s="181"/>
-      <c r="W21" s="181"/>
-      <c r="X21" s="181"/>
-      <c r="Y21" s="181"/>
-      <c r="Z21" s="181"/>
-      <c r="AA21" s="181"/>
-      <c r="AB21" s="181"/>
-      <c r="AC21" s="181"/>
-      <c r="AD21" s="181"/>
-      <c r="AE21" s="182"/>
-      <c r="AF21" s="177"/>
-      <c r="AG21" s="178"/>
-      <c r="AH21" s="178"/>
-      <c r="AI21" s="179"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="129"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="129"/>
+      <c r="O21" s="129"/>
+      <c r="P21" s="130"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="132"/>
+      <c r="S21" s="132"/>
+      <c r="T21" s="132"/>
+      <c r="U21" s="132"/>
+      <c r="V21" s="132"/>
+      <c r="W21" s="132"/>
+      <c r="X21" s="132"/>
+      <c r="Y21" s="132"/>
+      <c r="Z21" s="132"/>
+      <c r="AA21" s="132"/>
+      <c r="AB21" s="132"/>
+      <c r="AC21" s="132"/>
+      <c r="AD21" s="132"/>
+      <c r="AE21" s="133"/>
+      <c r="AF21" s="128"/>
+      <c r="AG21" s="129"/>
+      <c r="AH21" s="129"/>
+      <c r="AI21" s="130"/>
     </row>
     <row r="22" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="14"/>
-      <c r="B22" s="171"/>
-      <c r="C22" s="172"/>
-      <c r="D22" s="173"/>
-      <c r="E22" s="174"/>
-      <c r="F22" s="175"/>
-      <c r="G22" s="171"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="172"/>
-      <c r="J22" s="177"/>
-      <c r="K22" s="178"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="178"/>
-      <c r="N22" s="178"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="179"/>
-      <c r="Q22" s="180"/>
-      <c r="R22" s="181"/>
-      <c r="S22" s="181"/>
-      <c r="T22" s="181"/>
-      <c r="U22" s="181"/>
-      <c r="V22" s="181"/>
-      <c r="W22" s="181"/>
-      <c r="X22" s="181"/>
-      <c r="Y22" s="181"/>
-      <c r="Z22" s="181"/>
-      <c r="AA22" s="181"/>
-      <c r="AB22" s="181"/>
-      <c r="AC22" s="181"/>
-      <c r="AD22" s="181"/>
-      <c r="AE22" s="182"/>
-      <c r="AF22" s="177"/>
-      <c r="AG22" s="178"/>
-      <c r="AH22" s="178"/>
-      <c r="AI22" s="179"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="122"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="129"/>
+      <c r="M22" s="129"/>
+      <c r="N22" s="129"/>
+      <c r="O22" s="129"/>
+      <c r="P22" s="130"/>
+      <c r="Q22" s="131"/>
+      <c r="R22" s="132"/>
+      <c r="S22" s="132"/>
+      <c r="T22" s="132"/>
+      <c r="U22" s="132"/>
+      <c r="V22" s="132"/>
+      <c r="W22" s="132"/>
+      <c r="X22" s="132"/>
+      <c r="Y22" s="132"/>
+      <c r="Z22" s="132"/>
+      <c r="AA22" s="132"/>
+      <c r="AB22" s="132"/>
+      <c r="AC22" s="132"/>
+      <c r="AD22" s="132"/>
+      <c r="AE22" s="133"/>
+      <c r="AF22" s="128"/>
+      <c r="AG22" s="129"/>
+      <c r="AH22" s="129"/>
+      <c r="AI22" s="130"/>
     </row>
     <row r="23" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="14"/>
-      <c r="B23" s="171"/>
-      <c r="C23" s="172"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="174"/>
-      <c r="F23" s="175"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="176"/>
-      <c r="I23" s="172"/>
-      <c r="J23" s="177"/>
-      <c r="K23" s="178"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="178"/>
-      <c r="N23" s="178"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="179"/>
-      <c r="Q23" s="180"/>
-      <c r="R23" s="181"/>
-      <c r="S23" s="181"/>
-      <c r="T23" s="181"/>
-      <c r="U23" s="181"/>
-      <c r="V23" s="181"/>
-      <c r="W23" s="181"/>
-      <c r="X23" s="181"/>
-      <c r="Y23" s="181"/>
-      <c r="Z23" s="181"/>
-      <c r="AA23" s="181"/>
-      <c r="AB23" s="181"/>
-      <c r="AC23" s="181"/>
-      <c r="AD23" s="181"/>
-      <c r="AE23" s="182"/>
-      <c r="AF23" s="177"/>
-      <c r="AG23" s="178"/>
-      <c r="AH23" s="178"/>
-      <c r="AI23" s="179"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="129"/>
+      <c r="N23" s="129"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="130"/>
+      <c r="Q23" s="131"/>
+      <c r="R23" s="132"/>
+      <c r="S23" s="132"/>
+      <c r="T23" s="132"/>
+      <c r="U23" s="132"/>
+      <c r="V23" s="132"/>
+      <c r="W23" s="132"/>
+      <c r="X23" s="132"/>
+      <c r="Y23" s="132"/>
+      <c r="Z23" s="132"/>
+      <c r="AA23" s="132"/>
+      <c r="AB23" s="132"/>
+      <c r="AC23" s="132"/>
+      <c r="AD23" s="132"/>
+      <c r="AE23" s="133"/>
+      <c r="AF23" s="128"/>
+      <c r="AG23" s="129"/>
+      <c r="AH23" s="129"/>
+      <c r="AI23" s="130"/>
     </row>
     <row r="24" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="14"/>
-      <c r="B24" s="171"/>
-      <c r="C24" s="172"/>
-      <c r="D24" s="173"/>
-      <c r="E24" s="174"/>
-      <c r="F24" s="175"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="176"/>
-      <c r="I24" s="172"/>
-      <c r="J24" s="177"/>
-      <c r="K24" s="178"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="178"/>
-      <c r="N24" s="178"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="179"/>
-      <c r="Q24" s="180"/>
-      <c r="R24" s="181"/>
-      <c r="S24" s="181"/>
-      <c r="T24" s="181"/>
-      <c r="U24" s="181"/>
-      <c r="V24" s="181"/>
-      <c r="W24" s="181"/>
-      <c r="X24" s="181"/>
-      <c r="Y24" s="181"/>
-      <c r="Z24" s="181"/>
-      <c r="AA24" s="181"/>
-      <c r="AB24" s="181"/>
-      <c r="AC24" s="181"/>
-      <c r="AD24" s="181"/>
-      <c r="AE24" s="182"/>
-      <c r="AF24" s="177"/>
-      <c r="AG24" s="178"/>
-      <c r="AH24" s="178"/>
-      <c r="AI24" s="179"/>
+      <c r="B24" s="122"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="129"/>
+      <c r="M24" s="129"/>
+      <c r="N24" s="129"/>
+      <c r="O24" s="129"/>
+      <c r="P24" s="130"/>
+      <c r="Q24" s="131"/>
+      <c r="R24" s="132"/>
+      <c r="S24" s="132"/>
+      <c r="T24" s="132"/>
+      <c r="U24" s="132"/>
+      <c r="V24" s="132"/>
+      <c r="W24" s="132"/>
+      <c r="X24" s="132"/>
+      <c r="Y24" s="132"/>
+      <c r="Z24" s="132"/>
+      <c r="AA24" s="132"/>
+      <c r="AB24" s="132"/>
+      <c r="AC24" s="132"/>
+      <c r="AD24" s="132"/>
+      <c r="AE24" s="133"/>
+      <c r="AF24" s="128"/>
+      <c r="AG24" s="129"/>
+      <c r="AH24" s="129"/>
+      <c r="AI24" s="130"/>
     </row>
     <row r="25" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="14"/>
-      <c r="B25" s="171"/>
-      <c r="C25" s="172"/>
-      <c r="D25" s="173"/>
-      <c r="E25" s="174"/>
-      <c r="F25" s="175"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="176"/>
-      <c r="I25" s="172"/>
-      <c r="J25" s="177"/>
-      <c r="K25" s="178"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="178"/>
-      <c r="N25" s="178"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="179"/>
-      <c r="Q25" s="180"/>
-      <c r="R25" s="181"/>
-      <c r="S25" s="181"/>
-      <c r="T25" s="181"/>
-      <c r="U25" s="181"/>
-      <c r="V25" s="181"/>
-      <c r="W25" s="181"/>
-      <c r="X25" s="181"/>
-      <c r="Y25" s="181"/>
-      <c r="Z25" s="181"/>
-      <c r="AA25" s="181"/>
-      <c r="AB25" s="181"/>
-      <c r="AC25" s="181"/>
-      <c r="AD25" s="181"/>
-      <c r="AE25" s="182"/>
-      <c r="AF25" s="177"/>
-      <c r="AG25" s="178"/>
-      <c r="AH25" s="178"/>
-      <c r="AI25" s="179"/>
+      <c r="B25" s="122"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="122"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="129"/>
+      <c r="M25" s="129"/>
+      <c r="N25" s="129"/>
+      <c r="O25" s="129"/>
+      <c r="P25" s="130"/>
+      <c r="Q25" s="131"/>
+      <c r="R25" s="132"/>
+      <c r="S25" s="132"/>
+      <c r="T25" s="132"/>
+      <c r="U25" s="132"/>
+      <c r="V25" s="132"/>
+      <c r="W25" s="132"/>
+      <c r="X25" s="132"/>
+      <c r="Y25" s="132"/>
+      <c r="Z25" s="132"/>
+      <c r="AA25" s="132"/>
+      <c r="AB25" s="132"/>
+      <c r="AC25" s="132"/>
+      <c r="AD25" s="132"/>
+      <c r="AE25" s="133"/>
+      <c r="AF25" s="128"/>
+      <c r="AG25" s="129"/>
+      <c r="AH25" s="129"/>
+      <c r="AI25" s="130"/>
     </row>
     <row r="26" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="14"/>
-      <c r="B26" s="171"/>
-      <c r="C26" s="172"/>
-      <c r="D26" s="173"/>
-      <c r="E26" s="174"/>
-      <c r="F26" s="175"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="176"/>
-      <c r="I26" s="172"/>
-      <c r="J26" s="177"/>
-      <c r="K26" s="178"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="178"/>
-      <c r="N26" s="178"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="179"/>
-      <c r="Q26" s="180"/>
-      <c r="R26" s="181"/>
-      <c r="S26" s="181"/>
-      <c r="T26" s="181"/>
-      <c r="U26" s="181"/>
-      <c r="V26" s="181"/>
-      <c r="W26" s="181"/>
-      <c r="X26" s="181"/>
-      <c r="Y26" s="181"/>
-      <c r="Z26" s="181"/>
-      <c r="AA26" s="181"/>
-      <c r="AB26" s="181"/>
-      <c r="AC26" s="181"/>
-      <c r="AD26" s="181"/>
-      <c r="AE26" s="182"/>
-      <c r="AF26" s="177"/>
-      <c r="AG26" s="178"/>
-      <c r="AH26" s="178"/>
-      <c r="AI26" s="179"/>
+      <c r="B26" s="122"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="122"/>
+      <c r="H26" s="127"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="129"/>
+      <c r="L26" s="129"/>
+      <c r="M26" s="129"/>
+      <c r="N26" s="129"/>
+      <c r="O26" s="129"/>
+      <c r="P26" s="130"/>
+      <c r="Q26" s="131"/>
+      <c r="R26" s="132"/>
+      <c r="S26" s="132"/>
+      <c r="T26" s="132"/>
+      <c r="U26" s="132"/>
+      <c r="V26" s="132"/>
+      <c r="W26" s="132"/>
+      <c r="X26" s="132"/>
+      <c r="Y26" s="132"/>
+      <c r="Z26" s="132"/>
+      <c r="AA26" s="132"/>
+      <c r="AB26" s="132"/>
+      <c r="AC26" s="132"/>
+      <c r="AD26" s="132"/>
+      <c r="AE26" s="133"/>
+      <c r="AF26" s="128"/>
+      <c r="AG26" s="129"/>
+      <c r="AH26" s="129"/>
+      <c r="AI26" s="130"/>
     </row>
     <row r="27" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="14"/>
-      <c r="B27" s="171"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="173"/>
-      <c r="E27" s="174"/>
-      <c r="F27" s="175"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="176"/>
-      <c r="I27" s="172"/>
-      <c r="J27" s="177"/>
-      <c r="K27" s="178"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="178"/>
-      <c r="N27" s="178"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="179"/>
-      <c r="Q27" s="180"/>
-      <c r="R27" s="181"/>
-      <c r="S27" s="181"/>
-      <c r="T27" s="181"/>
-      <c r="U27" s="181"/>
-      <c r="V27" s="181"/>
-      <c r="W27" s="181"/>
-      <c r="X27" s="181"/>
-      <c r="Y27" s="181"/>
-      <c r="Z27" s="181"/>
-      <c r="AA27" s="181"/>
-      <c r="AB27" s="181"/>
-      <c r="AC27" s="181"/>
-      <c r="AD27" s="181"/>
-      <c r="AE27" s="182"/>
-      <c r="AF27" s="177"/>
-      <c r="AG27" s="178"/>
-      <c r="AH27" s="178"/>
-      <c r="AI27" s="179"/>
+      <c r="B27" s="122"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="127"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="129"/>
+      <c r="M27" s="129"/>
+      <c r="N27" s="129"/>
+      <c r="O27" s="129"/>
+      <c r="P27" s="130"/>
+      <c r="Q27" s="131"/>
+      <c r="R27" s="132"/>
+      <c r="S27" s="132"/>
+      <c r="T27" s="132"/>
+      <c r="U27" s="132"/>
+      <c r="V27" s="132"/>
+      <c r="W27" s="132"/>
+      <c r="X27" s="132"/>
+      <c r="Y27" s="132"/>
+      <c r="Z27" s="132"/>
+      <c r="AA27" s="132"/>
+      <c r="AB27" s="132"/>
+      <c r="AC27" s="132"/>
+      <c r="AD27" s="132"/>
+      <c r="AE27" s="133"/>
+      <c r="AF27" s="128"/>
+      <c r="AG27" s="129"/>
+      <c r="AH27" s="129"/>
+      <c r="AI27" s="130"/>
     </row>
     <row r="28" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="14"/>
-      <c r="B28" s="171"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="175"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="176"/>
-      <c r="I28" s="172"/>
-      <c r="J28" s="177"/>
-      <c r="K28" s="178"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="178"/>
-      <c r="N28" s="178"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="179"/>
-      <c r="Q28" s="180"/>
-      <c r="R28" s="181"/>
-      <c r="S28" s="181"/>
-      <c r="T28" s="181"/>
-      <c r="U28" s="181"/>
-      <c r="V28" s="181"/>
-      <c r="W28" s="181"/>
-      <c r="X28" s="181"/>
-      <c r="Y28" s="181"/>
-      <c r="Z28" s="181"/>
-      <c r="AA28" s="181"/>
-      <c r="AB28" s="181"/>
-      <c r="AC28" s="181"/>
-      <c r="AD28" s="181"/>
-      <c r="AE28" s="182"/>
-      <c r="AF28" s="177"/>
-      <c r="AG28" s="178"/>
-      <c r="AH28" s="178"/>
-      <c r="AI28" s="179"/>
+      <c r="B28" s="122"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="126"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="123"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="129"/>
+      <c r="L28" s="129"/>
+      <c r="M28" s="129"/>
+      <c r="N28" s="129"/>
+      <c r="O28" s="129"/>
+      <c r="P28" s="130"/>
+      <c r="Q28" s="131"/>
+      <c r="R28" s="132"/>
+      <c r="S28" s="132"/>
+      <c r="T28" s="132"/>
+      <c r="U28" s="132"/>
+      <c r="V28" s="132"/>
+      <c r="W28" s="132"/>
+      <c r="X28" s="132"/>
+      <c r="Y28" s="132"/>
+      <c r="Z28" s="132"/>
+      <c r="AA28" s="132"/>
+      <c r="AB28" s="132"/>
+      <c r="AC28" s="132"/>
+      <c r="AD28" s="132"/>
+      <c r="AE28" s="133"/>
+      <c r="AF28" s="128"/>
+      <c r="AG28" s="129"/>
+      <c r="AH28" s="129"/>
+      <c r="AI28" s="130"/>
     </row>
     <row r="29" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="14"/>
-      <c r="B29" s="171"/>
-      <c r="C29" s="172"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="175"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="176"/>
-      <c r="I29" s="172"/>
-      <c r="J29" s="177"/>
-      <c r="K29" s="178"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="178"/>
-      <c r="N29" s="178"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="179"/>
-      <c r="Q29" s="180"/>
-      <c r="R29" s="181"/>
-      <c r="S29" s="181"/>
-      <c r="T29" s="181"/>
-      <c r="U29" s="181"/>
-      <c r="V29" s="181"/>
-      <c r="W29" s="181"/>
-      <c r="X29" s="181"/>
-      <c r="Y29" s="181"/>
-      <c r="Z29" s="181"/>
-      <c r="AA29" s="181"/>
-      <c r="AB29" s="181"/>
-      <c r="AC29" s="181"/>
-      <c r="AD29" s="181"/>
-      <c r="AE29" s="182"/>
-      <c r="AF29" s="177"/>
-      <c r="AG29" s="178"/>
-      <c r="AH29" s="178"/>
-      <c r="AI29" s="179"/>
+      <c r="B29" s="122"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="124"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="123"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="129"/>
+      <c r="L29" s="129"/>
+      <c r="M29" s="129"/>
+      <c r="N29" s="129"/>
+      <c r="O29" s="129"/>
+      <c r="P29" s="130"/>
+      <c r="Q29" s="131"/>
+      <c r="R29" s="132"/>
+      <c r="S29" s="132"/>
+      <c r="T29" s="132"/>
+      <c r="U29" s="132"/>
+      <c r="V29" s="132"/>
+      <c r="W29" s="132"/>
+      <c r="X29" s="132"/>
+      <c r="Y29" s="132"/>
+      <c r="Z29" s="132"/>
+      <c r="AA29" s="132"/>
+      <c r="AB29" s="132"/>
+      <c r="AC29" s="132"/>
+      <c r="AD29" s="132"/>
+      <c r="AE29" s="133"/>
+      <c r="AF29" s="128"/>
+      <c r="AG29" s="129"/>
+      <c r="AH29" s="129"/>
+      <c r="AI29" s="130"/>
     </row>
     <row r="30" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="14"/>
-      <c r="B30" s="171"/>
-      <c r="C30" s="172"/>
-      <c r="D30" s="173"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="175"/>
-      <c r="G30" s="171"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="172"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="178"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="178"/>
-      <c r="N30" s="178"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="179"/>
-      <c r="Q30" s="180"/>
-      <c r="R30" s="181"/>
-      <c r="S30" s="181"/>
-      <c r="T30" s="181"/>
-      <c r="U30" s="181"/>
-      <c r="V30" s="181"/>
-      <c r="W30" s="181"/>
-      <c r="X30" s="181"/>
-      <c r="Y30" s="181"/>
-      <c r="Z30" s="181"/>
-      <c r="AA30" s="181"/>
-      <c r="AB30" s="181"/>
-      <c r="AC30" s="181"/>
-      <c r="AD30" s="181"/>
-      <c r="AE30" s="182"/>
-      <c r="AF30" s="177"/>
-      <c r="AG30" s="178"/>
-      <c r="AH30" s="178"/>
-      <c r="AI30" s="179"/>
+      <c r="B30" s="122"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="126"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="127"/>
+      <c r="I30" s="123"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="129"/>
+      <c r="L30" s="129"/>
+      <c r="M30" s="129"/>
+      <c r="N30" s="129"/>
+      <c r="O30" s="129"/>
+      <c r="P30" s="130"/>
+      <c r="Q30" s="131"/>
+      <c r="R30" s="132"/>
+      <c r="S30" s="132"/>
+      <c r="T30" s="132"/>
+      <c r="U30" s="132"/>
+      <c r="V30" s="132"/>
+      <c r="W30" s="132"/>
+      <c r="X30" s="132"/>
+      <c r="Y30" s="132"/>
+      <c r="Z30" s="132"/>
+      <c r="AA30" s="132"/>
+      <c r="AB30" s="132"/>
+      <c r="AC30" s="132"/>
+      <c r="AD30" s="132"/>
+      <c r="AE30" s="133"/>
+      <c r="AF30" s="128"/>
+      <c r="AG30" s="129"/>
+      <c r="AH30" s="129"/>
+      <c r="AI30" s="130"/>
     </row>
     <row r="31" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="14"/>
-      <c r="B31" s="171"/>
-      <c r="C31" s="172"/>
-      <c r="D31" s="173"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="171"/>
-      <c r="H31" s="176"/>
-      <c r="I31" s="172"/>
-      <c r="J31" s="177"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="178"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="180"/>
-      <c r="R31" s="181"/>
-      <c r="S31" s="181"/>
-      <c r="T31" s="181"/>
-      <c r="U31" s="181"/>
-      <c r="V31" s="181"/>
-      <c r="W31" s="181"/>
-      <c r="X31" s="181"/>
-      <c r="Y31" s="181"/>
-      <c r="Z31" s="181"/>
-      <c r="AA31" s="181"/>
-      <c r="AB31" s="181"/>
-      <c r="AC31" s="181"/>
-      <c r="AD31" s="181"/>
-      <c r="AE31" s="182"/>
-      <c r="AF31" s="177"/>
-      <c r="AG31" s="178"/>
-      <c r="AH31" s="178"/>
-      <c r="AI31" s="179"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="127"/>
+      <c r="I31" s="123"/>
+      <c r="J31" s="128"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="129"/>
+      <c r="M31" s="129"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="129"/>
+      <c r="P31" s="130"/>
+      <c r="Q31" s="131"/>
+      <c r="R31" s="132"/>
+      <c r="S31" s="132"/>
+      <c r="T31" s="132"/>
+      <c r="U31" s="132"/>
+      <c r="V31" s="132"/>
+      <c r="W31" s="132"/>
+      <c r="X31" s="132"/>
+      <c r="Y31" s="132"/>
+      <c r="Z31" s="132"/>
+      <c r="AA31" s="132"/>
+      <c r="AB31" s="132"/>
+      <c r="AC31" s="132"/>
+      <c r="AD31" s="132"/>
+      <c r="AE31" s="133"/>
+      <c r="AF31" s="128"/>
+      <c r="AG31" s="129"/>
+      <c r="AH31" s="129"/>
+      <c r="AI31" s="130"/>
     </row>
     <row r="32" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="14"/>
-      <c r="B32" s="171"/>
-      <c r="C32" s="172"/>
-      <c r="D32" s="173"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="175"/>
-      <c r="G32" s="171"/>
-      <c r="H32" s="176"/>
-      <c r="I32" s="172"/>
-      <c r="J32" s="177"/>
-      <c r="K32" s="183"/>
-      <c r="L32" s="178"/>
-      <c r="M32" s="178"/>
-      <c r="N32" s="178"/>
-      <c r="O32" s="178"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="180"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="181"/>
-      <c r="T32" s="181"/>
-      <c r="U32" s="181"/>
-      <c r="V32" s="181"/>
-      <c r="W32" s="181"/>
-      <c r="X32" s="181"/>
-      <c r="Y32" s="181"/>
-      <c r="Z32" s="181"/>
-      <c r="AA32" s="181"/>
-      <c r="AB32" s="181"/>
-      <c r="AC32" s="181"/>
-      <c r="AD32" s="181"/>
-      <c r="AE32" s="182"/>
-      <c r="AF32" s="177"/>
-      <c r="AG32" s="178"/>
-      <c r="AH32" s="178"/>
-      <c r="AI32" s="179"/>
+      <c r="B32" s="122"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="127"/>
+      <c r="I32" s="123"/>
+      <c r="J32" s="128"/>
+      <c r="K32" s="134"/>
+      <c r="L32" s="129"/>
+      <c r="M32" s="129"/>
+      <c r="N32" s="129"/>
+      <c r="O32" s="129"/>
+      <c r="P32" s="130"/>
+      <c r="Q32" s="131"/>
+      <c r="R32" s="132"/>
+      <c r="S32" s="132"/>
+      <c r="T32" s="132"/>
+      <c r="U32" s="132"/>
+      <c r="V32" s="132"/>
+      <c r="W32" s="132"/>
+      <c r="X32" s="132"/>
+      <c r="Y32" s="132"/>
+      <c r="Z32" s="132"/>
+      <c r="AA32" s="132"/>
+      <c r="AB32" s="132"/>
+      <c r="AC32" s="132"/>
+      <c r="AD32" s="132"/>
+      <c r="AE32" s="133"/>
+      <c r="AF32" s="128"/>
+      <c r="AG32" s="129"/>
+      <c r="AH32" s="129"/>
+      <c r="AI32" s="130"/>
     </row>
     <row r="33" spans="1:35" s="13" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="14"/>
-      <c r="B33" s="171"/>
-      <c r="C33" s="172"/>
-      <c r="D33" s="173"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="175"/>
-      <c r="G33" s="171"/>
-      <c r="H33" s="176"/>
-      <c r="I33" s="172"/>
-      <c r="J33" s="177"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="178"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="178"/>
-      <c r="O33" s="178"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="180"/>
-      <c r="R33" s="181"/>
-      <c r="S33" s="181"/>
-      <c r="T33" s="181"/>
-      <c r="U33" s="181"/>
-      <c r="V33" s="181"/>
-      <c r="W33" s="181"/>
-      <c r="X33" s="181"/>
-      <c r="Y33" s="181"/>
-      <c r="Z33" s="181"/>
-      <c r="AA33" s="181"/>
-      <c r="AB33" s="181"/>
-      <c r="AC33" s="181"/>
-      <c r="AD33" s="181"/>
-      <c r="AE33" s="182"/>
-      <c r="AF33" s="177"/>
-      <c r="AG33" s="178"/>
-      <c r="AH33" s="178"/>
-      <c r="AI33" s="179"/>
+      <c r="B33" s="122"/>
+      <c r="C33" s="123"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="122"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="129"/>
+      <c r="M33" s="129"/>
+      <c r="N33" s="129"/>
+      <c r="O33" s="129"/>
+      <c r="P33" s="130"/>
+      <c r="Q33" s="131"/>
+      <c r="R33" s="132"/>
+      <c r="S33" s="132"/>
+      <c r="T33" s="132"/>
+      <c r="U33" s="132"/>
+      <c r="V33" s="132"/>
+      <c r="W33" s="132"/>
+      <c r="X33" s="132"/>
+      <c r="Y33" s="132"/>
+      <c r="Z33" s="132"/>
+      <c r="AA33" s="132"/>
+      <c r="AB33" s="132"/>
+      <c r="AC33" s="132"/>
+      <c r="AD33" s="132"/>
+      <c r="AE33" s="133"/>
+      <c r="AF33" s="128"/>
+      <c r="AG33" s="129"/>
+      <c r="AH33" s="129"/>
+      <c r="AI33" s="130"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:N2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="Q7:AE7"/>
+    <mergeCell ref="AF7:AI7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="G33:I33"/>
@@ -10084,167 +10245,6 @@
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="Q32:AE32"/>
     <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q7:AE7"/>
-    <mergeCell ref="AF7:AI7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:N2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="S1:Z3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(メッセージ)_(取引ID)_(取引名).xlsx
@@ -10402,8 +10402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -10443,8 +10443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -10478,8 +10478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -10515,8 +10515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -10548,8 +10548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -10581,8 +10581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -10614,8 +10614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -10647,8 +10647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -10684,8 +10684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -10717,8 +10717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -10750,8 +10750,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -10785,8 +10785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -10818,8 +10818,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -10851,8 +10851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -10884,8 +10884,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -10921,8 +10921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -10954,8 +10954,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -10991,8 +10991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -11024,8 +11024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -11059,8 +11059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -11092,8 +11092,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -11125,8 +11125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -11158,8 +11158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -11193,8 +11193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -11226,8 +11226,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -11261,8 +11261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -11300,8 +11300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -11333,8 +11333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -11366,8 +11366,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -11399,8 +11399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -11436,8 +11436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -11469,8 +11469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -11510,8 +11510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -11543,8 +11543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -11576,8 +11576,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -11611,8 +11611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -11644,8 +11644,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -11677,8 +11677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -11712,8 +11712,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -11745,8 +11745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -11780,8 +11780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -11813,8 +11813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -11846,8 +11846,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -11879,8 +11879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -11912,8 +11912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -11945,8 +11945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -11980,8 +11980,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -12015,8 +12015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -12050,8 +12050,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -12087,8 +12087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -12120,8 +12120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -12153,8 +12153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -12186,8 +12186,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -12219,8 +12219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -12254,8 +12254,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -12287,8 +12287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -12320,8 +12320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -12353,8 +12353,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -12386,8 +12386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -12419,8 +12419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -12452,8 +12452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -12485,8 +12485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -12520,8 +12520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -12555,8 +12555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -12588,8 +12588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -12621,8 +12621,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -12654,8 +12654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -12687,8 +12687,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -12726,8 +12726,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -12759,8 +12759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -12794,8 +12794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -12829,8 +12829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -12862,8 +12862,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -12897,8 +12897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -12932,8 +12932,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -12971,8 +12971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -13006,8 +13006,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -13041,8 +13041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -13080,8 +13080,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -13113,8 +13113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -13148,8 +13148,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -13183,8 +13183,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -13216,8 +13216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -13251,8 +13251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -13290,8 +13290,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -13323,8 +13323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -13356,8 +13356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -13389,8 +13389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -13422,8 +13422,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -13457,8 +13457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -13490,8 +13490,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -13523,8 +13523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -13556,8 +13556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -13589,8 +13589,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -13624,8 +13624,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -13665,8 +13665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -13704,8 +13704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -13737,8 +13737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -13776,8 +13776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -13815,8 +13815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -13848,8 +13848,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -13889,8 +13889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -13924,8 +13924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -13957,8 +13957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -13990,8 +13990,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -14025,8 +14025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -14058,8 +14058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -14091,8 +14091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -14124,8 +14124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -14157,8 +14157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -14192,8 +14192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -14225,8 +14225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -14258,8 +14258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -14291,8 +14291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -14324,8 +14324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -14359,8 +14359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -14396,8 +14396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -14435,8 +14435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -14470,8 +14470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -14503,8 +14503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -14536,8 +14536,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -14577,8 +14577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -14612,8 +14612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -14645,8 +14645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -14678,8 +14678,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -14713,8 +14713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -14746,8 +14746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -14783,8 +14783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -14822,8 +14822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -14857,8 +14857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -14892,8 +14892,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -14927,8 +14927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -14962,8 +14962,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -14997,8 +14997,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -15030,8 +15030,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -15063,8 +15063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -15096,8 +15096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -15129,8 +15129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -15162,8 +15162,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -15199,8 +15199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -15232,8 +15232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -15267,8 +15267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -15300,8 +15300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -15333,8 +15333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -15366,8 +15366,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -15399,8 +15399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -15432,8 +15432,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -15465,8 +15465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -15498,8 +15498,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -15531,8 +15531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -15564,8 +15564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -15597,8 +15597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -15632,8 +15632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -15665,8 +15665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -15698,8 +15698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -15731,8 +15731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -15764,8 +15764,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -15797,8 +15797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -15830,8 +15830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -15865,8 +15865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -15898,8 +15898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -15931,8 +15931,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -15964,8 +15964,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -15997,8 +15997,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -16030,8 +16030,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -16063,8 +16063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -16096,8 +16096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -16129,8 +16129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -16164,8 +16164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -16199,8 +16199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -16240,8 +16240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -16277,8 +16277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -16314,8 +16314,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -16355,8 +16355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -16390,8 +16390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -16423,8 +16423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -16458,8 +16458,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -16491,8 +16491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -16528,8 +16528,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -16567,8 +16567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -16600,8 +16600,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -16633,8 +16633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -16666,8 +16666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -16699,8 +16699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -16732,8 +16732,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -16765,8 +16765,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -16800,8 +16800,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -16837,8 +16837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -16870,8 +16870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -16903,8 +16903,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -16936,8 +16936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -16969,8 +16969,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -17002,8 +17002,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -17035,8 +17035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -17068,8 +17068,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -17101,8 +17101,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -17134,8 +17134,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -17167,8 +17167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -17200,8 +17200,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -17233,8 +17233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -17270,8 +17270,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -17303,8 +17303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -17336,8 +17336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -17369,8 +17369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -17402,8 +17402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -17435,8 +17435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -17468,8 +17468,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -17501,8 +17501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -17534,8 +17534,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -17567,8 +17567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -17600,8 +17600,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -17633,8 +17633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -17666,8 +17666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -17699,8 +17699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -17732,8 +17732,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -17767,8 +17767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -17800,8 +17800,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -17833,8 +17833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -17868,8 +17868,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -17903,8 +17903,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -17944,8 +17944,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -17979,8 +17979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -18012,8 +18012,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -18045,8 +18045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -18078,8 +18078,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -18111,8 +18111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -18146,8 +18146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -18179,8 +18179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -18212,8 +18212,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -18245,8 +18245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -18278,8 +18278,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -18313,8 +18313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -18352,8 +18352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -18393,8 +18393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -18426,8 +18426,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -18463,8 +18463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -18496,8 +18496,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -18535,8 +18535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -18570,8 +18570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -18605,8 +18605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -18640,8 +18640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -18677,8 +18677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -18710,8 +18710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -18745,8 +18745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -18778,8 +18778,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -18811,8 +18811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -18844,8 +18844,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -18877,8 +18877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -18910,8 +18910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -18943,8 +18943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -18976,8 +18976,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -19009,8 +19009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -19042,8 +19042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -19075,8 +19075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -19110,8 +19110,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -19143,8 +19143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -19176,8 +19176,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -19209,8 +19209,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -19242,8 +19242,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -19275,8 +19275,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -19310,8 +19310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -19343,8 +19343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -19376,8 +19376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -19409,8 +19409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -19442,8 +19442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -19475,8 +19475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -19508,8 +19508,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -19541,8 +19541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -19576,8 +19576,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -19617,8 +19617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -19650,8 +19650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -19683,8 +19683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -19716,8 +19716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -19755,8 +19755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -19790,8 +19790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -19825,8 +19825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -19860,8 +19860,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -19897,8 +19897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -19930,8 +19930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -19963,8 +19963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -19996,8 +19996,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -20029,8 +20029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -20062,8 +20062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -20095,8 +20095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -20128,8 +20128,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -20335,8 +20335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -20376,8 +20376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -20411,8 +20411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -20448,8 +20448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -20481,8 +20481,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -20514,8 +20514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -20547,8 +20547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -20580,8 +20580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -20617,8 +20617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -20650,8 +20650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -20683,8 +20683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -20718,8 +20718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -20751,8 +20751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -20784,8 +20784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -20817,8 +20817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -20854,8 +20854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -20887,8 +20887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -20924,8 +20924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -20957,8 +20957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -20992,8 +20992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -21025,8 +21025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -21058,8 +21058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -21091,8 +21091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -21126,8 +21126,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -21159,8 +21159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -21194,8 +21194,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -21233,8 +21233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -21266,8 +21266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -21299,8 +21299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -21332,8 +21332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -21369,8 +21369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -21402,8 +21402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -21443,8 +21443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -21476,8 +21476,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -21509,8 +21509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -21544,8 +21544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -21577,8 +21577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -21610,8 +21610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -21645,8 +21645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -21678,8 +21678,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -21713,8 +21713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -21746,8 +21746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -21779,8 +21779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -21812,8 +21812,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -21845,8 +21845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -21878,8 +21878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -21913,8 +21913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -21948,8 +21948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -21983,8 +21983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -22020,8 +22020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -22053,8 +22053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -22086,8 +22086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -22119,8 +22119,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -22152,8 +22152,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -22187,8 +22187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -22220,8 +22220,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -22253,8 +22253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -22286,8 +22286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -22319,8 +22319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -22352,8 +22352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -22385,8 +22385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -22418,8 +22418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -22453,8 +22453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -22488,8 +22488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -22521,8 +22521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -22554,8 +22554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -22587,8 +22587,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -22620,8 +22620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -22659,8 +22659,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -22692,8 +22692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -22727,8 +22727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -22762,8 +22762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -22795,8 +22795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -22830,8 +22830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -22865,8 +22865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -22904,8 +22904,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -22939,8 +22939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -22974,8 +22974,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -23013,8 +23013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -23046,8 +23046,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -23081,8 +23081,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -23116,8 +23116,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -23149,8 +23149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -23184,8 +23184,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -23223,8 +23223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -23256,8 +23256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -23289,8 +23289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -23322,8 +23322,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -23355,8 +23355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -23390,8 +23390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -23423,8 +23423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -23456,8 +23456,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -23489,8 +23489,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -23522,8 +23522,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -23557,8 +23557,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -23598,8 +23598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -23637,8 +23637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -23670,8 +23670,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -23709,8 +23709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -23748,8 +23748,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -23781,8 +23781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -23822,8 +23822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -23857,8 +23857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -23890,8 +23890,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -23923,8 +23923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -23958,8 +23958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -23991,8 +23991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -24024,8 +24024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -24057,8 +24057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -24090,8 +24090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -24125,8 +24125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -24158,8 +24158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -24191,8 +24191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -24224,8 +24224,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -24257,8 +24257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -24292,8 +24292,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -24329,8 +24329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -24368,8 +24368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -24403,8 +24403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -24436,8 +24436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -24469,8 +24469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -24510,8 +24510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -24545,8 +24545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -24578,8 +24578,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -24611,8 +24611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -24646,8 +24646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -24679,8 +24679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -24716,8 +24716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -24755,8 +24755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -24790,8 +24790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -24825,8 +24825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -24860,8 +24860,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -24895,8 +24895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -24930,8 +24930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -24963,8 +24963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -24996,8 +24996,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -25029,8 +25029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -25062,8 +25062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -25095,8 +25095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -25132,8 +25132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -25165,8 +25165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -25200,8 +25200,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -25233,8 +25233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -25266,8 +25266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -25299,8 +25299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -25332,8 +25332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -25365,8 +25365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -25398,8 +25398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -25431,8 +25431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -25464,8 +25464,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -25497,8 +25497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -25530,8 +25530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -25565,8 +25565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -25598,8 +25598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -25631,8 +25631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -25664,8 +25664,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -25697,8 +25697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -25730,8 +25730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -25763,8 +25763,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -25798,8 +25798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -25831,8 +25831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -25864,8 +25864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -25897,8 +25897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -25930,8 +25930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -25963,8 +25963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -25996,8 +25996,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -26029,8 +26029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -26062,8 +26062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -26097,8 +26097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -26132,8 +26132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -26173,8 +26173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -26210,8 +26210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -26247,8 +26247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -26288,8 +26288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -26323,8 +26323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -26356,8 +26356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -26391,8 +26391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -26424,8 +26424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -26461,8 +26461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -26500,8 +26500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -26533,8 +26533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -26566,8 +26566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -26599,8 +26599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -26632,8 +26632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -26665,8 +26665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -26698,8 +26698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -26733,8 +26733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -26770,8 +26770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -26803,8 +26803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -26836,8 +26836,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -26869,8 +26869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -26902,8 +26902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -26935,8 +26935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -26968,8 +26968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -27001,8 +27001,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -27034,8 +27034,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -27067,8 +27067,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -27100,8 +27100,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -27133,8 +27133,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -27166,8 +27166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -27203,8 +27203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -27236,8 +27236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -27269,8 +27269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -27302,8 +27302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -27335,8 +27335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -27368,8 +27368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -27401,8 +27401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -27434,8 +27434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -27467,8 +27467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -27500,8 +27500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -27533,8 +27533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -27566,8 +27566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -27599,8 +27599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -27632,8 +27632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -27665,8 +27665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -27700,8 +27700,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -27733,8 +27733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -27766,8 +27766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -27801,8 +27801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -27836,8 +27836,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -27877,8 +27877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -27912,8 +27912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -27945,8 +27945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -27978,8 +27978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -28011,8 +28011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -28044,8 +28044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -28079,8 +28079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -28112,8 +28112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -28145,8 +28145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -28178,8 +28178,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -28211,8 +28211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -28246,8 +28246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -28285,8 +28285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -28326,8 +28326,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -28359,8 +28359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -28396,8 +28396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -28429,8 +28429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -28468,8 +28468,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -28503,8 +28503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -28538,8 +28538,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -28573,8 +28573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -28610,8 +28610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -28643,8 +28643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -28678,8 +28678,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -28711,8 +28711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -28744,8 +28744,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -28777,8 +28777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -28810,8 +28810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -28843,8 +28843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -28876,8 +28876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -28909,8 +28909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -28942,8 +28942,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -28975,8 +28975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -29008,8 +29008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -29043,8 +29043,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -29076,8 +29076,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -29109,8 +29109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -29142,8 +29142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -29175,8 +29175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -29208,8 +29208,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -29243,8 +29243,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -29276,8 +29276,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -29309,8 +29309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -29342,8 +29342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -29375,8 +29375,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -29408,8 +29408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -29441,8 +29441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -29474,8 +29474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -29509,8 +29509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -29550,8 +29550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -29583,8 +29583,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -29616,8 +29616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -29649,8 +29649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -29688,8 +29688,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -29723,8 +29723,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -29758,8 +29758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -29793,8 +29793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -29830,8 +29830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -29863,8 +29863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -29896,8 +29896,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -29929,8 +29929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -29962,8 +29962,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -29995,8 +29995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -30028,8 +30028,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -30061,8 +30061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -30094,8 +30094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -30137,8 +30137,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -30174,8 +30174,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -30211,8 +30211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -30272,8 +30272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-2-1</v>
       </c>
@@ -30307,8 +30307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-3-1</v>
       </c>
@@ -30342,8 +30342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-4-1</v>
       </c>
@@ -30377,8 +30377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -30416,8 +30416,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -30451,8 +30451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -30486,8 +30486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-4-1</v>
       </c>
@@ -30521,8 +30521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-5-1</v>
       </c>
@@ -30556,8 +30556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-6-1</v>
       </c>
@@ -30591,8 +30591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-7-1</v>
       </c>
@@ -30626,8 +30626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-8-1</v>
       </c>
@@ -30661,8 +30661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-9-1</v>
       </c>
@@ -30696,8 +30696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-10-1</v>
       </c>
@@ -30731,8 +30731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-11-1</v>
       </c>
@@ -31211,11 +31211,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C11),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -31247,11 +31247,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C12),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-1</v>
       </c>
